--- a/Financial Analysis/LCID.xlsx
+++ b/Financial Analysis/LCID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F025B2E0-39AE-4CD2-ACDF-2D6D7697CB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5F2BF2-0D17-49A6-AC41-7CB2A6FB7952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1AB2C153-F3A3-43B3-970A-67C6BEA1AC7C}"/>
   </bookViews>
@@ -315,7 +315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -337,6 +337,11 @@
     <xf numFmtId="3" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -408,13 +413,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
@@ -432,8 +437,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13045440" y="0"/>
-          <a:ext cx="0" cy="6202680"/>
+          <a:off x="13655040" y="0"/>
+          <a:ext cx="0" cy="7665720"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -783,17 +788,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>1.98</v>
+        <v>12.84</v>
       </c>
       <c r="E3" s="4">
-        <v>45889</v>
+        <v>46002</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45904</v>
+        <v>46002</v>
       </c>
       <c r="G3" s="4">
-        <v>45972</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -801,11 +806,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>3072.5</f>
-        <v>3072.5</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -814,7 +819,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>6083.55</v>
+        <v>4162.7280000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -822,11 +827,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1795.7+1030.1+776.7</f>
-        <v>3602.5</v>
+        <f>1635.1+701.9+656.2</f>
+        <v>2993.2</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -834,11 +839,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>2038.9</f>
-        <v>2038.9</v>
+        <f>2040.4</f>
+        <v>2040.4</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +852,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>1563.6</v>
+        <v>952.79999999999973</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -856,7 +861,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>4519.9500000000007</v>
+        <v>3209.9280000000003</v>
       </c>
     </row>
   </sheetData>
@@ -1028,11 +1033,11 @@
       <c r="T3" s="12">
         <v>3309</v>
       </c>
-      <c r="U3" s="12">
+      <c r="U3" s="13">
         <f>Q3*1.5</f>
         <v>4171.5</v>
       </c>
-      <c r="V3" s="12">
+      <c r="V3" s="13">
         <f>R3*1.7</f>
         <v>5268.3</v>
       </c>
@@ -1049,7 +1054,7 @@
         <f>SUM(O3:R3)</f>
         <v>10241</v>
       </c>
-      <c r="AD3" s="6">
+      <c r="AD3" s="14">
         <f>SUM(S3:V3)</f>
         <v>15857.8</v>
       </c>
@@ -1092,11 +1097,11 @@
       <c r="T4" s="12">
         <v>3863</v>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="13">
         <f>Q4*2.5</f>
         <v>4512.5</v>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="13">
         <f>R4*2.2</f>
         <v>7449.2000000000007</v>
       </c>
@@ -1113,7 +1118,7 @@
         <f>SUM(O4:R4)</f>
         <v>9029</v>
       </c>
-      <c r="AD4" s="6">
+      <c r="AD4" s="14">
         <f>SUM(S4:V4)</f>
         <v>18036.7</v>
       </c>
@@ -1169,8 +1174,7 @@
         <v>259.39999999999998</v>
       </c>
       <c r="U6" s="2">
-        <f>Q6*1.55</f>
-        <v>310</v>
+        <v>336.6</v>
       </c>
       <c r="V6" s="9">
         <f>R6*1.65</f>
@@ -1196,47 +1200,47 @@
       </c>
       <c r="AD6" s="9">
         <f>SUM(S6:V6)</f>
-        <v>1191.3249999999998</v>
+        <v>1217.925</v>
       </c>
       <c r="AE6" s="9">
-        <f>AD6*1.4</f>
-        <v>1667.8549999999996</v>
+        <f>AD6*1.5</f>
+        <v>1826.8874999999998</v>
       </c>
       <c r="AF6" s="9">
-        <f>AE6*1.35</f>
-        <v>2251.6042499999994</v>
+        <f>AE6*1.4</f>
+        <v>2557.6424999999995</v>
       </c>
       <c r="AG6" s="9">
-        <f>AF6*1.3</f>
-        <v>2927.0855249999995</v>
+        <f>AF6*1.35</f>
+        <v>3452.8173749999996</v>
       </c>
       <c r="AH6" s="9">
-        <f>AG6*1.25</f>
-        <v>3658.8569062499992</v>
+        <f>AG6*1.3</f>
+        <v>4488.6625875</v>
       </c>
       <c r="AI6" s="9">
-        <f>AH6*1.2</f>
-        <v>4390.6282874999988</v>
+        <f>AH6*1.25</f>
+        <v>5610.8282343749997</v>
       </c>
       <c r="AJ6" s="9">
-        <f>AI6*1.15</f>
-        <v>5049.2225306249984</v>
+        <f>AI6*1.2</f>
+        <v>6732.9938812499995</v>
       </c>
       <c r="AK6" s="9">
         <f t="shared" ref="AK6:AN6" si="0">AJ6*1.15</f>
-        <v>5806.6059102187473</v>
+        <v>7742.9429634374992</v>
       </c>
       <c r="AL6" s="9">
         <f t="shared" si="0"/>
-        <v>6677.5967967515589</v>
+        <v>8904.3844079531227</v>
       </c>
       <c r="AM6" s="9">
         <f t="shared" si="0"/>
-        <v>7679.2363162642923</v>
+        <v>10240.042069146089</v>
       </c>
       <c r="AN6" s="9">
         <f t="shared" si="0"/>
-        <v>8831.1217637039354</v>
+        <v>11776.048379518003</v>
       </c>
     </row>
     <row r="7" spans="2:40" x14ac:dyDescent="0.3">
@@ -1268,8 +1272,7 @@
         <v>531.79999999999995</v>
       </c>
       <c r="U7" s="6">
-        <f>U6-U8</f>
-        <v>604.5</v>
+        <v>670.2</v>
       </c>
       <c r="V7" s="6">
         <f>V6-V8</f>
@@ -1295,47 +1298,47 @@
       </c>
       <c r="AD7" s="6">
         <f>SUM(S7:V7)</f>
-        <v>2373.75</v>
+        <v>2439.4499999999998</v>
       </c>
       <c r="AE7" s="6">
         <f t="shared" ref="AE7:AN7" si="1">AE6-AE8</f>
-        <v>2168.2114999999994</v>
+        <v>2374.9537499999997</v>
       </c>
       <c r="AF7" s="6">
         <f t="shared" si="1"/>
-        <v>2364.1844624999994</v>
+        <v>2685.5246249999996</v>
       </c>
       <c r="AG7" s="6">
         <f t="shared" si="1"/>
-        <v>2634.3769724999997</v>
+        <v>3107.5356374999997</v>
       </c>
       <c r="AH7" s="6">
         <f t="shared" si="1"/>
-        <v>3110.0283703124992</v>
+        <v>3815.363199375</v>
       </c>
       <c r="AI7" s="6">
         <f t="shared" si="1"/>
-        <v>3644.2214786249988</v>
+        <v>4656.9874345312501</v>
       </c>
       <c r="AJ7" s="6">
         <f t="shared" si="1"/>
-        <v>4140.3624751124989</v>
+        <v>5521.0549826249999</v>
       </c>
       <c r="AK7" s="6">
         <f t="shared" si="1"/>
-        <v>4703.3507872771852</v>
+        <v>6271.7838003843744</v>
       </c>
       <c r="AL7" s="6">
         <f t="shared" si="1"/>
-        <v>5342.0774374012472</v>
+        <v>7123.5075263624985</v>
       </c>
       <c r="AM7" s="6">
         <f t="shared" si="1"/>
-        <v>6143.389053011434</v>
+        <v>8192.0336553168709</v>
       </c>
       <c r="AN7" s="6">
         <f t="shared" si="1"/>
-        <v>7064.8974109631481</v>
+        <v>9420.8387036144013</v>
       </c>
     </row>
     <row r="8" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1343,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" ref="M8:T8" si="2">M6-M7</f>
+        <f t="shared" ref="M8:U8" si="2">M6-M7</f>
         <v>-331.9</v>
       </c>
       <c r="N8" s="9">
@@ -1375,8 +1378,8 @@
         <v>-272.39999999999998</v>
       </c>
       <c r="U8" s="9">
-        <f>U6*-0.95</f>
-        <v>-294.5</v>
+        <f t="shared" si="2"/>
+        <v>-333.6</v>
       </c>
       <c r="V8" s="9">
         <f>V6*-1</f>
@@ -1408,47 +1411,47 @@
       </c>
       <c r="AD8" s="9">
         <f>-AD6*0.6</f>
-        <v>-714.79499999999985</v>
+        <v>-730.755</v>
       </c>
       <c r="AE8" s="9">
         <f>-AE6*0.3</f>
-        <v>-500.35649999999987</v>
+        <v>-548.06624999999997</v>
       </c>
       <c r="AF8" s="9">
         <f>-AF6*0.05</f>
-        <v>-112.58021249999997</v>
+        <v>-127.88212499999997</v>
       </c>
       <c r="AG8" s="9">
         <f>AG6*0.1</f>
-        <v>292.70855249999994</v>
+        <v>345.28173749999996</v>
       </c>
       <c r="AH8" s="9">
         <f>AH6*0.15</f>
-        <v>548.82853593749985</v>
+        <v>673.29938812499995</v>
       </c>
       <c r="AI8" s="9">
         <f>AI6*0.17</f>
-        <v>746.4068088749998</v>
+        <v>953.84079984375001</v>
       </c>
       <c r="AJ8" s="9">
         <f>AJ6*0.18</f>
-        <v>908.86005551249968</v>
+        <v>1211.9388986249999</v>
       </c>
       <c r="AK8" s="9">
         <f>AK6*0.19</f>
-        <v>1103.2551229415619</v>
+        <v>1471.1591630531248</v>
       </c>
       <c r="AL8" s="9">
         <f>AL6*0.2</f>
-        <v>1335.5193593503118</v>
+        <v>1780.8768815906246</v>
       </c>
       <c r="AM8" s="9">
         <f t="shared" ref="AM8:AN8" si="4">AM6*0.2</f>
-        <v>1535.8472632528585</v>
+        <v>2048.0084138292182</v>
       </c>
       <c r="AN8" s="9">
         <f t="shared" si="4"/>
-        <v>1766.2243527407873</v>
+        <v>2355.2096759036008</v>
       </c>
     </row>
     <row r="9" spans="2:40" x14ac:dyDescent="0.3">
@@ -1480,12 +1483,11 @@
         <v>273.8</v>
       </c>
       <c r="U9" s="6">
-        <f>Q9*0.85</f>
-        <v>275.73999999999995</v>
+        <v>325.3</v>
       </c>
       <c r="V9" s="6">
-        <f>R9*1.01</f>
-        <v>283.10300000000001</v>
+        <f>R9*1.2</f>
+        <v>336.36</v>
       </c>
       <c r="X9" s="6">
         <v>220.2</v>
@@ -1507,47 +1509,47 @@
       </c>
       <c r="AD9" s="6">
         <f t="shared" ref="AD9:AD11" si="5">SUM(S9:V9)</f>
-        <v>1083.8430000000001</v>
+        <v>1186.6599999999999</v>
       </c>
       <c r="AE9" s="6">
         <f>AD9*1.02</f>
-        <v>1105.5198600000001</v>
+        <v>1210.3932</v>
       </c>
       <c r="AF9" s="6">
         <f>AE9*1.01</f>
-        <v>1116.5750586000001</v>
+        <v>1222.497132</v>
       </c>
       <c r="AG9" s="6">
         <f t="shared" ref="AG9:AN9" si="6">AF9*1.01</f>
-        <v>1127.7408091860002</v>
+        <v>1234.7221033200001</v>
       </c>
       <c r="AH9" s="6">
         <f t="shared" si="6"/>
-        <v>1139.0182172778602</v>
+        <v>1247.0693243532</v>
       </c>
       <c r="AI9" s="6">
         <f t="shared" si="6"/>
-        <v>1150.4083994506389</v>
+        <v>1259.540017596732</v>
       </c>
       <c r="AJ9" s="6">
         <f t="shared" si="6"/>
-        <v>1161.9124834451452</v>
+        <v>1272.1354177726994</v>
       </c>
       <c r="AK9" s="6">
         <f t="shared" si="6"/>
-        <v>1173.5316082795966</v>
+        <v>1284.8567719504265</v>
       </c>
       <c r="AL9" s="6">
         <f t="shared" si="6"/>
-        <v>1185.2669243623927</v>
+        <v>1297.7053396699307</v>
       </c>
       <c r="AM9" s="6">
         <f t="shared" si="6"/>
-        <v>1197.1195936060167</v>
+        <v>1310.6823930666301</v>
       </c>
       <c r="AN9" s="6">
         <f t="shared" si="6"/>
-        <v>1209.0907895420769</v>
+        <v>1323.7892169972963</v>
       </c>
     </row>
     <row r="10" spans="2:40" x14ac:dyDescent="0.3">
@@ -1579,12 +1581,11 @@
         <v>256.89999999999998</v>
       </c>
       <c r="U10" s="6">
-        <f>Q10*1.03</f>
-        <v>240.608</v>
+        <v>283.10000000000002</v>
       </c>
       <c r="V10" s="6">
-        <f>R10*1.06</f>
-        <v>258.53399999999999</v>
+        <f>R10*1.2</f>
+        <v>292.68</v>
       </c>
       <c r="X10" s="6">
         <v>38.4</v>
@@ -1606,47 +1607,47 @@
       </c>
       <c r="AD10" s="6">
         <f t="shared" si="5"/>
-        <v>968.24199999999996</v>
+        <v>1044.8800000000001</v>
       </c>
       <c r="AE10" s="6">
         <f t="shared" ref="AE10:AN10" si="7">AD10*1.01</f>
-        <v>977.92441999999994</v>
+        <v>1055.3288000000002</v>
       </c>
       <c r="AF10" s="6">
         <f t="shared" si="7"/>
-        <v>987.70366419999993</v>
+        <v>1065.8820880000003</v>
       </c>
       <c r="AG10" s="6">
         <f t="shared" si="7"/>
-        <v>997.58070084199994</v>
+        <v>1076.5409088800004</v>
       </c>
       <c r="AH10" s="6">
         <f t="shared" si="7"/>
-        <v>1007.55650785042</v>
+        <v>1087.3063179688004</v>
       </c>
       <c r="AI10" s="6">
         <f t="shared" si="7"/>
-        <v>1017.6320729289241</v>
+        <v>1098.1793811484883</v>
       </c>
       <c r="AJ10" s="6">
         <f t="shared" si="7"/>
-        <v>1027.8083936582134</v>
+        <v>1109.1611749599733</v>
       </c>
       <c r="AK10" s="6">
         <f t="shared" si="7"/>
-        <v>1038.0864775947955</v>
+        <v>1120.252786709573</v>
       </c>
       <c r="AL10" s="6">
         <f t="shared" si="7"/>
-        <v>1048.4673423707434</v>
+        <v>1131.4553145766688</v>
       </c>
       <c r="AM10" s="6">
         <f t="shared" si="7"/>
-        <v>1058.9520157944507</v>
+        <v>1142.7698677224355</v>
       </c>
       <c r="AN10" s="6">
         <f t="shared" si="7"/>
-        <v>1069.5415359523952</v>
+        <v>1154.1975663996598</v>
       </c>
     </row>
     <row r="11" spans="2:40" x14ac:dyDescent="0.3">
@@ -1774,11 +1775,11 @@
       </c>
       <c r="U12" s="6">
         <f t="shared" ref="U12:V12" si="9">SUM(U9:U11)</f>
-        <v>516.34799999999996</v>
+        <v>608.40000000000009</v>
       </c>
       <c r="V12" s="6">
         <f t="shared" si="9"/>
-        <v>541.63699999999994</v>
+        <v>629.04</v>
       </c>
       <c r="X12" s="6">
         <f t="shared" ref="X12:AD12" si="10">SUM(X9:X11)</f>
@@ -1806,47 +1807,47 @@
       </c>
       <c r="AD12" s="6">
         <f t="shared" si="10"/>
-        <v>2052.085</v>
+        <v>2231.54</v>
       </c>
       <c r="AE12" s="6">
         <f t="shared" ref="AE12:AN12" si="11">SUM(AE9:AE11)</f>
-        <v>2083.4442800000002</v>
+        <v>2265.7220000000002</v>
       </c>
       <c r="AF12" s="6">
         <f t="shared" si="11"/>
-        <v>2104.2787228000002</v>
+        <v>2288.3792200000003</v>
       </c>
       <c r="AG12" s="6">
         <f t="shared" si="11"/>
-        <v>2125.3215100280004</v>
+        <v>2311.2630122000005</v>
       </c>
       <c r="AH12" s="6">
         <f t="shared" si="11"/>
-        <v>2146.5747251282801</v>
+        <v>2334.3756423220002</v>
       </c>
       <c r="AI12" s="6">
         <f t="shared" si="11"/>
-        <v>2168.0404723795627</v>
+        <v>2357.7193987452201</v>
       </c>
       <c r="AJ12" s="6">
         <f t="shared" si="11"/>
-        <v>2189.7208771033584</v>
+        <v>2381.2965927326727</v>
       </c>
       <c r="AK12" s="6">
         <f t="shared" si="11"/>
-        <v>2211.6180858743919</v>
+        <v>2405.1095586599995</v>
       </c>
       <c r="AL12" s="6">
         <f t="shared" si="11"/>
-        <v>2233.7342667331359</v>
+        <v>2429.1606542465997</v>
       </c>
       <c r="AM12" s="6">
         <f t="shared" si="11"/>
-        <v>2256.0716094004674</v>
+        <v>2453.4522607890658</v>
       </c>
       <c r="AN12" s="6">
         <f t="shared" si="11"/>
-        <v>2278.6323254944718</v>
+        <v>2477.9867833969561</v>
       </c>
     </row>
     <row r="13" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1887,11 +1888,11 @@
       </c>
       <c r="U13" s="9">
         <f t="shared" ref="U13:V13" si="13">U8-U12</f>
-        <v>-810.84799999999996</v>
+        <v>-942.00000000000011</v>
       </c>
       <c r="V13" s="9">
         <f t="shared" si="13"/>
-        <v>-928.5619999999999</v>
+        <v>-1015.9649999999999</v>
       </c>
       <c r="X13" s="9">
         <f t="shared" ref="X13:AD13" si="14">X8-X12</f>
@@ -1919,47 +1920,47 @@
       </c>
       <c r="AD13" s="9">
         <f t="shared" si="14"/>
-        <v>-2766.88</v>
+        <v>-2962.2950000000001</v>
       </c>
       <c r="AE13" s="9">
         <f t="shared" ref="AE13:AN13" si="15">AE8-AE12</f>
-        <v>-2583.80078</v>
+        <v>-2813.7882500000001</v>
       </c>
       <c r="AF13" s="9">
         <f t="shared" si="15"/>
-        <v>-2216.8589353000002</v>
+        <v>-2416.2613450000003</v>
       </c>
       <c r="AG13" s="9">
         <f t="shared" si="15"/>
-        <v>-1832.6129575280004</v>
+        <v>-1965.9812747000005</v>
       </c>
       <c r="AH13" s="9">
         <f t="shared" si="15"/>
-        <v>-1597.7461891907801</v>
+        <v>-1661.0762541970003</v>
       </c>
       <c r="AI13" s="9">
         <f t="shared" si="15"/>
-        <v>-1421.6336635045629</v>
+        <v>-1403.87859890147</v>
       </c>
       <c r="AJ13" s="9">
         <f t="shared" si="15"/>
-        <v>-1280.8608215908587</v>
+        <v>-1169.3576941076728</v>
       </c>
       <c r="AK13" s="9">
         <f t="shared" si="15"/>
-        <v>-1108.36296293283</v>
+        <v>-933.95039560687474</v>
       </c>
       <c r="AL13" s="9">
         <f t="shared" si="15"/>
-        <v>-898.21490738282409</v>
+        <v>-648.2837726559751</v>
       </c>
       <c r="AM13" s="9">
         <f t="shared" si="15"/>
-        <v>-720.22434614760891</v>
+        <v>-405.44384695984763</v>
       </c>
       <c r="AN13" s="9">
         <f t="shared" si="15"/>
-        <v>-512.40797275368459</v>
+        <v>-122.77710749335529</v>
       </c>
     </row>
     <row r="14" spans="2:40" x14ac:dyDescent="0.3">
@@ -1991,7 +1992,7 @@
         <v>-261.2</v>
       </c>
       <c r="U14" s="6">
-        <v>-300</v>
+        <v>36.799999999999997</v>
       </c>
       <c r="V14" s="6">
         <v>-300</v>
@@ -2016,47 +2017,47 @@
       </c>
       <c r="AD14" s="6">
         <f>SUM(S14:V14)</f>
-        <v>-1185.5999999999999</v>
+        <v>-848.8</v>
       </c>
       <c r="AE14" s="6">
         <f t="shared" ref="AE14:AN14" si="16">AD14*1.05</f>
-        <v>-1244.8799999999999</v>
+        <v>-891.24</v>
       </c>
       <c r="AF14" s="6">
         <f t="shared" si="16"/>
-        <v>-1307.124</v>
+        <v>-935.80200000000002</v>
       </c>
       <c r="AG14" s="6">
         <f t="shared" si="16"/>
-        <v>-1372.4802000000002</v>
+        <v>-982.59210000000007</v>
       </c>
       <c r="AH14" s="6">
         <f t="shared" si="16"/>
-        <v>-1441.1042100000002</v>
+        <v>-1031.7217050000002</v>
       </c>
       <c r="AI14" s="6">
         <f t="shared" si="16"/>
-        <v>-1513.1594205000004</v>
+        <v>-1083.3077902500002</v>
       </c>
       <c r="AJ14" s="6">
         <f t="shared" si="16"/>
-        <v>-1588.8173915250004</v>
+        <v>-1137.4731797625002</v>
       </c>
       <c r="AK14" s="6">
         <f t="shared" si="16"/>
-        <v>-1668.2582611012506</v>
+        <v>-1194.3468387506252</v>
       </c>
       <c r="AL14" s="6">
         <f t="shared" si="16"/>
-        <v>-1751.6711741563131</v>
+        <v>-1254.0641806881565</v>
       </c>
       <c r="AM14" s="6">
         <f t="shared" si="16"/>
-        <v>-1839.2547328641288</v>
+        <v>-1316.7673897225643</v>
       </c>
       <c r="AN14" s="6">
         <f t="shared" si="16"/>
-        <v>-1931.2174695073352</v>
+        <v>-1382.6057592086927</v>
       </c>
     </row>
     <row r="15" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -2097,11 +2098,11 @@
       </c>
       <c r="U15" s="9">
         <f t="shared" ref="U15:V15" si="18">U13-U14</f>
-        <v>-510.84799999999996</v>
+        <v>-978.80000000000007</v>
       </c>
       <c r="V15" s="9">
         <f t="shared" si="18"/>
-        <v>-628.5619999999999</v>
+        <v>-715.96499999999992</v>
       </c>
       <c r="X15" s="9">
         <f t="shared" ref="X15:AD15" si="19">X13-X14</f>
@@ -2129,47 +2130,47 @@
       </c>
       <c r="AD15" s="9">
         <f t="shared" si="19"/>
-        <v>-1581.2800000000002</v>
+        <v>-2113.4949999999999</v>
       </c>
       <c r="AE15" s="9">
         <f t="shared" ref="AE15:AN15" si="20">AE13-AE14</f>
-        <v>-1338.9207800000001</v>
+        <v>-1922.5482500000001</v>
       </c>
       <c r="AF15" s="9">
         <f t="shared" si="20"/>
-        <v>-909.73493530000019</v>
+        <v>-1480.4593450000002</v>
       </c>
       <c r="AG15" s="9">
         <f t="shared" si="20"/>
-        <v>-460.13275752800018</v>
+        <v>-983.38917470000047</v>
       </c>
       <c r="AH15" s="9">
         <f t="shared" si="20"/>
-        <v>-156.64197919077992</v>
+        <v>-629.3545491970001</v>
       </c>
       <c r="AI15" s="9">
         <f t="shared" si="20"/>
-        <v>91.525756995437405</v>
+        <v>-320.57080865146986</v>
       </c>
       <c r="AJ15" s="9">
         <f t="shared" si="20"/>
-        <v>307.95656993414173</v>
+        <v>-31.884514345172647</v>
       </c>
       <c r="AK15" s="9">
         <f t="shared" si="20"/>
-        <v>559.8952981684206</v>
+        <v>260.3964431437505</v>
       </c>
       <c r="AL15" s="9">
         <f t="shared" si="20"/>
-        <v>853.45626677348901</v>
+        <v>605.78040803218141</v>
       </c>
       <c r="AM15" s="9">
         <f t="shared" si="20"/>
-        <v>1119.0303867165198</v>
+        <v>911.32354276271667</v>
       </c>
       <c r="AN15" s="9">
         <f t="shared" si="20"/>
-        <v>1418.8094967536506</v>
+        <v>1259.8286517153374</v>
       </c>
     </row>
     <row r="16" spans="2:40" x14ac:dyDescent="0.3">
@@ -2201,7 +2202,7 @@
         <v>-2.4</v>
       </c>
       <c r="U16" s="6">
-        <v>-2</v>
+        <v>-0.4</v>
       </c>
       <c r="V16" s="6">
         <v>-2</v>
@@ -2226,7 +2227,7 @@
       </c>
       <c r="AD16" s="6">
         <f>SUM(S16:V16)</f>
-        <v>-7.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AE16" s="6">
         <v>0</v>
@@ -2297,11 +2298,11 @@
       </c>
       <c r="U17" s="9">
         <f t="shared" ref="U17:V17" si="22">U15-U16</f>
-        <v>-508.84799999999996</v>
+        <v>-978.40000000000009</v>
       </c>
       <c r="V17" s="9">
         <f t="shared" si="22"/>
-        <v>-626.5619999999999</v>
+        <v>-713.96499999999992</v>
       </c>
       <c r="X17" s="9">
         <f t="shared" ref="X17:AD17" si="23">X15-X16</f>
@@ -2329,431 +2330,431 @@
       </c>
       <c r="AD17" s="9">
         <f t="shared" si="23"/>
-        <v>-1573.4800000000002</v>
+        <v>-2107.2950000000001</v>
       </c>
       <c r="AE17" s="9">
         <f t="shared" ref="AE17:AN17" si="24">AE15-AE16</f>
-        <v>-1338.9207800000001</v>
+        <v>-1922.5482500000001</v>
       </c>
       <c r="AF17" s="9">
         <f t="shared" si="24"/>
-        <v>-909.73493530000019</v>
+        <v>-1480.4593450000002</v>
       </c>
       <c r="AG17" s="9">
         <f t="shared" si="24"/>
-        <v>-460.13275752800018</v>
+        <v>-983.38917470000047</v>
       </c>
       <c r="AH17" s="9">
         <f t="shared" si="24"/>
-        <v>-156.64197919077992</v>
+        <v>-629.3545491970001</v>
       </c>
       <c r="AI17" s="9">
         <f t="shared" si="24"/>
-        <v>91.525756995437405</v>
+        <v>-320.57080865146986</v>
       </c>
       <c r="AJ17" s="9">
         <f t="shared" si="24"/>
-        <v>307.95656993414173</v>
+        <v>-31.884514345172647</v>
       </c>
       <c r="AK17" s="9">
         <f t="shared" si="24"/>
-        <v>559.8952981684206</v>
+        <v>260.3964431437505</v>
       </c>
       <c r="AL17" s="9">
         <f t="shared" si="24"/>
-        <v>853.45626677348901</v>
+        <v>605.78040803218141</v>
       </c>
       <c r="AM17" s="9">
         <f t="shared" si="24"/>
-        <v>1119.0303867165198</v>
+        <v>911.32354276271667</v>
       </c>
       <c r="AN17" s="9">
         <f t="shared" si="24"/>
-        <v>1418.8094967536506</v>
+        <v>1259.8286517153374</v>
       </c>
       <c r="AO17" s="2">
         <f>AN17*(1+$AQ$27)</f>
-        <v>1404.6214017861141</v>
+        <v>1247.230365198184</v>
       </c>
       <c r="AP17" s="2">
         <f t="shared" ref="AP17:DA17" si="25">AO17*(1+$AQ$27)</f>
-        <v>1390.575187768253</v>
+        <v>1234.7580615462023</v>
       </c>
       <c r="AQ17" s="2">
         <f t="shared" si="25"/>
-        <v>1376.6694358905704</v>
+        <v>1222.4104809307403</v>
       </c>
       <c r="AR17" s="2">
         <f t="shared" si="25"/>
-        <v>1362.9027415316648</v>
+        <v>1210.1863761214329</v>
       </c>
       <c r="AS17" s="2">
         <f t="shared" si="25"/>
-        <v>1349.2737141163482</v>
+        <v>1198.0845123602185</v>
       </c>
       <c r="AT17" s="2">
         <f t="shared" si="25"/>
-        <v>1335.7809769751848</v>
+        <v>1186.1036672366163</v>
       </c>
       <c r="AU17" s="2">
         <f t="shared" si="25"/>
-        <v>1322.4231672054329</v>
+        <v>1174.24263056425</v>
       </c>
       <c r="AV17" s="2">
         <f t="shared" si="25"/>
-        <v>1309.1989355333785</v>
+        <v>1162.5002042586075</v>
       </c>
       <c r="AW17" s="2">
         <f t="shared" si="25"/>
-        <v>1296.1069461780446</v>
+        <v>1150.8752022160213</v>
       </c>
       <c r="AX17" s="2">
         <f t="shared" si="25"/>
-        <v>1283.1458767162642</v>
+        <v>1139.3664501938611</v>
       </c>
       <c r="AY17" s="2">
         <f t="shared" si="25"/>
-        <v>1270.3144179491014</v>
+        <v>1127.9727856919224</v>
       </c>
       <c r="AZ17" s="2">
         <f t="shared" si="25"/>
-        <v>1257.6112737696103</v>
+        <v>1116.6930578350032</v>
       </c>
       <c r="BA17" s="2">
         <f t="shared" si="25"/>
-        <v>1245.0351610319142</v>
+        <v>1105.5261272566531</v>
       </c>
       <c r="BB17" s="2">
         <f t="shared" si="25"/>
-        <v>1232.5848094215951</v>
+        <v>1094.4708659840867</v>
       </c>
       <c r="BC17" s="2">
         <f t="shared" si="25"/>
-        <v>1220.2589613273792</v>
+        <v>1083.5261573242458</v>
       </c>
       <c r="BD17" s="2">
         <f t="shared" si="25"/>
-        <v>1208.0563717141054</v>
+        <v>1072.6908957510034</v>
       </c>
       <c r="BE17" s="2">
         <f t="shared" si="25"/>
-        <v>1195.9758079969642</v>
+        <v>1061.9639867934934</v>
       </c>
       <c r="BF17" s="2">
         <f t="shared" si="25"/>
-        <v>1184.0160499169947</v>
+        <v>1051.3443469255585</v>
       </c>
       <c r="BG17" s="2">
         <f t="shared" si="25"/>
-        <v>1172.1758894178247</v>
+        <v>1040.8309034563028</v>
       </c>
       <c r="BH17" s="2">
         <f t="shared" si="25"/>
-        <v>1160.4541305236464</v>
+        <v>1030.4225944217399</v>
       </c>
       <c r="BI17" s="2">
         <f t="shared" si="25"/>
-        <v>1148.8495892184098</v>
+        <v>1020.1183684775225</v>
       </c>
       <c r="BJ17" s="2">
         <f t="shared" si="25"/>
-        <v>1137.3610933262257</v>
+        <v>1009.9171847927472</v>
       </c>
       <c r="BK17" s="2">
         <f t="shared" si="25"/>
-        <v>1125.9874823929636</v>
+        <v>999.81801294481977</v>
       </c>
       <c r="BL17" s="2">
         <f t="shared" si="25"/>
-        <v>1114.7276075690338</v>
+        <v>989.81983281537157</v>
       </c>
       <c r="BM17" s="2">
         <f t="shared" si="25"/>
-        <v>1103.5803314933435</v>
+        <v>979.92163448721783</v>
       </c>
       <c r="BN17" s="2">
         <f t="shared" si="25"/>
-        <v>1092.54452817841</v>
+        <v>970.12241814234562</v>
       </c>
       <c r="BO17" s="2">
         <f t="shared" si="25"/>
-        <v>1081.619082896626</v>
+        <v>960.42119396092221</v>
       </c>
       <c r="BP17" s="2">
         <f t="shared" si="25"/>
-        <v>1070.8028920676597</v>
+        <v>950.81698202131292</v>
       </c>
       <c r="BQ17" s="2">
         <f t="shared" si="25"/>
-        <v>1060.0948631469832</v>
+        <v>941.30881220109984</v>
       </c>
       <c r="BR17" s="2">
         <f t="shared" si="25"/>
-        <v>1049.4939145155133</v>
+        <v>931.89572407908884</v>
       </c>
       <c r="BS17" s="2">
         <f t="shared" si="25"/>
-        <v>1038.9989753703583</v>
+        <v>922.57676683829789</v>
       </c>
       <c r="BT17" s="2">
         <f t="shared" si="25"/>
-        <v>1028.6089856166548</v>
+        <v>913.35099916991487</v>
       </c>
       <c r="BU17" s="2">
         <f t="shared" si="25"/>
-        <v>1018.3228957604882</v>
+        <v>904.21748917821571</v>
       </c>
       <c r="BV17" s="2">
         <f t="shared" si="25"/>
-        <v>1008.1396668028833</v>
+        <v>895.1753142864336</v>
       </c>
       <c r="BW17" s="2">
         <f t="shared" si="25"/>
-        <v>998.05827013485452</v>
+        <v>886.22356114356921</v>
       </c>
       <c r="BX17" s="2">
         <f t="shared" si="25"/>
-        <v>988.07768743350596</v>
+        <v>877.36132553213349</v>
       </c>
       <c r="BY17" s="2">
         <f t="shared" si="25"/>
-        <v>978.19691055917087</v>
+        <v>868.58771227681211</v>
       </c>
       <c r="BZ17" s="2">
         <f t="shared" si="25"/>
-        <v>968.4149414535791</v>
+        <v>859.90183515404397</v>
       </c>
       <c r="CA17" s="2">
         <f t="shared" si="25"/>
-        <v>958.73079203904331</v>
+        <v>851.30281680250357</v>
       </c>
       <c r="CB17" s="2">
         <f t="shared" si="25"/>
-        <v>949.14348411865285</v>
+        <v>842.78978863447855</v>
       </c>
       <c r="CC17" s="2">
         <f t="shared" si="25"/>
-        <v>939.65204927746629</v>
+        <v>834.36189074813376</v>
       </c>
       <c r="CD17" s="2">
         <f t="shared" si="25"/>
-        <v>930.25552878469159</v>
+        <v>826.01827184065246</v>
       </c>
       <c r="CE17" s="2">
         <f t="shared" si="25"/>
-        <v>920.95297349684472</v>
+        <v>817.75808912224591</v>
       </c>
       <c r="CF17" s="2">
         <f t="shared" si="25"/>
-        <v>911.74344376187628</v>
+        <v>809.58050823102349</v>
       </c>
       <c r="CG17" s="2">
         <f t="shared" si="25"/>
-        <v>902.62600932425755</v>
+        <v>801.48470314871327</v>
       </c>
       <c r="CH17" s="2">
         <f t="shared" si="25"/>
-        <v>893.59974923101493</v>
+        <v>793.46985611722607</v>
       </c>
       <c r="CI17" s="2">
         <f t="shared" si="25"/>
-        <v>884.66375173870472</v>
+        <v>785.53515755605383</v>
       </c>
       <c r="CJ17" s="2">
         <f t="shared" si="25"/>
-        <v>875.81711422131764</v>
+        <v>777.67980598049326</v>
       </c>
       <c r="CK17" s="2">
         <f t="shared" si="25"/>
-        <v>867.05894307910444</v>
+        <v>769.90300792068831</v>
       </c>
       <c r="CL17" s="2">
         <f t="shared" si="25"/>
-        <v>858.38835364831334</v>
+        <v>762.20397784148145</v>
       </c>
       <c r="CM17" s="2">
         <f t="shared" si="25"/>
-        <v>849.80447011183026</v>
+        <v>754.58193806306667</v>
       </c>
       <c r="CN17" s="2">
         <f t="shared" si="25"/>
-        <v>841.306425410712</v>
+        <v>747.03611868243604</v>
       </c>
       <c r="CO17" s="2">
         <f t="shared" si="25"/>
-        <v>832.8933611566049</v>
+        <v>739.56575749561171</v>
       </c>
       <c r="CP17" s="2">
         <f t="shared" si="25"/>
-        <v>824.56442754503882</v>
+        <v>732.17009992065562</v>
       </c>
       <c r="CQ17" s="2">
         <f t="shared" si="25"/>
-        <v>816.31878326958838</v>
+        <v>724.84839892144907</v>
       </c>
       <c r="CR17" s="2">
         <f t="shared" si="25"/>
-        <v>808.15559543689244</v>
+        <v>717.59991493223458</v>
       </c>
       <c r="CS17" s="2">
         <f t="shared" si="25"/>
-        <v>800.07403948252352</v>
+        <v>710.42391578291222</v>
       </c>
       <c r="CT17" s="2">
         <f t="shared" si="25"/>
-        <v>792.07329908769827</v>
+        <v>703.31967662508305</v>
       </c>
       <c r="CU17" s="2">
         <f t="shared" si="25"/>
-        <v>784.15256609682126</v>
+        <v>696.28647985883219</v>
       </c>
       <c r="CV17" s="2">
         <f t="shared" si="25"/>
-        <v>776.31104043585299</v>
+        <v>689.32361506024381</v>
       </c>
       <c r="CW17" s="2">
         <f t="shared" si="25"/>
-        <v>768.5479300314945</v>
+        <v>682.43037890964138</v>
       </c>
       <c r="CX17" s="2">
         <f t="shared" si="25"/>
-        <v>760.86245073117959</v>
+        <v>675.60607512054492</v>
       </c>
       <c r="CY17" s="2">
         <f t="shared" si="25"/>
-        <v>753.2538262238678</v>
+        <v>668.85001436933942</v>
       </c>
       <c r="CZ17" s="2">
         <f t="shared" si="25"/>
-        <v>745.72128796162917</v>
+        <v>662.16151422564599</v>
       </c>
       <c r="DA17" s="2">
         <f t="shared" si="25"/>
-        <v>738.26407508201282</v>
+        <v>655.53989908338951</v>
       </c>
       <c r="DB17" s="2">
         <f t="shared" ref="DB17:EF17" si="26">DA17*(1+$AQ$27)</f>
-        <v>730.88143433119274</v>
+        <v>648.98450009255566</v>
       </c>
       <c r="DC17" s="2">
         <f t="shared" si="26"/>
-        <v>723.57261998788078</v>
+        <v>642.49465509163008</v>
       </c>
       <c r="DD17" s="2">
         <f t="shared" si="26"/>
-        <v>716.33689378800193</v>
+        <v>636.0697085407138</v>
       </c>
       <c r="DE17" s="2">
         <f t="shared" si="26"/>
-        <v>709.17352485012191</v>
+        <v>629.70901145530661</v>
       </c>
       <c r="DF17" s="2">
         <f t="shared" si="26"/>
-        <v>702.0817896016207</v>
+        <v>623.41192134075357</v>
       </c>
       <c r="DG17" s="2">
         <f t="shared" si="26"/>
-        <v>695.06097170560452</v>
+        <v>617.17780212734601</v>
       </c>
       <c r="DH17" s="2">
         <f t="shared" si="26"/>
-        <v>688.11036198854845</v>
+        <v>611.00602410607257</v>
       </c>
       <c r="DI17" s="2">
         <f t="shared" si="26"/>
-        <v>681.22925836866295</v>
+        <v>604.89596386501182</v>
       </c>
       <c r="DJ17" s="2">
         <f t="shared" si="26"/>
-        <v>674.41696578497636</v>
+        <v>598.84700422636172</v>
       </c>
       <c r="DK17" s="2">
         <f t="shared" si="26"/>
-        <v>667.67279612712662</v>
+        <v>592.85853418409806</v>
       </c>
       <c r="DL17" s="2">
         <f t="shared" si="26"/>
-        <v>660.99606816585538</v>
+        <v>586.92994884225709</v>
       </c>
       <c r="DM17" s="2">
         <f t="shared" si="26"/>
-        <v>654.38610748419683</v>
+        <v>581.06064935383449</v>
       </c>
       <c r="DN17" s="2">
         <f t="shared" si="26"/>
-        <v>647.84224640935486</v>
+        <v>575.25004286029616</v>
       </c>
       <c r="DO17" s="2">
         <f t="shared" si="26"/>
-        <v>641.36382394526129</v>
+        <v>569.4975424316932</v>
       </c>
       <c r="DP17" s="2">
         <f t="shared" si="26"/>
-        <v>634.95018570580862</v>
+        <v>563.8025670073763</v>
       </c>
       <c r="DQ17" s="2">
         <f t="shared" si="26"/>
-        <v>628.60068384875058</v>
+        <v>558.16454133730258</v>
       </c>
       <c r="DR17" s="2">
         <f t="shared" si="26"/>
-        <v>622.31467701026304</v>
+        <v>552.58289592392953</v>
       </c>
       <c r="DS17" s="2">
         <f t="shared" si="26"/>
-        <v>616.09153024016041</v>
+        <v>547.05706696469019</v>
       </c>
       <c r="DT17" s="2">
         <f t="shared" si="26"/>
-        <v>609.93061493775883</v>
+        <v>541.58649629504328</v>
       </c>
       <c r="DU17" s="2">
         <f t="shared" si="26"/>
-        <v>603.83130878838119</v>
+        <v>536.17063133209285</v>
       </c>
       <c r="DV17" s="2">
         <f t="shared" si="26"/>
-        <v>597.79299570049739</v>
+        <v>530.8089250187719</v>
       </c>
       <c r="DW17" s="2">
         <f t="shared" si="26"/>
-        <v>591.81506574349237</v>
+        <v>525.50083576858412</v>
       </c>
       <c r="DX17" s="2">
         <f t="shared" si="26"/>
-        <v>585.89691508605745</v>
+        <v>520.2458274108983</v>
       </c>
       <c r="DY17" s="2">
         <f t="shared" si="26"/>
-        <v>580.03794593519683</v>
+        <v>515.04336913678935</v>
       </c>
       <c r="DZ17" s="2">
         <f t="shared" si="26"/>
-        <v>574.2375664758448</v>
+        <v>509.89293544542147</v>
       </c>
       <c r="EA17" s="2">
         <f t="shared" si="26"/>
-        <v>568.49519081108633</v>
+        <v>504.79400609096723</v>
       </c>
       <c r="EB17" s="2">
         <f t="shared" si="26"/>
-        <v>562.81023890297547</v>
+        <v>499.74606603005753</v>
       </c>
       <c r="EC17" s="2">
         <f t="shared" si="26"/>
-        <v>557.18213651394569</v>
+        <v>494.74860536975694</v>
       </c>
       <c r="ED17" s="2">
         <f t="shared" si="26"/>
-        <v>551.61031514880619</v>
+        <v>489.80111931605938</v>
       </c>
       <c r="EE17" s="2">
         <f t="shared" si="26"/>
-        <v>546.0942119973181</v>
+        <v>484.9031081228988</v>
       </c>
       <c r="EF17" s="2">
         <f t="shared" si="26"/>
-        <v>540.6332698773449</v>
+        <v>480.05407704166981</v>
       </c>
     </row>
     <row r="18" spans="2:136" x14ac:dyDescent="0.3">
@@ -2793,80 +2794,80 @@
         <v>3050.3</v>
       </c>
       <c r="U18" s="6">
-        <f t="shared" ref="U18:V18" si="27">3050.3</f>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="V18" s="6">
+        <f>324.2</f>
+        <v>324.2</v>
+      </c>
+      <c r="X18" s="6">
+        <f t="shared" ref="X18:AC18" si="27">3031.5</f>
+        <v>3031.5</v>
+      </c>
+      <c r="Y18" s="6">
         <f t="shared" si="27"/>
-        <v>3050.3</v>
-      </c>
-      <c r="X18" s="6">
-        <f t="shared" ref="X18:AC18" si="28">3031.5</f>
         <v>3031.5</v>
       </c>
-      <c r="Y18" s="6">
-        <f t="shared" si="28"/>
+      <c r="Z18" s="6">
+        <f t="shared" si="27"/>
         <v>3031.5</v>
       </c>
-      <c r="Z18" s="6">
-        <f t="shared" si="28"/>
+      <c r="AA18" s="6">
+        <f t="shared" si="27"/>
         <v>3031.5</v>
       </c>
-      <c r="AA18" s="6">
-        <f t="shared" si="28"/>
+      <c r="AB18" s="6">
+        <f t="shared" si="27"/>
         <v>3031.5</v>
       </c>
-      <c r="AB18" s="6">
-        <f t="shared" si="28"/>
+      <c r="AC18" s="6">
+        <f t="shared" si="27"/>
         <v>3031.5</v>
       </c>
-      <c r="AC18" s="6">
-        <f t="shared" si="28"/>
-        <v>3031.5</v>
-      </c>
       <c r="AD18" s="6">
-        <f t="shared" ref="AD18:AN18" si="29">3050.3</f>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AE18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AF18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AG18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AH18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AI18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AJ18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AK18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AL18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AM18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
       <c r="AN18" s="6">
-        <f t="shared" si="29"/>
-        <v>3050.3</v>
+        <f>324.2</f>
+        <v>324.2</v>
       </c>
     </row>
     <row r="19" spans="2:136" x14ac:dyDescent="0.3">
@@ -2874,112 +2875,112 @@
         <v>24</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" ref="M19:T19" si="30">M17/M18</f>
+        <f t="shared" ref="M19:T19" si="28">M17/M18</f>
         <v>-0.20811479465611082</v>
       </c>
       <c r="N19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.21563582384957938</v>
+      </c>
+      <c r="O19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.22460827972950687</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.2108972887912664</v>
+      </c>
+      <c r="Q19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.32742866567705758</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.13102424542305793</v>
+      </c>
+      <c r="S19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.12005376520342262</v>
+      </c>
+      <c r="T19" s="8">
+        <f t="shared" si="28"/>
+        <v>-0.17686784906402653</v>
+      </c>
+      <c r="U19" s="8">
+        <f t="shared" ref="U19:V19" si="29">U17/U18</f>
+        <v>-3.0178901912399758</v>
+      </c>
+      <c r="V19" s="8">
+        <f t="shared" si="29"/>
+        <v>-2.2022362739049965</v>
+      </c>
+      <c r="X19" s="8">
+        <f t="shared" ref="X19:AD19" si="30">X17/X18</f>
+        <v>-9.1472868217054248E-2</v>
+      </c>
+      <c r="Y19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.21563582384957938</v>
-      </c>
-      <c r="O19" s="8">
+        <v>-0.23727527626587497</v>
+      </c>
+      <c r="Z19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.22460827972950687</v>
-      </c>
-      <c r="P19" s="8">
+        <v>-0.85096486887679379</v>
+      </c>
+      <c r="AA19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.2108972887912664</v>
-      </c>
-      <c r="Q19" s="8">
+        <v>-0.43031502556490187</v>
+      </c>
+      <c r="AB19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.32742866567705758</v>
-      </c>
-      <c r="R19" s="8">
+        <v>-0.93297047666171873</v>
+      </c>
+      <c r="AC19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.13102424542305793</v>
-      </c>
-      <c r="S19" s="8">
+        <v>-0.89526636978393548</v>
+      </c>
+      <c r="AD19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.12005376520342262</v>
-      </c>
-      <c r="T19" s="8">
-        <f t="shared" si="30"/>
-        <v>-0.17686784906402653</v>
-      </c>
-      <c r="U19" s="8">
-        <f t="shared" ref="U19:V19" si="31">U17/U18</f>
-        <v>-0.16681900140969738</v>
-      </c>
-      <c r="V19" s="8">
+        <v>-6.4999845774213449</v>
+      </c>
+      <c r="AE19" s="8">
+        <f t="shared" ref="AE19:AN19" si="31">AE17/AE18</f>
+        <v>-5.9301303207896368</v>
+      </c>
+      <c r="AF19" s="8">
         <f t="shared" si="31"/>
-        <v>-0.20540995967609738</v>
-      </c>
-      <c r="X19" s="8">
-        <f t="shared" ref="X19:AD19" si="32">X17/X18</f>
-        <v>-9.1472868217054248E-2</v>
-      </c>
-      <c r="Y19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.23727527626587497</v>
-      </c>
-      <c r="Z19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.85096486887679379</v>
-      </c>
-      <c r="AA19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.43031502556490187</v>
-      </c>
-      <c r="AB19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.93297047666171873</v>
-      </c>
-      <c r="AC19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.89526636978393548</v>
-      </c>
-      <c r="AD19" s="8">
-        <f t="shared" si="32"/>
-        <v>-0.51584434317935945</v>
-      </c>
-      <c r="AE19" s="8">
-        <f t="shared" ref="AE19:AN19" si="33">AE17/AE18</f>
-        <v>-0.43894724453332462</v>
-      </c>
-      <c r="AF19" s="8">
-        <f t="shared" si="33"/>
-        <v>-0.29824441376258076</v>
+        <v>-4.5665001388032085</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="33"/>
-        <v>-0.15084836164573981</v>
+        <f t="shared" si="31"/>
+        <v>-3.0332793790869848</v>
       </c>
       <c r="AH19" s="8">
-        <f t="shared" si="33"/>
-        <v>-5.1352974851909622E-2</v>
+        <f t="shared" si="31"/>
+        <v>-1.9412540073935847</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="33"/>
-        <v>3.0005493556514901E-2</v>
+        <f t="shared" si="31"/>
+        <v>-0.98880570219454</v>
       </c>
       <c r="AJ19" s="8">
-        <f t="shared" si="33"/>
-        <v>0.10095943675511973</v>
+        <f t="shared" si="31"/>
+        <v>-9.8348286073944011E-2</v>
       </c>
       <c r="AK19" s="8">
-        <f t="shared" si="33"/>
-        <v>0.18355417439872163</v>
+        <f t="shared" si="31"/>
+        <v>0.80319692518121688</v>
       </c>
       <c r="AL19" s="8">
-        <f t="shared" si="33"/>
-        <v>0.27979420606939936</v>
+        <f t="shared" si="31"/>
+        <v>1.868539198125174</v>
       </c>
       <c r="AM19" s="8">
-        <f t="shared" si="33"/>
-        <v>0.36685912425548955</v>
+        <f t="shared" si="31"/>
+        <v>2.8109918037097987</v>
       </c>
       <c r="AN19" s="8">
-        <f t="shared" si="33"/>
-        <v>0.46513769031034669</v>
+        <f t="shared" si="31"/>
+        <v>3.8859612946185611</v>
       </c>
     </row>
     <row r="21" spans="2:136" x14ac:dyDescent="0.3">
@@ -2988,39 +2989,39 @@
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10">
-        <f t="shared" ref="R21" si="34">R3/N3-1</f>
+        <f t="shared" ref="R21" si="32">R3/N3-1</f>
         <v>0.78719723183390999</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" ref="S21" si="35">S3/O3-1</f>
+        <f t="shared" ref="S21" si="33">S3/O3-1</f>
         <v>0.58057956278596845</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" ref="T21" si="36">T3/P3-1</f>
+        <f t="shared" ref="T21" si="34">T3/P3-1</f>
         <v>0.3822055137844611</v>
       </c>
-      <c r="U21" s="10">
-        <f t="shared" ref="U21" si="37">U3/Q3-1</f>
+      <c r="U21" s="15">
+        <f t="shared" ref="U21" si="35">U3/Q3-1</f>
         <v>0.5</v>
       </c>
-      <c r="V21" s="10">
-        <f t="shared" ref="V21" si="38">V3/R3-1</f>
+      <c r="V21" s="15">
+        <f t="shared" ref="V21" si="36">V3/R3-1</f>
         <v>0.7</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" ref="AA21:AA22" si="39">AA3/Z3-1</f>
+        <f t="shared" ref="AA21:AA22" si="37">AA3/Z3-1</f>
         <v>13.563333333333333</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" ref="AB21:AB22" si="40">AB3/AA3-1</f>
+        <f t="shared" ref="AB21:AB22" si="38">AB3/AA3-1</f>
         <v>0.37354085603112841</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" ref="AC21" si="41">AC3/AB3-1</f>
+        <f t="shared" ref="AC21" si="39">AC3/AB3-1</f>
         <v>0.70654890851524743</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" ref="AD21" si="42">AD3/AC3-1</f>
+        <f t="shared" ref="AD21" si="40">AD3/AC3-1</f>
         <v>0.54846206425153787</v>
       </c>
     </row>
@@ -3031,43 +3032,43 @@
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10">
-        <f t="shared" ref="Q22" si="43">Q4/M4-1</f>
+        <f t="shared" ref="Q22" si="41">Q4/M4-1</f>
         <v>0.1645161290322581</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" ref="R22" si="44">R4/N4-1</f>
+        <f t="shared" ref="R22" si="42">R4/N4-1</f>
         <v>0.95271049596309121</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" ref="S22" si="45">S4/O4-1</f>
+        <f t="shared" ref="S22" si="43">S4/O4-1</f>
         <v>0.28009259259259256</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22" si="46">T4/P4-1</f>
+        <f t="shared" ref="T22" si="44">T4/P4-1</f>
         <v>0.83080568720379144</v>
       </c>
-      <c r="U22" s="10">
-        <f t="shared" ref="U22" si="47">U4/Q4-1</f>
+      <c r="U22" s="15">
+        <f t="shared" ref="U22" si="45">U4/Q4-1</f>
         <v>1.5</v>
       </c>
-      <c r="V22" s="10">
-        <f t="shared" ref="V22" si="48">V4/R4-1</f>
+      <c r="V22" s="15">
+        <f t="shared" ref="V22" si="46">V4/R4-1</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="37"/>
         <v>16.95</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="38"/>
         <v>0.17381615598885802</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AD22" si="49">AC4/AB4-1</f>
+        <f t="shared" ref="AC22:AD22" si="47">AC4/AB4-1</f>
         <v>7.130991931656383E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="47"/>
         <v>0.99764093476575488</v>
       </c>
     </row>
@@ -3080,51 +3081,51 @@
         <v>1</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" ref="O23:V23" si="50">O3/O4</f>
+        <f t="shared" ref="O23:V23" si="48">O3/O4</f>
         <v>1.1383101851851851</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>1.1345971563981043</v>
       </c>
       <c r="Q23" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>1.5407202216066482</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0.91523922031896043</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>1.4055153707052441</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="48"/>
         <v>0.85658814392958837</v>
       </c>
-      <c r="U23" s="10">
-        <f t="shared" si="50"/>
+      <c r="U23" s="15">
+        <f t="shared" si="48"/>
         <v>0.92443213296398896</v>
       </c>
-      <c r="V23" s="10">
-        <f t="shared" si="50"/>
+      <c r="V23" s="15">
+        <f t="shared" si="48"/>
         <v>0.70723030661010577</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" ref="AA23:AD23" si="51">AA3/AA4</f>
+        <f t="shared" ref="AA23:AD23" si="49">AA3/AA4</f>
         <v>0.60849582172701955</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0.71203132415756998</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>1.134234134455643</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0.87919630531083837</v>
       </c>
     </row>
@@ -3137,52 +3138,52 @@
         <v>90657.43944636677</v>
       </c>
       <c r="O24" s="6">
-        <f t="shared" ref="O24:V24" si="52">(O6/O3)*1000000</f>
+        <f t="shared" ref="O24:V24" si="50">(O6/O3)*1000000</f>
         <v>87798.67819013726</v>
       </c>
       <c r="P24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>83792.815371762743</v>
       </c>
       <c r="Q24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>71916.5767709457</v>
       </c>
       <c r="R24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>75669.570829299773</v>
       </c>
       <c r="S24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>75587.005467996147</v>
       </c>
       <c r="T24" s="6">
-        <f t="shared" si="52"/>
+        <f t="shared" si="50"/>
         <v>78392.263523723159</v>
       </c>
-      <c r="U24" s="6">
-        <f t="shared" si="52"/>
-        <v>74313.795996643894</v>
-      </c>
-      <c r="V24" s="6">
-        <f t="shared" si="52"/>
+      <c r="U24" s="14">
+        <f t="shared" si="50"/>
+        <v>80690.399137001092</v>
+      </c>
+      <c r="V24" s="14">
+        <f t="shared" si="50"/>
         <v>73443.995216673298</v>
       </c>
       <c r="AA24" s="6">
-        <f t="shared" ref="AA24:AD24" si="53">(AA6/AA3)*1000000</f>
+        <f t="shared" ref="AA24:AD24" si="51">(AA6/AA3)*1000000</f>
         <v>139208.05676356147</v>
       </c>
       <c r="AB24" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>99200.133311114812</v>
       </c>
       <c r="AC24" s="6">
-        <f t="shared" si="53"/>
+        <f t="shared" si="51"/>
         <v>78879.015721120973</v>
       </c>
       <c r="AD24" s="6">
-        <f t="shared" si="53"/>
-        <v>75125.49029499678</v>
+        <f t="shared" si="51"/>
+        <v>76802.898258270376</v>
       </c>
     </row>
     <row r="26" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -3191,92 +3192,92 @@
       </c>
       <c r="M26" s="11"/>
       <c r="Q26" s="11">
-        <f t="shared" ref="Q26:V26" si="54">Q6/M6-1</f>
+        <f t="shared" ref="Q26:V26" si="52">Q6/M6-1</f>
         <v>0.45137880986937584</v>
       </c>
       <c r="R26" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0.49173027989821905</v>
       </c>
       <c r="S26" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0.36074116965836711</v>
       </c>
       <c r="T26" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0.29312063808574274</v>
       </c>
       <c r="U26" s="11">
-        <f t="shared" si="54"/>
-        <v>0.55000000000000004</v>
+        <f t="shared" si="52"/>
+        <v>0.68300000000000005</v>
       </c>
       <c r="V26" s="11">
-        <f t="shared" si="54"/>
+        <f t="shared" si="52"/>
         <v>0.64999999999999991</v>
       </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11">
-        <f t="shared" ref="Y26:AA26" si="55">Y6/X6-1</f>
+        <f t="shared" ref="Y26:AA26" si="53">Y6/X6-1</f>
         <v>-0.13043478260869557</v>
       </c>
       <c r="Z26" s="11">
+        <f t="shared" si="53"/>
+        <v>5.7750000000000004</v>
+      </c>
+      <c r="AA26" s="11">
+        <f t="shared" si="53"/>
+        <v>21.44280442804428</v>
+      </c>
+      <c r="AB26" s="11">
+        <f t="shared" ref="AB26" si="54">AB6/AA6-1</f>
+        <v>-2.1210128247287185E-2</v>
+      </c>
+      <c r="AC26" s="11">
+        <f t="shared" ref="AC26:AN26" si="55">AC6/AB6-1</f>
+        <v>0.35696287586091047</v>
+      </c>
+      <c r="AD26" s="11">
         <f t="shared" si="55"/>
-        <v>5.7750000000000004</v>
-      </c>
-      <c r="AA26" s="11">
+        <v>0.5077061153750928</v>
+      </c>
+      <c r="AE26" s="11">
         <f t="shared" si="55"/>
-        <v>21.44280442804428</v>
-      </c>
-      <c r="AB26" s="11">
-        <f t="shared" ref="AB26" si="56">AB6/AA6-1</f>
-        <v>-2.1210128247287185E-2</v>
-      </c>
-      <c r="AC26" s="11">
-        <f t="shared" ref="AC26:AN26" si="57">AC6/AB6-1</f>
-        <v>0.35696287586091047</v>
-      </c>
-      <c r="AD26" s="11">
-        <f t="shared" si="57"/>
-        <v>0.47477717256746699</v>
-      </c>
-      <c r="AE26" s="11">
-        <f t="shared" si="57"/>
+        <v>0.5</v>
+      </c>
+      <c r="AF26" s="11">
+        <f t="shared" si="55"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="AF26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AG26" s="11">
+        <f t="shared" si="55"/>
         <v>0.35000000000000009</v>
       </c>
-      <c r="AG26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AH26" s="11">
+        <f t="shared" si="55"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AH26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AI26" s="11">
+        <f t="shared" si="55"/>
         <v>0.25</v>
       </c>
-      <c r="AI26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AJ26" s="11">
+        <f t="shared" si="55"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AJ26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AK26" s="11">
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AK26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AL26" s="11">
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AL26" s="11">
-        <f t="shared" si="57"/>
+      <c r="AM26" s="11">
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AM26" s="11">
-        <f t="shared" si="57"/>
-        <v>0.14999999999999991</v>
-      </c>
       <c r="AN26" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
@@ -3293,7 +3294,7 @@
         <v>-1.608142493638677</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" ref="O27" si="58">O8/O6</f>
+        <f t="shared" ref="O27" si="56">O8/O6</f>
         <v>-1.3439490445859874</v>
       </c>
       <c r="P27" s="10">
@@ -3313,35 +3314,35 @@
         <v>-0.9727659574468086</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" ref="T27:V27" si="59">T8/T6</f>
+        <f t="shared" ref="T27:V27" si="57">T8/T6</f>
         <v>-1.0501156515034695</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="59"/>
-        <v>-0.95</v>
+        <f t="shared" si="57"/>
+        <v>-0.9910873440285205</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="57"/>
         <v>-1</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" ref="X27:AA27" si="60">X8/X6</f>
+        <f t="shared" ref="X27:AA27" si="58">X8/X6</f>
         <v>0.15217391304347822</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>0.22499999999999998</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-4.7158671586715872</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="58"/>
         <v>-1.7065110161131203</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" ref="AB27" si="61">AB8/AB6</f>
+        <f t="shared" ref="AB27" si="59">AB8/AB6</f>
         <v>-2.2523097597849824</v>
       </c>
       <c r="AC27" s="10">
@@ -3349,47 +3350,47 @@
         <v>-1.1427333498390693</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" ref="AD27:AN27" si="62">AD8/AD6</f>
+        <f t="shared" ref="AD27:AN27" si="60">AD8/AD6</f>
         <v>-0.6</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>-0.3</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>-0.05</v>
       </c>
       <c r="AG27" s="10">
-        <f t="shared" si="62"/>
-        <v>9.9999999999999992E-2</v>
+        <f t="shared" si="60"/>
+        <v>0.1</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.15</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.17</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.18</v>
       </c>
       <c r="AK27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.18999999999999997</v>
       </c>
       <c r="AL27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.2</v>
       </c>
       <c r="AM27" s="10">
-        <f t="shared" si="62"/>
-        <v>0.2</v>
+        <f t="shared" si="60"/>
+        <v>0.20000000000000004</v>
       </c>
       <c r="AN27" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>0.2</v>
       </c>
       <c r="AP27" s="1" t="s">
@@ -3408,44 +3409,44 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10">
-        <f t="shared" ref="Q28:S29" si="63">Q9/M9-1</f>
+        <f t="shared" ref="Q28:S29" si="61">Q9/M9-1</f>
         <v>0.40554592720970528</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.15349794238683123</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-0.11735769501054127</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" ref="T28:V28" si="64">T9/P9-1</f>
+        <f t="shared" ref="T28:V28" si="62">T9/P9-1</f>
         <v>-4.6657381615598847E-2</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="64"/>
-        <v>-0.15000000000000013</v>
+        <f t="shared" si="62"/>
+        <v>2.7743526510481953E-3</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="64"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="62"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="X28" s="10"/>
       <c r="Y28" s="10">
-        <f t="shared" ref="Y28:AA28" si="65">Y9/X9-1</f>
+        <f t="shared" ref="Y28:AA28" si="63">Y9/X9-1</f>
         <v>1.3210717529518621</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>0.46781451770690663</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="63"/>
         <v>9.5041322314049603E-2</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" ref="AB28" si="66">AB9/AA9-1</f>
+        <f t="shared" ref="AB28" si="64">AB9/AA9-1</f>
         <v>0.1405964698721851</v>
       </c>
       <c r="AC28" s="10">
@@ -3453,47 +3454,47 @@
         <v>0.25560298826040562</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" ref="AD28:AN28" si="67">AD9/AC9-1</f>
-        <v>-7.875648108797273E-2</v>
+        <f t="shared" ref="AD28:AN28" si="65">AD9/AC9-1</f>
+        <v>8.6357841053972262E-3</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN28" s="10">
-        <f t="shared" si="67"/>
+        <f t="shared" si="65"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP28" s="1" t="s">
@@ -3512,44 +3513,44 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>0.23141802846599901</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>1.2033195020746845E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="61"/>
         <v>-4.6904315196998336E-3</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" ref="T29:V29" si="68">T10/P10-1</f>
+        <f t="shared" ref="T29:V29" si="66">T10/P10-1</f>
         <v>0.22216936251189345</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="68"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.21190068493150704</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="68"/>
-        <v>5.9999999999999831E-2</v>
+        <f t="shared" si="66"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="X29" s="10"/>
       <c r="Y29" s="10">
-        <f t="shared" ref="Y29:AA29" si="69">Y10/X10-1</f>
+        <f t="shared" ref="Y29:AA29" si="67">Y10/X10-1</f>
         <v>1.3177083333333335</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>6.3314606741573032</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.12582375478927199</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" ref="AB29" si="70">AB10/AA10-1</f>
+        <f t="shared" ref="AB29" si="68">AB10/AA10-1</f>
         <v>8.5216444323441332E-2</v>
       </c>
       <c r="AC29" s="10">
@@ -3557,47 +3558,47 @@
         <v>0.13020572002007014</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" ref="AD29:AN29" si="71">AD10/AC10-1</f>
-        <v>7.4630410654827894E-2</v>
+        <f t="shared" ref="AD29:AN29" si="69">AD10/AC10-1</f>
+        <v>0.15968923418423975</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="69"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP29" s="1" t="s">
@@ -3605,7 +3606,7 @@
       </c>
       <c r="AQ29" s="6">
         <f>NPV(AQ28,AD17:EF17)</f>
-        <v>3661.5888406859026</v>
+        <v>106.79980947248835</v>
       </c>
     </row>
     <row r="30" spans="2:136" x14ac:dyDescent="0.3">
@@ -3617,115 +3618,115 @@
         <v>1.3766328011611029</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" ref="N30:P30" si="72">N10/N6</f>
+        <f t="shared" ref="N30:P30" si="70">N10/N6</f>
         <v>1.5330788804071247</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1.2345107122177186</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>1.0478564307078764</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" ref="Q30:AN30" si="73">Q10/Q6</f>
+        <f t="shared" ref="Q30:AN30" si="71">Q10/Q6</f>
         <v>1.1679999999999999</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>1.0400852878464819</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.90297872340425522</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.99036237471087119</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.77615483870967739</v>
+        <f t="shared" si="71"/>
+        <v>0.8410576351752822</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.66817600310137626</v>
+        <f t="shared" si="71"/>
+        <v>0.75642566388835053</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>8.3478260869565215</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>22.25</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>24.077490774907748</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>1.20782637290365</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>1.3391567277003193</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>1.1153750928447637</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.81274379367510974</v>
+        <f t="shared" si="71"/>
+        <v>0.85791818051193636</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.58633659400847205</v>
+        <f t="shared" si="71"/>
+        <v>0.57766490821137062</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.43866663699893094</v>
+        <f t="shared" si="71"/>
+        <v>0.41674396949534603</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.34081023336070787</v>
+        <f t="shared" si="71"/>
+        <v>0.31178622902985148</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.27537466855545201</v>
+        <f t="shared" si="71"/>
+        <v>0.24223391640011532</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.23177367936750543</v>
+        <f t="shared" si="71"/>
+        <v>0.19572500445129321</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.2035577531836352</v>
+        <f t="shared" si="71"/>
+        <v>0.16473521207983846</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.17877680931780138</v>
+        <f t="shared" si="71"/>
+        <v>0.14468049060924942</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.1570126760095473</v>
+        <f t="shared" si="71"/>
+        <v>0.12706721349160169</v>
       </c>
       <c r="AM30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.13789808936490675</v>
+        <f t="shared" si="71"/>
+        <v>0.11159816141436324</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="73"/>
-        <v>0.12111049587700506</v>
+        <f t="shared" si="71"/>
+        <v>9.8012298285658148E-2</v>
       </c>
       <c r="AP30" s="1" t="s">
         <v>53</v>
       </c>
       <c r="AQ30" s="6">
         <f>Main!D8</f>
-        <v>1563.6</v>
+        <v>952.79999999999973</v>
       </c>
     </row>
     <row r="31" spans="2:136" x14ac:dyDescent="0.3">
@@ -3741,7 +3742,7 @@
         <v>-4.6870229007633588</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" ref="O31" si="74">O13/O6</f>
+        <f t="shared" ref="O31" si="72">O13/O6</f>
         <v>-4.2264041690793288</v>
       </c>
       <c r="P31" s="10">
@@ -3761,35 +3762,35 @@
         <v>-2.9446808510638296</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" ref="T31:V31" si="75">T13/T6</f>
+        <f t="shared" ref="T31:V31" si="73">T13/T6</f>
         <v>-3.0959907478797226</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="75"/>
-        <v>-2.6156387096774192</v>
+        <f t="shared" si="73"/>
+        <v>-2.7985739750445635</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="75"/>
-        <v>-2.3998501001486074</v>
+        <f t="shared" si="73"/>
+        <v>-2.6257414227563483</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" ref="X31:AA31" si="76">X13/X6</f>
+        <f t="shared" ref="X31:AA31" si="74">X13/X6</f>
         <v>-56.065217391304344</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>-149.80000000000001</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>-56.476014760147599</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="76"/>
+        <f t="shared" si="74"/>
         <v>-4.2650443932916797</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="77">AB13/AB6</f>
+        <f t="shared" ref="AB31" si="75">AB13/AB6</f>
         <v>-5.2066185116747858</v>
       </c>
       <c r="AC31" s="10">
@@ -3797,55 +3798,55 @@
         <v>-3.7396632829908403</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" ref="AD31:AN31" si="78">AD13/AD6</f>
-        <v>-2.3225232409292178</v>
+        <f t="shared" ref="AD31:AN31" si="76">AD13/AD6</f>
+        <v>-2.4322474700823125</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" si="78"/>
-        <v>-1.5491759055793224</v>
+        <f t="shared" si="76"/>
+        <v>-1.5402088251192263</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.984568640470456</v>
+        <f t="shared" si="76"/>
+        <v>-0.94472208097887056</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.62608794375012344</v>
+        <f t="shared" si="76"/>
+        <v>-0.56938466799159937</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.4366790585500997</v>
+        <f t="shared" si="76"/>
+        <v>-0.37006039590116557</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.32378820761300059</v>
+        <f t="shared" si="76"/>
+        <v>-0.25020879988814176</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.25367486059924405</v>
+        <f t="shared" si="76"/>
+        <v>-0.17367573990585275</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.19087966017846655</v>
+        <f t="shared" si="76"/>
+        <v>-0.12061956287383591</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" si="78"/>
-        <v>-0.13451170154804457</v>
+        <f t="shared" si="76"/>
+        <v>-7.2805007393542884E-2</v>
       </c>
       <c r="AM31" s="10">
-        <f t="shared" si="78"/>
-        <v>-9.3788537881326128E-2</v>
+        <f t="shared" si="76"/>
+        <v>-3.9593963015198561E-2</v>
       </c>
       <c r="AN31" s="10">
-        <f t="shared" si="78"/>
-        <v>-5.8022976747947277E-2</v>
+        <f t="shared" si="76"/>
+        <v>-1.0426002300304799E-2</v>
       </c>
       <c r="AP31" s="1" t="s">
         <v>54</v>
       </c>
       <c r="AQ31" s="6">
         <f>AQ29+AQ30</f>
-        <v>5225.1888406859025</v>
+        <v>1059.599809472488</v>
       </c>
     </row>
     <row r="32" spans="2:136" x14ac:dyDescent="0.3">
@@ -3861,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" ref="O32" si="79">O16/O15</f>
+        <f t="shared" ref="O32" si="77">O16/O15</f>
         <v>-2.9381519024533566E-4</v>
       </c>
       <c r="P32" s="10">
@@ -3881,35 +3882,35 @@
         <v>3.8084874863982586E-3</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" ref="T32:V32" si="80">T16/T15</f>
+        <f t="shared" ref="T32:V32" si="78">T16/T15</f>
         <v>4.4288614135449336E-3</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="80"/>
-        <v>3.9150588824855932E-3</v>
+        <f t="shared" si="78"/>
+        <v>4.086636697997548E-4</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="80"/>
-        <v>3.1818659098068296E-3</v>
+        <f t="shared" si="78"/>
+        <v>2.7934326398636809E-3</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" ref="X32:AA32" si="81">X16/X15</f>
+        <f t="shared" ref="X32:AA32" si="79">X16/X15</f>
         <v>0</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>2.7797081306462821E-4</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>3.8762694782541279E-5</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-3.0672494440610386E-4</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" ref="AB32" si="82">AB16/AB15</f>
+        <f t="shared" ref="AB32" si="80">AB16/AB15</f>
         <v>-3.5369433735365894E-4</v>
       </c>
       <c r="AC32" s="10">
@@ -3917,47 +3918,47 @@
         <v>-4.4234739015039799E-4</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" ref="AD32:AN32" si="83">AD16/AD15</f>
-        <v>4.9327127390468477E-3</v>
+        <f t="shared" ref="AD32:AN32" si="81">AD16/AD15</f>
+        <v>2.9335295328354223E-3</v>
       </c>
       <c r="AE32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AF32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AG32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AH32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AL32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AM32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="AP32" s="1" t="s">
@@ -3965,7 +3966,7 @@
       </c>
       <c r="AQ32" s="5">
         <f>AQ31/AN18</f>
-        <v>1.7130081764698233</v>
+        <v>3.268352280914522</v>
       </c>
     </row>
     <row r="33" spans="2:43" x14ac:dyDescent="0.3">
@@ -3981,7 +3982,7 @@
         <v>-4.1583969465648858</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" ref="O33" si="84">O17/O6</f>
+        <f t="shared" ref="O33" si="82">O17/O6</f>
         <v>-3.9426751592356695</v>
       </c>
       <c r="P33" s="10">
@@ -4001,35 +4002,35 @@
         <v>-1.5582978723404257</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:V33" si="85">T17/T6</f>
+        <f t="shared" ref="T33:V33" si="83">T17/T6</f>
         <v>-2.0797995373939866</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="85"/>
-        <v>-1.6414451612903225</v>
+        <f t="shared" si="83"/>
+        <v>-2.9067142008318481</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="85"/>
-        <v>-1.6193370808296181</v>
+        <f t="shared" si="83"/>
+        <v>-1.8452284034373587</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" ref="X33:AA33" si="86">X17/X6</f>
+        <f t="shared" ref="X33:AA33" si="84">X17/X6</f>
         <v>-60.282608695652172</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-179.82499999999999</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-95.191881918819192</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-2.1448536665570535</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="87">AB17/AB6</f>
+        <f t="shared" ref="AB33" si="85">AB17/AB6</f>
         <v>-4.7510498908113563</v>
       </c>
       <c r="AC33" s="10">
@@ -4037,55 +4038,55 @@
         <v>-3.3597425105224072</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33:AN33" si="88">AD17/AD6</f>
-        <v>-1.320781482802762</v>
+        <f t="shared" ref="AD33:AN33" si="86">AD17/AD6</f>
+        <v>-1.7302337992897758</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" si="88"/>
-        <v>-0.80278008579882576</v>
+        <f t="shared" si="86"/>
+        <v>-1.052362693378766</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" si="88"/>
-        <v>-0.40403855841895858</v>
+        <f t="shared" si="86"/>
+        <v>-0.57883748217352526</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" si="88"/>
-        <v>-0.15719826209314477</v>
+        <f t="shared" si="86"/>
+        <v>-0.28480775780966422</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" si="88"/>
-        <v>-4.2811725958237574E-2</v>
+        <f t="shared" si="86"/>
+        <v>-0.1402098146003718</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" si="88"/>
-        <v>2.0845708404878815E-2</v>
+        <f t="shared" si="86"/>
+        <v>-5.7134311595474961E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="88"/>
-        <v>6.0990888808385026E-2</v>
+        <f t="shared" si="86"/>
+        <v>-4.7355626497692874E-3</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="88"/>
-        <v>9.6423850150238299E-2</v>
+        <f t="shared" si="86"/>
+        <v>3.3630164186066382E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" si="88"/>
-        <v>0.12780889483903382</v>
+        <f t="shared" si="86"/>
+        <v>6.80316999220201E-2</v>
       </c>
       <c r="AM33" s="10">
-        <f t="shared" si="88"/>
-        <v>0.14572157186339763</v>
+        <f t="shared" si="86"/>
+        <v>8.8996074099011127E-2</v>
       </c>
       <c r="AN33" s="10">
-        <f t="shared" si="88"/>
-        <v>0.1606601669320179</v>
+        <f t="shared" si="86"/>
+        <v>0.10698229245614756</v>
       </c>
       <c r="AP33" s="1" t="s">
         <v>56</v>
       </c>
       <c r="AQ33" s="5">
         <f>Main!D3</f>
-        <v>1.98</v>
+        <v>12.84</v>
       </c>
     </row>
     <row r="34" spans="2:43" x14ac:dyDescent="0.3">
@@ -4094,7 +4095,7 @@
       </c>
       <c r="AQ34" s="11">
         <f>AQ32/AQ33-1</f>
-        <v>-0.1348443553182711</v>
+        <v>-0.74545542983531754</v>
       </c>
     </row>
     <row r="35" spans="2:43" x14ac:dyDescent="0.3">

--- a/Financial Analysis/LCID.xlsx
+++ b/Financial Analysis/LCID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE5F2BF2-0D17-49A6-AC41-7CB2A6FB7952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9D14FBA-226B-4829-B0A2-8BB15ABA0865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{1AB2C153-F3A3-43B3-970A-67C6BEA1AC7C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>LCID</t>
   </si>
@@ -226,7 +226,19 @@
     <t>ASP</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -363,13 +375,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -387,8 +399,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18531840" y="15240"/>
-          <a:ext cx="0" cy="6126480"/>
+          <a:off x="21583650" y="15240"/>
+          <a:ext cx="0" cy="7692390"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -413,14 +425,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:to>
@@ -437,7 +449,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13655040" y="0"/>
+          <a:off x="14249400" y="0"/>
           <a:ext cx="0" cy="7665720"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -791,14 +803,14 @@
         <v>12.84</v>
       </c>
       <c r="E3" s="4">
-        <v>46002</v>
+        <v>46078</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>46002</v>
+        <v>46078</v>
       </c>
       <c r="G3" s="4">
-        <v>46084</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -806,11 +818,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -819,7 +831,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>4162.7280000000001</v>
+        <v>4173</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -827,11 +839,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>1635.1+701.9+656.2</f>
-        <v>2993.2</v>
+        <f>997.8+631.1+512.2</f>
+        <v>2141.1000000000004</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -839,11 +851,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>2040.4</f>
-        <v>2040.4</v>
+        <f>671.7+2046.6</f>
+        <v>2718.3</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -852,7 +864,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>952.79999999999973</v>
+        <v>-577.19999999999982</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -861,7 +873,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>3209.9280000000003</v>
+        <v>4750.2</v>
       </c>
     </row>
   </sheetData>
@@ -871,20 +883,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C59EB153-B42C-4EA2-9808-5A7F3690FC48}">
-  <dimension ref="B2:EF35"/>
+  <dimension ref="B2:EJ35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="17" width="8.88671875" style="1"/>
     <col min="18" max="18" width="8.88671875" style="1" customWidth="1"/>
-    <col min="19" max="41" width="8.88671875" style="1"/>
-    <col min="42" max="42" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.77734375" style="1" customWidth="1"/>
-    <col min="44" max="16384" width="8.88671875" style="1"/>
+    <col min="19" max="45" width="8.88671875" style="1"/>
+    <col min="46" max="46" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C2" s="7" t="s">
         <v>25</v>
       </c>
@@ -945,59 +957,71 @@
       <c r="V2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="X2" s="1">
+      <c r="W2" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB2" s="1">
         <v>2019</v>
       </c>
-      <c r="Y2" s="1">
+      <c r="AC2" s="1">
         <v>2020</v>
       </c>
-      <c r="Z2" s="1">
+      <c r="AD2" s="1">
         <v>2021</v>
       </c>
-      <c r="AA2" s="1">
+      <c r="AE2" s="1">
         <v>2022</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AF2" s="1">
         <v>2023</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AG2" s="1">
         <v>2024</v>
       </c>
-      <c r="AD2" s="1">
+      <c r="AH2" s="1">
         <v>2025</v>
       </c>
-      <c r="AE2" s="1">
+      <c r="AI2" s="1">
         <v>2026</v>
       </c>
-      <c r="AF2" s="1">
+      <c r="AJ2" s="1">
         <v>2027</v>
       </c>
-      <c r="AG2" s="1">
+      <c r="AK2" s="1">
         <v>2028</v>
       </c>
-      <c r="AH2" s="1">
+      <c r="AL2" s="1">
         <v>2029</v>
       </c>
-      <c r="AI2" s="1">
+      <c r="AM2" s="1">
         <v>2030</v>
       </c>
-      <c r="AJ2" s="1">
+      <c r="AN2" s="1">
         <v>2031</v>
       </c>
-      <c r="AK2" s="1">
+      <c r="AO2" s="1">
         <v>2032</v>
       </c>
-      <c r="AL2" s="1">
+      <c r="AP2" s="1">
         <v>2033</v>
       </c>
-      <c r="AM2" s="1">
+      <c r="AQ2" s="1">
         <v>2034</v>
       </c>
-      <c r="AN2" s="1">
+      <c r="AR2" s="1">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>62</v>
       </c>
@@ -1033,33 +1057,35 @@
       <c r="T3" s="12">
         <v>3309</v>
       </c>
-      <c r="U3" s="13">
-        <f>Q3*1.5</f>
-        <v>4171.5</v>
-      </c>
-      <c r="V3" s="13">
-        <f>R3*1.7</f>
-        <v>5268.3</v>
-      </c>
-      <c r="Z3" s="6">
+      <c r="U3" s="12">
+        <v>4078</v>
+      </c>
+      <c r="V3" s="12">
+        <v>5345</v>
+      </c>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AD3" s="6">
         <v>300</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AE3" s="6">
         <v>4369</v>
       </c>
-      <c r="AB3" s="6">
+      <c r="AF3" s="6">
         <v>6001</v>
       </c>
-      <c r="AC3" s="6">
+      <c r="AG3" s="6">
         <f>SUM(O3:R3)</f>
         <v>10241</v>
       </c>
-      <c r="AD3" s="14">
+      <c r="AH3" s="14">
         <f>SUM(S3:V3)</f>
-        <v>15857.8</v>
+        <v>15841</v>
       </c>
     </row>
-    <row r="4" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>60</v>
       </c>
@@ -1097,33 +1123,38 @@
       <c r="T4" s="12">
         <v>3863</v>
       </c>
-      <c r="U4" s="13">
-        <f>Q4*2.5</f>
-        <v>4512.5</v>
-      </c>
-      <c r="V4" s="13">
-        <f>R4*2.2</f>
-        <v>7449.2000000000007</v>
-      </c>
-      <c r="Z4" s="6">
+      <c r="U4" s="12">
+        <v>3891</v>
+      </c>
+      <c r="V4" s="12">
+        <v>7874</v>
+      </c>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AD4" s="6">
         <v>400</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AE4" s="6">
         <v>7180</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AF4" s="6">
         <v>8428</v>
       </c>
-      <c r="AC4" s="6">
+      <c r="AG4" s="6">
         <f>SUM(O4:R4)</f>
         <v>9029</v>
       </c>
-      <c r="AD4" s="14">
+      <c r="AH4" s="14">
         <f>SUM(S4:V4)</f>
-        <v>18036.7</v>
+        <v>17840</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>26000</v>
       </c>
     </row>
-    <row r="5" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:44" x14ac:dyDescent="0.3">
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1144,8 +1175,12 @@
       <c r="T5" s="7"/>
       <c r="U5" s="7"/>
       <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
     </row>
-    <row r="6" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1173,77 +1208,80 @@
       <c r="T6" s="9">
         <v>259.39999999999998</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6" s="9">
         <v>336.6</v>
       </c>
       <c r="V6" s="9">
-        <f>R6*1.65</f>
-        <v>386.92499999999995</v>
-      </c>
-      <c r="X6" s="9">
+        <v>522.70000000000005</v>
+      </c>
+      <c r="W6" s="9"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+      <c r="Z6" s="9"/>
+      <c r="AB6" s="9">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y6" s="9">
+      <c r="AC6" s="9">
         <v>4</v>
       </c>
-      <c r="Z6" s="9">
+      <c r="AD6" s="9">
         <v>27.1</v>
       </c>
-      <c r="AA6" s="9">
+      <c r="AE6" s="9">
         <v>608.20000000000005</v>
       </c>
-      <c r="AB6" s="9">
+      <c r="AF6" s="9">
         <v>595.29999999999995</v>
       </c>
-      <c r="AC6" s="9">
+      <c r="AG6" s="9">
         <v>807.8</v>
       </c>
-      <c r="AD6" s="9">
+      <c r="AH6" s="9">
         <f>SUM(S6:V6)</f>
-        <v>1217.925</v>
-      </c>
-      <c r="AE6" s="9">
-        <f>AD6*1.5</f>
-        <v>1826.8874999999998</v>
-      </c>
-      <c r="AF6" s="9">
-        <f>AE6*1.4</f>
-        <v>2557.6424999999995</v>
-      </c>
-      <c r="AG6" s="9">
-        <f>AF6*1.35</f>
-        <v>3452.8173749999996</v>
-      </c>
-      <c r="AH6" s="9">
-        <f>AG6*1.3</f>
-        <v>4488.6625875</v>
+        <v>1353.7</v>
       </c>
       <c r="AI6" s="9">
-        <f>AH6*1.25</f>
-        <v>5610.8282343749997</v>
+        <f>AH6*1.5</f>
+        <v>2030.5500000000002</v>
       </c>
       <c r="AJ6" s="9">
-        <f>AI6*1.2</f>
-        <v>6732.9938812499995</v>
+        <f>AI6*1.4</f>
+        <v>2842.77</v>
       </c>
       <c r="AK6" s="9">
-        <f t="shared" ref="AK6:AN6" si="0">AJ6*1.15</f>
-        <v>7742.9429634374992</v>
+        <f>AJ6*1.35</f>
+        <v>3837.7395000000001</v>
       </c>
       <c r="AL6" s="9">
+        <f>AK6*1.3</f>
+        <v>4989.0613499999999</v>
+      </c>
+      <c r="AM6" s="9">
+        <f>AL6*1.25</f>
+        <v>6236.3266874999999</v>
+      </c>
+      <c r="AN6" s="9">
+        <f>AM6*1.2</f>
+        <v>7483.5920249999999</v>
+      </c>
+      <c r="AO6" s="9">
+        <f t="shared" ref="AO6:AR6" si="0">AN6*1.15</f>
+        <v>8606.1308287499996</v>
+      </c>
+      <c r="AP6" s="9">
         <f t="shared" si="0"/>
-        <v>8904.3844079531227</v>
-      </c>
-      <c r="AM6" s="9">
+        <v>9897.0504530624985</v>
+      </c>
+      <c r="AQ6" s="9">
         <f t="shared" si="0"/>
-        <v>10240.042069146089</v>
-      </c>
-      <c r="AN6" s="9">
+        <v>11381.608021021872</v>
+      </c>
+      <c r="AR6" s="9">
         <f t="shared" si="0"/>
-        <v>11776.048379518003</v>
+        <v>13088.849224175152</v>
       </c>
     </row>
-    <row r="7" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1275,78 +1313,81 @@
         <v>670.2</v>
       </c>
       <c r="V7" s="6">
-        <f>V6-V8</f>
-        <v>773.84999999999991</v>
-      </c>
-      <c r="X7" s="6">
+        <v>944.6</v>
+      </c>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AB7" s="6">
         <v>3.9</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="AC7" s="6">
         <v>3.1</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="AD7" s="6">
         <v>154.9</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AE7" s="6">
         <v>1646.1</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AF7" s="6">
         <v>1936.1</v>
       </c>
-      <c r="AC7" s="6">
+      <c r="AG7" s="6">
         <v>1730.9</v>
       </c>
-      <c r="AD7" s="6">
+      <c r="AH7" s="6">
         <f>SUM(S7:V7)</f>
-        <v>2439.4499999999998</v>
-      </c>
-      <c r="AE7" s="6">
-        <f t="shared" ref="AE7:AN7" si="1">AE6-AE8</f>
-        <v>2374.9537499999997</v>
-      </c>
-      <c r="AF7" s="6">
-        <f t="shared" si="1"/>
-        <v>2685.5246249999996</v>
-      </c>
-      <c r="AG7" s="6">
-        <f t="shared" si="1"/>
-        <v>3107.5356374999997</v>
-      </c>
-      <c r="AH7" s="6">
-        <f t="shared" si="1"/>
-        <v>3815.363199375</v>
+        <v>2610.1999999999998</v>
       </c>
       <c r="AI7" s="6">
-        <f t="shared" si="1"/>
-        <v>4656.9874345312501</v>
+        <f t="shared" ref="AI7:AR7" si="1">AI6-AI8</f>
+        <v>3248.88</v>
       </c>
       <c r="AJ7" s="6">
         <f t="shared" si="1"/>
-        <v>5521.0549826249999</v>
+        <v>3695.6010000000001</v>
       </c>
       <c r="AK7" s="6">
         <f t="shared" si="1"/>
-        <v>6271.7838003843744</v>
+        <v>4029.626475</v>
       </c>
       <c r="AL7" s="6">
         <f t="shared" si="1"/>
-        <v>7123.5075263624985</v>
+        <v>4490.1552149999998</v>
       </c>
       <c r="AM7" s="6">
         <f t="shared" si="1"/>
-        <v>8192.0336553168709</v>
+        <v>5300.8776843750002</v>
       </c>
       <c r="AN7" s="6">
         <f t="shared" si="1"/>
-        <v>9420.8387036144013</v>
+        <v>5986.8736200000003</v>
+      </c>
+      <c r="AO7" s="6">
+        <f t="shared" si="1"/>
+        <v>6626.7207381374992</v>
+      </c>
+      <c r="AP7" s="6">
+        <f t="shared" si="1"/>
+        <v>7521.7583443274989</v>
+      </c>
+      <c r="AQ7" s="6">
+        <f t="shared" si="1"/>
+        <v>8536.2060157664037</v>
+      </c>
+      <c r="AR7" s="6">
+        <f t="shared" si="1"/>
+        <v>9816.6369181313639</v>
       </c>
     </row>
-    <row r="8" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="M8" s="9">
-        <f t="shared" ref="M8:U8" si="2">M6-M7</f>
+        <f t="shared" ref="M8:V8" si="2">M6-M7</f>
         <v>-331.9</v>
       </c>
       <c r="N8" s="9">
@@ -1382,79 +1423,83 @@
         <v>-333.6</v>
       </c>
       <c r="V8" s="9">
-        <f>V6*-1</f>
-        <v>-386.92499999999995</v>
-      </c>
-      <c r="X8" s="9">
-        <f t="shared" ref="X8:AC8" si="3">X6-X7</f>
+        <f t="shared" si="2"/>
+        <v>-421.9</v>
+      </c>
+      <c r="W8" s="9"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
+      <c r="Z8" s="9"/>
+      <c r="AB8" s="9">
+        <f t="shared" ref="AB8:AH8" si="3">AB6-AB7</f>
         <v>0.69999999999999973</v>
       </c>
-      <c r="Y8" s="9">
+      <c r="AC8" s="9">
         <f t="shared" si="3"/>
         <v>0.89999999999999991</v>
       </c>
-      <c r="Z8" s="9">
+      <c r="AD8" s="9">
         <f t="shared" si="3"/>
         <v>-127.80000000000001</v>
       </c>
-      <c r="AA8" s="9">
+      <c r="AE8" s="9">
         <f t="shared" si="3"/>
         <v>-1037.8999999999999</v>
       </c>
-      <c r="AB8" s="9">
+      <c r="AF8" s="9">
         <f t="shared" si="3"/>
         <v>-1340.8</v>
       </c>
-      <c r="AC8" s="9">
+      <c r="AG8" s="9">
         <f t="shared" si="3"/>
         <v>-923.10000000000014</v>
       </c>
-      <c r="AD8" s="9">
-        <f>-AD6*0.6</f>
-        <v>-730.755</v>
-      </c>
-      <c r="AE8" s="9">
-        <f>-AE6*0.3</f>
-        <v>-548.06624999999997</v>
-      </c>
-      <c r="AF8" s="9">
-        <f>-AF6*0.05</f>
-        <v>-127.88212499999997</v>
-      </c>
-      <c r="AG8" s="9">
-        <f>AG6*0.1</f>
-        <v>345.28173749999996</v>
-      </c>
       <c r="AH8" s="9">
-        <f>AH6*0.15</f>
-        <v>673.29938812499995</v>
+        <f t="shared" si="3"/>
+        <v>-1256.4999999999998</v>
       </c>
       <c r="AI8" s="9">
-        <f>AI6*0.17</f>
-        <v>953.84079984375001</v>
+        <f>-AI6*0.6</f>
+        <v>-1218.3300000000002</v>
       </c>
       <c r="AJ8" s="9">
-        <f>AJ6*0.18</f>
-        <v>1211.9388986249999</v>
+        <f>-AJ6*0.3</f>
+        <v>-852.83100000000002</v>
       </c>
       <c r="AK8" s="9">
-        <f>AK6*0.19</f>
-        <v>1471.1591630531248</v>
+        <f>-AK6*0.05</f>
+        <v>-191.88697500000001</v>
       </c>
       <c r="AL8" s="9">
-        <f>AL6*0.2</f>
-        <v>1780.8768815906246</v>
+        <f>AL6*0.1</f>
+        <v>498.90613500000001</v>
       </c>
       <c r="AM8" s="9">
-        <f t="shared" ref="AM8:AN8" si="4">AM6*0.2</f>
-        <v>2048.0084138292182</v>
+        <f>AM6*0.15</f>
+        <v>935.44900312499999</v>
       </c>
       <c r="AN8" s="9">
-        <f t="shared" si="4"/>
-        <v>2355.2096759036008</v>
+        <f>AN6*0.2</f>
+        <v>1496.7184050000001</v>
+      </c>
+      <c r="AO8" s="9">
+        <f>AO6*0.23</f>
+        <v>1979.4100906125</v>
+      </c>
+      <c r="AP8" s="9">
+        <f>AP6*0.24</f>
+        <v>2375.2921087349996</v>
+      </c>
+      <c r="AQ8" s="9">
+        <f>AQ6*0.25</f>
+        <v>2845.4020052554679</v>
+      </c>
+      <c r="AR8" s="9">
+        <f>AR6*0.25</f>
+        <v>3272.212306043788</v>
       </c>
     </row>
-    <row r="9" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1486,73 +1531,76 @@
         <v>325.3</v>
       </c>
       <c r="V9" s="6">
-        <f>R9*1.2</f>
-        <v>336.36</v>
-      </c>
-      <c r="X9" s="6">
+        <v>361</v>
+      </c>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AB9" s="6">
         <v>220.2</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="AC9" s="6">
         <v>511.1</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AD9" s="6">
         <v>750.2</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AE9" s="6">
         <v>821.5</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AF9" s="6">
         <v>937</v>
       </c>
-      <c r="AC9" s="6">
+      <c r="AG9" s="6">
         <v>1176.5</v>
       </c>
-      <c r="AD9" s="6">
-        <f t="shared" ref="AD9:AD11" si="5">SUM(S9:V9)</f>
-        <v>1186.6599999999999</v>
-      </c>
-      <c r="AE9" s="6">
-        <f>AD9*1.02</f>
-        <v>1210.3932</v>
-      </c>
-      <c r="AF9" s="6">
-        <f>AE9*1.01</f>
-        <v>1222.497132</v>
-      </c>
-      <c r="AG9" s="6">
-        <f t="shared" ref="AG9:AN9" si="6">AF9*1.01</f>
-        <v>1234.7221033200001</v>
-      </c>
       <c r="AH9" s="6">
-        <f t="shared" si="6"/>
-        <v>1247.0693243532</v>
+        <f t="shared" ref="AH9:AH11" si="4">SUM(S9:V9)</f>
+        <v>1211.3</v>
       </c>
       <c r="AI9" s="6">
-        <f t="shared" si="6"/>
-        <v>1259.540017596732</v>
+        <f>AH9*1.02</f>
+        <v>1235.5260000000001</v>
       </c>
       <c r="AJ9" s="6">
-        <f t="shared" si="6"/>
-        <v>1272.1354177726994</v>
+        <f>AI9*1.01</f>
+        <v>1247.8812600000001</v>
       </c>
       <c r="AK9" s="6">
-        <f t="shared" si="6"/>
-        <v>1284.8567719504265</v>
+        <f t="shared" ref="AK9:AR9" si="5">AJ9*1.01</f>
+        <v>1260.3600726000002</v>
       </c>
       <c r="AL9" s="6">
-        <f t="shared" si="6"/>
-        <v>1297.7053396699307</v>
+        <f t="shared" si="5"/>
+        <v>1272.9636733260002</v>
       </c>
       <c r="AM9" s="6">
-        <f t="shared" si="6"/>
-        <v>1310.6823930666301</v>
+        <f t="shared" si="5"/>
+        <v>1285.6933100592603</v>
       </c>
       <c r="AN9" s="6">
-        <f t="shared" si="6"/>
-        <v>1323.7892169972963</v>
+        <f t="shared" si="5"/>
+        <v>1298.5502431598529</v>
+      </c>
+      <c r="AO9" s="6">
+        <f t="shared" si="5"/>
+        <v>1311.5357455914514</v>
+      </c>
+      <c r="AP9" s="6">
+        <f t="shared" si="5"/>
+        <v>1324.651103047366</v>
+      </c>
+      <c r="AQ9" s="6">
+        <f t="shared" si="5"/>
+        <v>1337.8976140778395</v>
+      </c>
+      <c r="AR9" s="6">
+        <f t="shared" si="5"/>
+        <v>1351.2765902186179</v>
       </c>
     </row>
-    <row r="10" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1584,73 +1632,76 @@
         <v>283.10000000000002</v>
       </c>
       <c r="V10" s="6">
-        <f>R10*1.2</f>
-        <v>292.68</v>
-      </c>
-      <c r="X10" s="6">
+        <v>281.8</v>
+      </c>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AB10" s="6">
         <v>38.4</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="AC10" s="6">
         <v>89</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="AD10" s="6">
         <v>652.5</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AE10" s="6">
         <v>734.6</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AF10" s="6">
         <v>797.2</v>
       </c>
-      <c r="AC10" s="6">
+      <c r="AG10" s="6">
         <v>901</v>
       </c>
-      <c r="AD10" s="6">
-        <f t="shared" si="5"/>
-        <v>1044.8800000000001</v>
-      </c>
-      <c r="AE10" s="6">
-        <f t="shared" ref="AE10:AN10" si="7">AD10*1.01</f>
-        <v>1055.3288000000002</v>
-      </c>
-      <c r="AF10" s="6">
-        <f t="shared" si="7"/>
-        <v>1065.8820880000003</v>
-      </c>
-      <c r="AG10" s="6">
-        <f t="shared" si="7"/>
-        <v>1076.5409088800004</v>
-      </c>
       <c r="AH10" s="6">
-        <f t="shared" si="7"/>
-        <v>1087.3063179688004</v>
+        <f t="shared" si="4"/>
+        <v>1034</v>
       </c>
       <c r="AI10" s="6">
-        <f t="shared" si="7"/>
-        <v>1098.1793811484883</v>
+        <f t="shared" ref="AI10:AR10" si="6">AH10*1.01</f>
+        <v>1044.3399999999999</v>
       </c>
       <c r="AJ10" s="6">
-        <f t="shared" si="7"/>
-        <v>1109.1611749599733</v>
+        <f t="shared" si="6"/>
+        <v>1054.7834</v>
       </c>
       <c r="AK10" s="6">
-        <f t="shared" si="7"/>
-        <v>1120.252786709573</v>
+        <f t="shared" si="6"/>
+        <v>1065.331234</v>
       </c>
       <c r="AL10" s="6">
-        <f t="shared" si="7"/>
-        <v>1131.4553145766688</v>
+        <f t="shared" si="6"/>
+        <v>1075.98454634</v>
       </c>
       <c r="AM10" s="6">
-        <f t="shared" si="7"/>
-        <v>1142.7698677224355</v>
+        <f t="shared" si="6"/>
+        <v>1086.7443918034</v>
       </c>
       <c r="AN10" s="6">
-        <f t="shared" si="7"/>
-        <v>1154.1975663996598</v>
+        <f t="shared" si="6"/>
+        <v>1097.6118357214341</v>
+      </c>
+      <c r="AO10" s="6">
+        <f t="shared" si="6"/>
+        <v>1108.5879540786484</v>
+      </c>
+      <c r="AP10" s="6">
+        <f t="shared" si="6"/>
+        <v>1119.6738336194348</v>
+      </c>
+      <c r="AQ10" s="6">
+        <f t="shared" si="6"/>
+        <v>1130.8705719556292</v>
+      </c>
+      <c r="AR10" s="6">
+        <f t="shared" si="6"/>
+        <v>1142.1792776751854</v>
       </c>
     </row>
-    <row r="11" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
@@ -1684,38 +1735,30 @@
       <c r="V11" s="6">
         <v>0</v>
       </c>
-      <c r="X11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="6">
-        <v>0</v>
-      </c>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
       <c r="AB11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6">
         <v>24.5</v>
       </c>
-      <c r="AC11" s="6">
+      <c r="AG11" s="6">
         <v>20.3</v>
       </c>
-      <c r="AD11" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AE11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="6">
-        <v>0</v>
-      </c>
       <c r="AH11" s="6">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AI11" s="6">
@@ -1736,234 +1779,254 @@
       <c r="AN11" s="6">
         <v>0</v>
       </c>
+      <c r="AO11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="12" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="M12" s="6">
-        <f t="shared" ref="M12:T12" si="8">SUM(M9:M11)</f>
+        <f t="shared" ref="M12:T12" si="7">SUM(M9:M11)</f>
         <v>421</v>
       </c>
       <c r="N12" s="6">
+        <f t="shared" si="7"/>
+        <v>484</v>
+      </c>
+      <c r="O12" s="6">
+        <f t="shared" si="7"/>
+        <v>497.8</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" si="7"/>
+        <v>517.6</v>
+      </c>
+      <c r="Q12" s="6">
+        <f t="shared" si="7"/>
+        <v>558.1</v>
+      </c>
+      <c r="R12" s="6">
+        <f t="shared" si="7"/>
+        <v>524.20000000000005</v>
+      </c>
+      <c r="S12" s="6">
+        <f t="shared" si="7"/>
+        <v>463.4</v>
+      </c>
+      <c r="T12" s="6">
+        <f t="shared" si="7"/>
+        <v>530.70000000000005</v>
+      </c>
+      <c r="U12" s="6">
+        <f t="shared" ref="U12:V12" si="8">SUM(U9:U11)</f>
+        <v>608.40000000000009</v>
+      </c>
+      <c r="V12" s="6">
         <f t="shared" si="8"/>
-        <v>484</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" si="8"/>
-        <v>497.8</v>
-      </c>
-      <c r="P12" s="6">
-        <f t="shared" si="8"/>
-        <v>517.6</v>
-      </c>
-      <c r="Q12" s="6">
-        <f t="shared" si="8"/>
-        <v>558.1</v>
-      </c>
-      <c r="R12" s="6">
-        <f t="shared" si="8"/>
-        <v>524.20000000000005</v>
-      </c>
-      <c r="S12" s="6">
-        <f t="shared" si="8"/>
-        <v>463.4</v>
-      </c>
-      <c r="T12" s="6">
-        <f t="shared" si="8"/>
-        <v>530.70000000000005</v>
-      </c>
-      <c r="U12" s="6">
-        <f t="shared" ref="U12:V12" si="9">SUM(U9:U11)</f>
-        <v>608.40000000000009</v>
-      </c>
-      <c r="V12" s="6">
+        <v>642.79999999999995</v>
+      </c>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AB12" s="6">
+        <f t="shared" ref="AB12:AH12" si="9">SUM(AB9:AB11)</f>
+        <v>258.59999999999997</v>
+      </c>
+      <c r="AC12" s="6">
         <f t="shared" si="9"/>
-        <v>629.04</v>
-      </c>
-      <c r="X12" s="6">
-        <f t="shared" ref="X12:AD12" si="10">SUM(X9:X11)</f>
-        <v>258.59999999999997</v>
-      </c>
-      <c r="Y12" s="6">
+        <v>600.1</v>
+      </c>
+      <c r="AD12" s="6">
+        <f t="shared" si="9"/>
+        <v>1402.7</v>
+      </c>
+      <c r="AE12" s="6">
+        <f t="shared" si="9"/>
+        <v>1556.1</v>
+      </c>
+      <c r="AF12" s="6">
+        <f t="shared" si="9"/>
+        <v>1758.7</v>
+      </c>
+      <c r="AG12" s="6">
+        <f t="shared" si="9"/>
+        <v>2097.8000000000002</v>
+      </c>
+      <c r="AH12" s="6">
+        <f t="shared" si="9"/>
+        <v>2245.3000000000002</v>
+      </c>
+      <c r="AI12" s="6">
+        <f t="shared" ref="AI12:AR12" si="10">SUM(AI9:AI11)</f>
+        <v>2279.866</v>
+      </c>
+      <c r="AJ12" s="6">
         <f t="shared" si="10"/>
-        <v>600.1</v>
-      </c>
-      <c r="Z12" s="6">
+        <v>2302.6646600000004</v>
+      </c>
+      <c r="AK12" s="6">
         <f t="shared" si="10"/>
-        <v>1402.7</v>
-      </c>
-      <c r="AA12" s="6">
+        <v>2325.6913066000002</v>
+      </c>
+      <c r="AL12" s="6">
         <f t="shared" si="10"/>
-        <v>1556.1</v>
-      </c>
-      <c r="AB12" s="6">
+        <v>2348.9482196660001</v>
+      </c>
+      <c r="AM12" s="6">
         <f t="shared" si="10"/>
-        <v>1758.7</v>
-      </c>
-      <c r="AC12" s="6">
+        <v>2372.4377018626601</v>
+      </c>
+      <c r="AN12" s="6">
         <f t="shared" si="10"/>
-        <v>2097.8000000000002</v>
-      </c>
-      <c r="AD12" s="6">
+        <v>2396.162078881287</v>
+      </c>
+      <c r="AO12" s="6">
         <f t="shared" si="10"/>
-        <v>2231.54</v>
-      </c>
-      <c r="AE12" s="6">
-        <f t="shared" ref="AE12:AN12" si="11">SUM(AE9:AE11)</f>
-        <v>2265.7220000000002</v>
-      </c>
-      <c r="AF12" s="6">
-        <f t="shared" si="11"/>
-        <v>2288.3792200000003</v>
-      </c>
-      <c r="AG12" s="6">
-        <f t="shared" si="11"/>
-        <v>2311.2630122000005</v>
-      </c>
-      <c r="AH12" s="6">
-        <f t="shared" si="11"/>
-        <v>2334.3756423220002</v>
-      </c>
-      <c r="AI12" s="6">
-        <f t="shared" si="11"/>
-        <v>2357.7193987452201</v>
-      </c>
-      <c r="AJ12" s="6">
-        <f t="shared" si="11"/>
-        <v>2381.2965927326727</v>
-      </c>
-      <c r="AK12" s="6">
-        <f t="shared" si="11"/>
-        <v>2405.1095586599995</v>
-      </c>
-      <c r="AL12" s="6">
-        <f t="shared" si="11"/>
-        <v>2429.1606542465997</v>
-      </c>
-      <c r="AM12" s="6">
-        <f t="shared" si="11"/>
-        <v>2453.4522607890658</v>
-      </c>
-      <c r="AN12" s="6">
-        <f t="shared" si="11"/>
-        <v>2477.9867833969561</v>
+        <v>2420.1236996701</v>
+      </c>
+      <c r="AP12" s="6">
+        <f t="shared" si="10"/>
+        <v>2444.3249366668006</v>
+      </c>
+      <c r="AQ12" s="6">
+        <f t="shared" si="10"/>
+        <v>2468.7681860334687</v>
+      </c>
+      <c r="AR12" s="6">
+        <f t="shared" si="10"/>
+        <v>2493.4558678938033</v>
       </c>
     </row>
-    <row r="13" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="M13" s="9">
-        <f t="shared" ref="M13:T13" si="12">M8-M12</f>
+        <f t="shared" ref="M13:T13" si="11">M8-M12</f>
         <v>-752.9</v>
       </c>
       <c r="N13" s="9">
+        <f t="shared" si="11"/>
+        <v>-736.8</v>
+      </c>
+      <c r="O13" s="9">
+        <f t="shared" si="11"/>
+        <v>-729.90000000000009</v>
+      </c>
+      <c r="P13" s="9">
+        <f t="shared" si="11"/>
+        <v>-787.4</v>
+      </c>
+      <c r="Q13" s="9">
+        <f t="shared" si="11"/>
+        <v>-770.6</v>
+      </c>
+      <c r="R13" s="9">
+        <f t="shared" si="11"/>
+        <v>-732.90000000000009</v>
+      </c>
+      <c r="S13" s="9">
+        <f t="shared" si="11"/>
+        <v>-692</v>
+      </c>
+      <c r="T13" s="9">
+        <f t="shared" si="11"/>
+        <v>-803.1</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" ref="U13:V13" si="12">U8-U12</f>
+        <v>-942.00000000000011</v>
+      </c>
+      <c r="V13" s="9">
         <f t="shared" si="12"/>
-        <v>-736.8</v>
-      </c>
-      <c r="O13" s="9">
-        <f t="shared" si="12"/>
-        <v>-729.90000000000009</v>
-      </c>
-      <c r="P13" s="9">
-        <f t="shared" si="12"/>
-        <v>-787.4</v>
-      </c>
-      <c r="Q13" s="9">
-        <f t="shared" si="12"/>
-        <v>-770.6</v>
-      </c>
-      <c r="R13" s="9">
-        <f t="shared" si="12"/>
-        <v>-732.90000000000009</v>
-      </c>
-      <c r="S13" s="9">
-        <f t="shared" si="12"/>
-        <v>-692</v>
-      </c>
-      <c r="T13" s="9">
-        <f t="shared" si="12"/>
-        <v>-803.1</v>
-      </c>
-      <c r="U13" s="9">
-        <f t="shared" ref="U13:V13" si="13">U8-U12</f>
-        <v>-942.00000000000011</v>
-      </c>
-      <c r="V13" s="9">
+        <v>-1064.6999999999998</v>
+      </c>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AB13" s="9">
+        <f t="shared" ref="AB13:AH13" si="13">AB8-AB12</f>
+        <v>-257.89999999999998</v>
+      </c>
+      <c r="AC13" s="9">
         <f t="shared" si="13"/>
-        <v>-1015.9649999999999</v>
-      </c>
-      <c r="X13" s="9">
-        <f t="shared" ref="X13:AD13" si="14">X8-X12</f>
-        <v>-257.89999999999998</v>
-      </c>
-      <c r="Y13" s="9">
+        <v>-599.20000000000005</v>
+      </c>
+      <c r="AD13" s="9">
+        <f t="shared" si="13"/>
+        <v>-1530.5</v>
+      </c>
+      <c r="AE13" s="9">
+        <f t="shared" si="13"/>
+        <v>-2594</v>
+      </c>
+      <c r="AF13" s="9">
+        <f t="shared" si="13"/>
+        <v>-3099.5</v>
+      </c>
+      <c r="AG13" s="9">
+        <f t="shared" si="13"/>
+        <v>-3020.9000000000005</v>
+      </c>
+      <c r="AH13" s="9">
+        <f t="shared" si="13"/>
+        <v>-3501.8</v>
+      </c>
+      <c r="AI13" s="9">
+        <f t="shared" ref="AI13:AR13" si="14">AI8-AI12</f>
+        <v>-3498.1959999999999</v>
+      </c>
+      <c r="AJ13" s="9">
         <f t="shared" si="14"/>
-        <v>-599.20000000000005</v>
-      </c>
-      <c r="Z13" s="9">
+        <v>-3155.4956600000005</v>
+      </c>
+      <c r="AK13" s="9">
         <f t="shared" si="14"/>
-        <v>-1530.5</v>
-      </c>
-      <c r="AA13" s="9">
+        <v>-2517.5782816000001</v>
+      </c>
+      <c r="AL13" s="9">
         <f t="shared" si="14"/>
-        <v>-2594</v>
-      </c>
-      <c r="AB13" s="9">
+        <v>-1850.0420846660002</v>
+      </c>
+      <c r="AM13" s="9">
         <f t="shared" si="14"/>
-        <v>-3099.5</v>
-      </c>
-      <c r="AC13" s="9">
+        <v>-1436.9886987376601</v>
+      </c>
+      <c r="AN13" s="9">
         <f t="shared" si="14"/>
-        <v>-3020.9000000000005</v>
-      </c>
-      <c r="AD13" s="9">
+        <v>-899.44367388128694</v>
+      </c>
+      <c r="AO13" s="9">
         <f t="shared" si="14"/>
-        <v>-2962.2950000000001</v>
-      </c>
-      <c r="AE13" s="9">
-        <f t="shared" ref="AE13:AN13" si="15">AE8-AE12</f>
-        <v>-2813.7882500000001</v>
-      </c>
-      <c r="AF13" s="9">
-        <f t="shared" si="15"/>
-        <v>-2416.2613450000003</v>
-      </c>
-      <c r="AG13" s="9">
-        <f t="shared" si="15"/>
-        <v>-1965.9812747000005</v>
-      </c>
-      <c r="AH13" s="9">
-        <f t="shared" si="15"/>
-        <v>-1661.0762541970003</v>
-      </c>
-      <c r="AI13" s="9">
-        <f t="shared" si="15"/>
-        <v>-1403.87859890147</v>
-      </c>
-      <c r="AJ13" s="9">
-        <f t="shared" si="15"/>
-        <v>-1169.3576941076728</v>
-      </c>
-      <c r="AK13" s="9">
-        <f t="shared" si="15"/>
-        <v>-933.95039560687474</v>
-      </c>
-      <c r="AL13" s="9">
-        <f t="shared" si="15"/>
-        <v>-648.2837726559751</v>
-      </c>
-      <c r="AM13" s="9">
-        <f t="shared" si="15"/>
-        <v>-405.44384695984763</v>
-      </c>
-      <c r="AN13" s="9">
-        <f t="shared" si="15"/>
-        <v>-122.77710749335529</v>
+        <v>-440.71360905760002</v>
+      </c>
+      <c r="AP13" s="9">
+        <f t="shared" si="14"/>
+        <v>-69.032827931800966</v>
+      </c>
+      <c r="AQ13" s="9">
+        <f t="shared" si="14"/>
+        <v>376.63381922199915</v>
+      </c>
+      <c r="AR13" s="9">
+        <f t="shared" si="14"/>
+        <v>778.75643814998466</v>
       </c>
     </row>
-    <row r="14" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>20</v>
       </c>
@@ -1995,185 +2058,193 @@
         <v>36.799999999999997</v>
       </c>
       <c r="V14" s="6">
-        <v>-300</v>
-      </c>
-      <c r="X14" s="6">
+        <v>-252.5</v>
+      </c>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AB14" s="6">
         <v>19.399999999999999</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="AC14" s="6">
         <v>120.3</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AD14" s="6">
         <v>1049.3</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AE14" s="6">
         <v>-1289.9000000000001</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AF14" s="6">
         <v>-272.2</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AG14" s="6">
         <v>-308.10000000000002</v>
       </c>
-      <c r="AD14" s="6">
+      <c r="AH14" s="6">
         <f>SUM(S14:V14)</f>
-        <v>-848.8</v>
-      </c>
-      <c r="AE14" s="6">
-        <f t="shared" ref="AE14:AN14" si="16">AD14*1.05</f>
-        <v>-891.24</v>
-      </c>
-      <c r="AF14" s="6">
-        <f t="shared" si="16"/>
-        <v>-935.80200000000002</v>
-      </c>
-      <c r="AG14" s="6">
-        <f t="shared" si="16"/>
-        <v>-982.59210000000007</v>
-      </c>
-      <c r="AH14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1031.7217050000002</v>
+        <v>-801.3</v>
       </c>
       <c r="AI14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1083.3077902500002</v>
+        <f t="shared" ref="AI14:AR14" si="15">AH14*1.05</f>
+        <v>-841.36500000000001</v>
       </c>
       <c r="AJ14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1137.4731797625002</v>
+        <f t="shared" si="15"/>
+        <v>-883.43325000000004</v>
       </c>
       <c r="AK14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1194.3468387506252</v>
+        <f t="shared" si="15"/>
+        <v>-927.60491250000007</v>
       </c>
       <c r="AL14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1254.0641806881565</v>
+        <f t="shared" si="15"/>
+        <v>-973.98515812500011</v>
       </c>
       <c r="AM14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1316.7673897225643</v>
+        <f t="shared" si="15"/>
+        <v>-1022.6844160312502</v>
       </c>
       <c r="AN14" s="6">
-        <f t="shared" si="16"/>
-        <v>-1382.6057592086927</v>
+        <f t="shared" si="15"/>
+        <v>-1073.8186368328127</v>
+      </c>
+      <c r="AO14" s="6">
+        <f t="shared" si="15"/>
+        <v>-1127.5095686744532</v>
+      </c>
+      <c r="AP14" s="6">
+        <f t="shared" si="15"/>
+        <v>-1183.885047108176</v>
+      </c>
+      <c r="AQ14" s="6">
+        <f t="shared" si="15"/>
+        <v>-1243.0792994635849</v>
+      </c>
+      <c r="AR14" s="6">
+        <f t="shared" si="15"/>
+        <v>-1305.2332644367641</v>
       </c>
     </row>
-    <row r="15" spans="2:40" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:44" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" ref="M15:T15" si="17">M13-M14</f>
+        <f t="shared" ref="M15:T15" si="16">M13-M14</f>
         <v>-630.6</v>
       </c>
       <c r="N15" s="9">
+        <f t="shared" si="16"/>
+        <v>-653.69999999999993</v>
+      </c>
+      <c r="O15" s="9">
+        <f t="shared" si="16"/>
+        <v>-680.7</v>
+      </c>
+      <c r="P15" s="9">
+        <f t="shared" si="16"/>
+        <v>-643.4</v>
+      </c>
+      <c r="Q15" s="9">
+        <f t="shared" si="16"/>
+        <v>-992.1</v>
+      </c>
+      <c r="R15" s="9">
+        <f t="shared" si="16"/>
+        <v>-396.60000000000008</v>
+      </c>
+      <c r="S15" s="9">
+        <f t="shared" si="16"/>
+        <v>-367.6</v>
+      </c>
+      <c r="T15" s="9">
+        <f t="shared" si="16"/>
+        <v>-541.90000000000009</v>
+      </c>
+      <c r="U15" s="9">
+        <f t="shared" ref="U15:V15" si="17">U13-U14</f>
+        <v>-978.80000000000007</v>
+      </c>
+      <c r="V15" s="9">
         <f t="shared" si="17"/>
-        <v>-653.69999999999993</v>
-      </c>
-      <c r="O15" s="9">
-        <f t="shared" si="17"/>
-        <v>-680.7</v>
-      </c>
-      <c r="P15" s="9">
-        <f t="shared" si="17"/>
-        <v>-643.4</v>
-      </c>
-      <c r="Q15" s="9">
-        <f t="shared" si="17"/>
-        <v>-992.1</v>
-      </c>
-      <c r="R15" s="9">
-        <f t="shared" si="17"/>
-        <v>-396.60000000000008</v>
-      </c>
-      <c r="S15" s="9">
-        <f t="shared" si="17"/>
-        <v>-367.6</v>
-      </c>
-      <c r="T15" s="9">
-        <f t="shared" si="17"/>
-        <v>-541.90000000000009</v>
-      </c>
-      <c r="U15" s="9">
-        <f t="shared" ref="U15:V15" si="18">U13-U14</f>
-        <v>-978.80000000000007</v>
-      </c>
-      <c r="V15" s="9">
+        <v>-812.19999999999982</v>
+      </c>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AB15" s="9">
+        <f t="shared" ref="AB15:AH15" si="18">AB13-AB14</f>
+        <v>-277.29999999999995</v>
+      </c>
+      <c r="AC15" s="9">
         <f t="shared" si="18"/>
-        <v>-715.96499999999992</v>
-      </c>
-      <c r="X15" s="9">
-        <f t="shared" ref="X15:AD15" si="19">X13-X14</f>
-        <v>-277.29999999999995</v>
-      </c>
-      <c r="Y15" s="9">
+        <v>-719.5</v>
+      </c>
+      <c r="AD15" s="9">
+        <f t="shared" si="18"/>
+        <v>-2579.8000000000002</v>
+      </c>
+      <c r="AE15" s="9">
+        <f t="shared" si="18"/>
+        <v>-1304.0999999999999</v>
+      </c>
+      <c r="AF15" s="9">
+        <f t="shared" si="18"/>
+        <v>-2827.3</v>
+      </c>
+      <c r="AG15" s="9">
+        <f t="shared" si="18"/>
+        <v>-2712.8000000000006</v>
+      </c>
+      <c r="AH15" s="9">
+        <f t="shared" si="18"/>
+        <v>-2700.5</v>
+      </c>
+      <c r="AI15" s="9">
+        <f t="shared" ref="AI15:AR15" si="19">AI13-AI14</f>
+        <v>-2656.8310000000001</v>
+      </c>
+      <c r="AJ15" s="9">
         <f t="shared" si="19"/>
-        <v>-719.5</v>
-      </c>
-      <c r="Z15" s="9">
+        <v>-2272.0624100000005</v>
+      </c>
+      <c r="AK15" s="9">
         <f t="shared" si="19"/>
-        <v>-2579.8000000000002</v>
-      </c>
-      <c r="AA15" s="9">
+        <v>-1589.9733691000001</v>
+      </c>
+      <c r="AL15" s="9">
         <f t="shared" si="19"/>
-        <v>-1304.0999999999999</v>
-      </c>
-      <c r="AB15" s="9">
+        <v>-876.05692654100005</v>
+      </c>
+      <c r="AM15" s="9">
         <f t="shared" si="19"/>
-        <v>-2827.3</v>
-      </c>
-      <c r="AC15" s="9">
+        <v>-414.30428270640994</v>
+      </c>
+      <c r="AN15" s="9">
         <f t="shared" si="19"/>
-        <v>-2712.8000000000006</v>
-      </c>
-      <c r="AD15" s="9">
+        <v>174.37496295152573</v>
+      </c>
+      <c r="AO15" s="9">
         <f t="shared" si="19"/>
-        <v>-2113.4949999999999</v>
-      </c>
-      <c r="AE15" s="9">
-        <f t="shared" ref="AE15:AN15" si="20">AE13-AE14</f>
-        <v>-1922.5482500000001</v>
-      </c>
-      <c r="AF15" s="9">
-        <f t="shared" si="20"/>
-        <v>-1480.4593450000002</v>
-      </c>
-      <c r="AG15" s="9">
-        <f t="shared" si="20"/>
-        <v>-983.38917470000047</v>
-      </c>
-      <c r="AH15" s="9">
-        <f t="shared" si="20"/>
-        <v>-629.3545491970001</v>
-      </c>
-      <c r="AI15" s="9">
-        <f t="shared" si="20"/>
-        <v>-320.57080865146986</v>
-      </c>
-      <c r="AJ15" s="9">
-        <f t="shared" si="20"/>
-        <v>-31.884514345172647</v>
-      </c>
-      <c r="AK15" s="9">
-        <f t="shared" si="20"/>
-        <v>260.3964431437505</v>
-      </c>
-      <c r="AL15" s="9">
-        <f t="shared" si="20"/>
-        <v>605.78040803218141</v>
-      </c>
-      <c r="AM15" s="9">
-        <f t="shared" si="20"/>
-        <v>911.32354276271667</v>
-      </c>
-      <c r="AN15" s="9">
-        <f t="shared" si="20"/>
-        <v>1259.8286517153374</v>
+        <v>686.79595961685322</v>
+      </c>
+      <c r="AP15" s="9">
+        <f t="shared" si="19"/>
+        <v>1114.852219176375</v>
+      </c>
+      <c r="AQ15" s="9">
+        <f t="shared" si="19"/>
+        <v>1619.713118685584</v>
+      </c>
+      <c r="AR15" s="9">
+        <f t="shared" si="19"/>
+        <v>2083.9897025867485</v>
       </c>
     </row>
-    <row r="16" spans="2:40" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:44" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>22</v>
       </c>
@@ -2205,41 +2276,33 @@
         <v>-0.4</v>
       </c>
       <c r="V16" s="6">
-        <v>-2</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AB16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="6">
         <v>-0.2</v>
       </c>
-      <c r="Z16" s="6">
+      <c r="AD16" s="6">
         <v>-0.1</v>
       </c>
-      <c r="AA16" s="6">
+      <c r="AE16" s="6">
         <v>0.4</v>
       </c>
-      <c r="AB16" s="6">
+      <c r="AF16" s="6">
         <v>1</v>
       </c>
-      <c r="AC16" s="6">
+      <c r="AG16" s="6">
         <v>1.2</v>
       </c>
-      <c r="AD16" s="6">
+      <c r="AH16" s="6">
         <f>SUM(S16:V16)</f>
-        <v>-6.2</v>
-      </c>
-      <c r="AE16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>0</v>
+        <v>-2.4000000000000004</v>
       </c>
       <c r="AI16" s="6">
         <v>0</v>
@@ -2259,505 +2322,521 @@
       <c r="AN16" s="6">
         <v>0</v>
       </c>
+      <c r="AO16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="6">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="17" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:140" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
       <c r="M17" s="9">
-        <f t="shared" ref="M17:T17" si="21">M15-M16</f>
+        <f t="shared" ref="M17:T17" si="20">M15-M16</f>
         <v>-630.9</v>
       </c>
       <c r="N17" s="9">
+        <f t="shared" si="20"/>
+        <v>-653.69999999999993</v>
+      </c>
+      <c r="O17" s="9">
+        <f t="shared" si="20"/>
+        <v>-680.90000000000009</v>
+      </c>
+      <c r="P17" s="9">
+        <f t="shared" si="20"/>
+        <v>-643.29999999999995</v>
+      </c>
+      <c r="Q17" s="9">
+        <f t="shared" si="20"/>
+        <v>-992.6</v>
+      </c>
+      <c r="R17" s="9">
+        <f t="shared" si="20"/>
+        <v>-397.2000000000001</v>
+      </c>
+      <c r="S17" s="9">
+        <f t="shared" si="20"/>
+        <v>-366.20000000000005</v>
+      </c>
+      <c r="T17" s="9">
+        <f t="shared" si="20"/>
+        <v>-539.50000000000011</v>
+      </c>
+      <c r="U17" s="9">
+        <f t="shared" ref="U17:V17" si="21">U15-U16</f>
+        <v>-978.40000000000009</v>
+      </c>
+      <c r="V17" s="9">
         <f t="shared" si="21"/>
-        <v>-653.69999999999993</v>
-      </c>
-      <c r="O17" s="9">
-        <f t="shared" si="21"/>
-        <v>-680.90000000000009</v>
-      </c>
-      <c r="P17" s="9">
-        <f t="shared" si="21"/>
-        <v>-643.29999999999995</v>
-      </c>
-      <c r="Q17" s="9">
-        <f t="shared" si="21"/>
-        <v>-992.6</v>
-      </c>
-      <c r="R17" s="9">
-        <f t="shared" si="21"/>
-        <v>-397.2000000000001</v>
-      </c>
-      <c r="S17" s="9">
-        <f t="shared" si="21"/>
-        <v>-366.20000000000005</v>
-      </c>
-      <c r="T17" s="9">
-        <f t="shared" si="21"/>
-        <v>-539.50000000000011</v>
-      </c>
-      <c r="U17" s="9">
-        <f t="shared" ref="U17:V17" si="22">U15-U16</f>
-        <v>-978.40000000000009</v>
-      </c>
-      <c r="V17" s="9">
+        <v>-813.99999999999977</v>
+      </c>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AB17" s="9">
+        <f t="shared" ref="AB17:AH17" si="22">AB15-AB16</f>
+        <v>-277.29999999999995</v>
+      </c>
+      <c r="AC17" s="9">
         <f t="shared" si="22"/>
-        <v>-713.96499999999992</v>
-      </c>
-      <c r="X17" s="9">
-        <f t="shared" ref="X17:AD17" si="23">X15-X16</f>
-        <v>-277.29999999999995</v>
-      </c>
-      <c r="Y17" s="9">
+        <v>-719.3</v>
+      </c>
+      <c r="AD17" s="9">
+        <f t="shared" si="22"/>
+        <v>-2579.7000000000003</v>
+      </c>
+      <c r="AE17" s="9">
+        <f t="shared" si="22"/>
+        <v>-1304.5</v>
+      </c>
+      <c r="AF17" s="9">
+        <f t="shared" si="22"/>
+        <v>-2828.3</v>
+      </c>
+      <c r="AG17" s="9">
+        <f t="shared" si="22"/>
+        <v>-2714.0000000000005</v>
+      </c>
+      <c r="AH17" s="9">
+        <f t="shared" si="22"/>
+        <v>-2698.1</v>
+      </c>
+      <c r="AI17" s="9">
+        <f t="shared" ref="AI17:AR17" si="23">AI15-AI16</f>
+        <v>-2656.8310000000001</v>
+      </c>
+      <c r="AJ17" s="9">
         <f t="shared" si="23"/>
-        <v>-719.3</v>
-      </c>
-      <c r="Z17" s="9">
+        <v>-2272.0624100000005</v>
+      </c>
+      <c r="AK17" s="9">
         <f t="shared" si="23"/>
-        <v>-2579.7000000000003</v>
-      </c>
-      <c r="AA17" s="9">
+        <v>-1589.9733691000001</v>
+      </c>
+      <c r="AL17" s="9">
         <f t="shared" si="23"/>
-        <v>-1304.5</v>
-      </c>
-      <c r="AB17" s="9">
+        <v>-876.05692654100005</v>
+      </c>
+      <c r="AM17" s="9">
         <f t="shared" si="23"/>
-        <v>-2828.3</v>
-      </c>
-      <c r="AC17" s="9">
+        <v>-414.30428270640994</v>
+      </c>
+      <c r="AN17" s="9">
         <f t="shared" si="23"/>
-        <v>-2714.0000000000005</v>
-      </c>
-      <c r="AD17" s="9">
+        <v>174.37496295152573</v>
+      </c>
+      <c r="AO17" s="9">
         <f t="shared" si="23"/>
-        <v>-2107.2950000000001</v>
-      </c>
-      <c r="AE17" s="9">
-        <f t="shared" ref="AE17:AN17" si="24">AE15-AE16</f>
-        <v>-1922.5482500000001</v>
-      </c>
-      <c r="AF17" s="9">
-        <f t="shared" si="24"/>
-        <v>-1480.4593450000002</v>
-      </c>
-      <c r="AG17" s="9">
-        <f t="shared" si="24"/>
-        <v>-983.38917470000047</v>
-      </c>
-      <c r="AH17" s="9">
-        <f t="shared" si="24"/>
-        <v>-629.3545491970001</v>
-      </c>
-      <c r="AI17" s="9">
-        <f t="shared" si="24"/>
-        <v>-320.57080865146986</v>
-      </c>
-      <c r="AJ17" s="9">
-        <f t="shared" si="24"/>
-        <v>-31.884514345172647</v>
-      </c>
-      <c r="AK17" s="9">
-        <f t="shared" si="24"/>
-        <v>260.3964431437505</v>
-      </c>
-      <c r="AL17" s="9">
-        <f t="shared" si="24"/>
-        <v>605.78040803218141</v>
-      </c>
-      <c r="AM17" s="9">
-        <f t="shared" si="24"/>
-        <v>911.32354276271667</v>
-      </c>
-      <c r="AN17" s="9">
-        <f t="shared" si="24"/>
-        <v>1259.8286517153374</v>
-      </c>
-      <c r="AO17" s="2">
-        <f>AN17*(1+$AQ$27)</f>
-        <v>1247.230365198184</v>
-      </c>
-      <c r="AP17" s="2">
-        <f t="shared" ref="AP17:DA17" si="25">AO17*(1+$AQ$27)</f>
-        <v>1234.7580615462023</v>
-      </c>
-      <c r="AQ17" s="2">
+        <v>686.79595961685322</v>
+      </c>
+      <c r="AP17" s="9">
+        <f t="shared" si="23"/>
+        <v>1114.852219176375</v>
+      </c>
+      <c r="AQ17" s="9">
+        <f t="shared" si="23"/>
+        <v>1619.713118685584</v>
+      </c>
+      <c r="AR17" s="9">
+        <f t="shared" si="23"/>
+        <v>2083.9897025867485</v>
+      </c>
+      <c r="AS17" s="2">
+        <f>AR17*(1+$AU$27)</f>
+        <v>2063.1498055608808</v>
+      </c>
+      <c r="AT17" s="2">
+        <f t="shared" ref="AT17:DE17" si="24">AS17*(1+$AU$27)</f>
+        <v>2042.5183075052721</v>
+      </c>
+      <c r="AU17" s="2">
+        <f t="shared" si="24"/>
+        <v>2022.0931244302194</v>
+      </c>
+      <c r="AV17" s="2">
+        <f t="shared" si="24"/>
+        <v>2001.8721931859172</v>
+      </c>
+      <c r="AW17" s="2">
+        <f t="shared" si="24"/>
+        <v>1981.8534712540581</v>
+      </c>
+      <c r="AX17" s="2">
+        <f t="shared" si="24"/>
+        <v>1962.0349365415175</v>
+      </c>
+      <c r="AY17" s="2">
+        <f t="shared" si="24"/>
+        <v>1942.4145871761023</v>
+      </c>
+      <c r="AZ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1922.9904413043412</v>
+      </c>
+      <c r="BA17" s="2">
+        <f t="shared" si="24"/>
+        <v>1903.7605368912978</v>
+      </c>
+      <c r="BB17" s="2">
+        <f t="shared" si="24"/>
+        <v>1884.7229315223847</v>
+      </c>
+      <c r="BC17" s="2">
+        <f t="shared" si="24"/>
+        <v>1865.8757022071609</v>
+      </c>
+      <c r="BD17" s="2">
+        <f t="shared" si="24"/>
+        <v>1847.2169451850893</v>
+      </c>
+      <c r="BE17" s="2">
+        <f t="shared" si="24"/>
+        <v>1828.7447757332384</v>
+      </c>
+      <c r="BF17" s="2">
+        <f t="shared" si="24"/>
+        <v>1810.4573279759061</v>
+      </c>
+      <c r="BG17" s="2">
+        <f t="shared" si="24"/>
+        <v>1792.352754696147</v>
+      </c>
+      <c r="BH17" s="2">
+        <f t="shared" si="24"/>
+        <v>1774.4292271491856</v>
+      </c>
+      <c r="BI17" s="2">
+        <f t="shared" si="24"/>
+        <v>1756.6849348776939</v>
+      </c>
+      <c r="BJ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1739.1180855289169</v>
+      </c>
+      <c r="BK17" s="2">
+        <f t="shared" si="24"/>
+        <v>1721.7269046736278</v>
+      </c>
+      <c r="BL17" s="2">
+        <f t="shared" si="24"/>
+        <v>1704.5096356268916</v>
+      </c>
+      <c r="BM17" s="2">
+        <f t="shared" si="24"/>
+        <v>1687.4645392706227</v>
+      </c>
+      <c r="BN17" s="2">
+        <f t="shared" si="24"/>
+        <v>1670.5898938779164</v>
+      </c>
+      <c r="BO17" s="2">
+        <f t="shared" si="24"/>
+        <v>1653.8839949391372</v>
+      </c>
+      <c r="BP17" s="2">
+        <f t="shared" si="24"/>
+        <v>1637.3451549897459</v>
+      </c>
+      <c r="BQ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1620.9717034398484</v>
+      </c>
+      <c r="BR17" s="2">
+        <f t="shared" si="24"/>
+        <v>1604.76198640545</v>
+      </c>
+      <c r="BS17" s="2">
+        <f t="shared" si="24"/>
+        <v>1588.7143665413955</v>
+      </c>
+      <c r="BT17" s="2">
+        <f t="shared" si="24"/>
+        <v>1572.8272228759815</v>
+      </c>
+      <c r="BU17" s="2">
+        <f t="shared" si="24"/>
+        <v>1557.0989506472217</v>
+      </c>
+      <c r="BV17" s="2">
+        <f t="shared" si="24"/>
+        <v>1541.5279611407495</v>
+      </c>
+      <c r="BW17" s="2">
+        <f t="shared" si="24"/>
+        <v>1526.1126815293421</v>
+      </c>
+      <c r="BX17" s="2">
+        <f t="shared" si="24"/>
+        <v>1510.8515547140487</v>
+      </c>
+      <c r="BY17" s="2">
+        <f t="shared" si="24"/>
+        <v>1495.7430391669081</v>
+      </c>
+      <c r="BZ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1480.7856087752391</v>
+      </c>
+      <c r="CA17" s="2">
+        <f t="shared" si="24"/>
+        <v>1465.9777526874866</v>
+      </c>
+      <c r="CB17" s="2">
+        <f t="shared" si="24"/>
+        <v>1451.3179751606117</v>
+      </c>
+      <c r="CC17" s="2">
+        <f t="shared" si="24"/>
+        <v>1436.8047954090055</v>
+      </c>
+      <c r="CD17" s="2">
+        <f t="shared" si="24"/>
+        <v>1422.4367474549153</v>
+      </c>
+      <c r="CE17" s="2">
+        <f t="shared" si="24"/>
+        <v>1408.2123799803662</v>
+      </c>
+      <c r="CF17" s="2">
+        <f t="shared" si="24"/>
+        <v>1394.1302561805626</v>
+      </c>
+      <c r="CG17" s="2">
+        <f t="shared" si="24"/>
+        <v>1380.1889536187568</v>
+      </c>
+      <c r="CH17" s="2">
+        <f t="shared" si="24"/>
+        <v>1366.3870640825692</v>
+      </c>
+      <c r="CI17" s="2">
+        <f t="shared" si="24"/>
+        <v>1352.7231934417434</v>
+      </c>
+      <c r="CJ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1339.195961507326</v>
+      </c>
+      <c r="CK17" s="2">
+        <f t="shared" si="24"/>
+        <v>1325.8040018922527</v>
+      </c>
+      <c r="CL17" s="2">
+        <f t="shared" si="24"/>
+        <v>1312.5459618733303</v>
+      </c>
+      <c r="CM17" s="2">
+        <f t="shared" si="24"/>
+        <v>1299.4205022545971</v>
+      </c>
+      <c r="CN17" s="2">
+        <f t="shared" si="24"/>
+        <v>1286.4262972320512</v>
+      </c>
+      <c r="CO17" s="2">
+        <f t="shared" si="24"/>
+        <v>1273.5620342597306</v>
+      </c>
+      <c r="CP17" s="2">
+        <f t="shared" si="24"/>
+        <v>1260.8264139171333</v>
+      </c>
+      <c r="CQ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1248.218149777962</v>
+      </c>
+      <c r="CR17" s="2">
+        <f t="shared" si="24"/>
+        <v>1235.7359682801823</v>
+      </c>
+      <c r="CS17" s="2">
+        <f t="shared" si="24"/>
+        <v>1223.3786085973804</v>
+      </c>
+      <c r="CT17" s="2">
+        <f t="shared" si="24"/>
+        <v>1211.1448225114066</v>
+      </c>
+      <c r="CU17" s="2">
+        <f t="shared" si="24"/>
+        <v>1199.0333742862924</v>
+      </c>
+      <c r="CV17" s="2">
+        <f t="shared" si="24"/>
+        <v>1187.0430405434295</v>
+      </c>
+      <c r="CW17" s="2">
+        <f t="shared" si="24"/>
+        <v>1175.1726101379952</v>
+      </c>
+      <c r="CX17" s="2">
+        <f t="shared" si="24"/>
+        <v>1163.4208840366152</v>
+      </c>
+      <c r="CY17" s="2">
+        <f t="shared" si="24"/>
+        <v>1151.786675196249</v>
+      </c>
+      <c r="CZ17" s="2">
+        <f t="shared" si="24"/>
+        <v>1140.2688084442866</v>
+      </c>
+      <c r="DA17" s="2">
+        <f t="shared" si="24"/>
+        <v>1128.8661203598438</v>
+      </c>
+      <c r="DB17" s="2">
+        <f t="shared" si="24"/>
+        <v>1117.5774591562454</v>
+      </c>
+      <c r="DC17" s="2">
+        <f t="shared" si="24"/>
+        <v>1106.4016845646829</v>
+      </c>
+      <c r="DD17" s="2">
+        <f t="shared" si="24"/>
+        <v>1095.3376677190361</v>
+      </c>
+      <c r="DE17" s="2">
+        <f t="shared" si="24"/>
+        <v>1084.3842910418457</v>
+      </c>
+      <c r="DF17" s="2">
+        <f t="shared" ref="DF17:EJ17" si="25">DE17*(1+$AU$27)</f>
+        <v>1073.5404481314272</v>
+      </c>
+      <c r="DG17" s="2">
         <f t="shared" si="25"/>
-        <v>1222.4104809307403</v>
-      </c>
-      <c r="AR17" s="2">
+        <v>1062.8050436501128</v>
+      </c>
+      <c r="DH17" s="2">
         <f t="shared" si="25"/>
-        <v>1210.1863761214329</v>
-      </c>
-      <c r="AS17" s="2">
+        <v>1052.1769932136117</v>
+      </c>
+      <c r="DI17" s="2">
         <f t="shared" si="25"/>
-        <v>1198.0845123602185</v>
-      </c>
-      <c r="AT17" s="2">
+        <v>1041.6552232814756</v>
+      </c>
+      <c r="DJ17" s="2">
         <f t="shared" si="25"/>
-        <v>1186.1036672366163</v>
-      </c>
-      <c r="AU17" s="2">
+        <v>1031.2386710486608</v>
+      </c>
+      <c r="DK17" s="2">
         <f t="shared" si="25"/>
-        <v>1174.24263056425</v>
-      </c>
-      <c r="AV17" s="2">
+        <v>1020.9262843381741</v>
+      </c>
+      <c r="DL17" s="2">
         <f t="shared" si="25"/>
-        <v>1162.5002042586075</v>
-      </c>
-      <c r="AW17" s="2">
+        <v>1010.7170214947923</v>
+      </c>
+      <c r="DM17" s="2">
         <f t="shared" si="25"/>
-        <v>1150.8752022160213</v>
-      </c>
-      <c r="AX17" s="2">
+        <v>1000.6098512798444</v>
+      </c>
+      <c r="DN17" s="2">
         <f t="shared" si="25"/>
-        <v>1139.3664501938611</v>
-      </c>
-      <c r="AY17" s="2">
+        <v>990.60375276704599</v>
+      </c>
+      <c r="DO17" s="2">
         <f t="shared" si="25"/>
-        <v>1127.9727856919224</v>
-      </c>
-      <c r="AZ17" s="2">
+        <v>980.6977152393755</v>
+      </c>
+      <c r="DP17" s="2">
         <f t="shared" si="25"/>
-        <v>1116.6930578350032</v>
-      </c>
-      <c r="BA17" s="2">
+        <v>970.89073808698174</v>
+      </c>
+      <c r="DQ17" s="2">
         <f t="shared" si="25"/>
-        <v>1105.5261272566531</v>
-      </c>
-      <c r="BB17" s="2">
+        <v>961.1818307061119</v>
+      </c>
+      <c r="DR17" s="2">
         <f t="shared" si="25"/>
-        <v>1094.4708659840867</v>
-      </c>
-      <c r="BC17" s="2">
+        <v>951.57001239905082</v>
+      </c>
+      <c r="DS17" s="2">
         <f t="shared" si="25"/>
-        <v>1083.5261573242458</v>
-      </c>
-      <c r="BD17" s="2">
+        <v>942.05431227506028</v>
+      </c>
+      <c r="DT17" s="2">
         <f t="shared" si="25"/>
-        <v>1072.6908957510034</v>
-      </c>
-      <c r="BE17" s="2">
+        <v>932.6337691523097</v>
+      </c>
+      <c r="DU17" s="2">
         <f t="shared" si="25"/>
-        <v>1061.9639867934934</v>
-      </c>
-      <c r="BF17" s="2">
+        <v>923.30743146078657</v>
+      </c>
+      <c r="DV17" s="2">
         <f t="shared" si="25"/>
-        <v>1051.3443469255585</v>
-      </c>
-      <c r="BG17" s="2">
+        <v>914.07435714617873</v>
+      </c>
+      <c r="DW17" s="2">
         <f t="shared" si="25"/>
-        <v>1040.8309034563028</v>
-      </c>
-      <c r="BH17" s="2">
+        <v>904.9336135747169</v>
+      </c>
+      <c r="DX17" s="2">
         <f t="shared" si="25"/>
-        <v>1030.4225944217399</v>
-      </c>
-      <c r="BI17" s="2">
+        <v>895.88427743896978</v>
+      </c>
+      <c r="DY17" s="2">
         <f t="shared" si="25"/>
-        <v>1020.1183684775225</v>
-      </c>
-      <c r="BJ17" s="2">
+        <v>886.92543466458005</v>
+      </c>
+      <c r="DZ17" s="2">
         <f t="shared" si="25"/>
-        <v>1009.9171847927472</v>
-      </c>
-      <c r="BK17" s="2">
+        <v>878.05618031793426</v>
+      </c>
+      <c r="EA17" s="2">
         <f t="shared" si="25"/>
-        <v>999.81801294481977</v>
-      </c>
-      <c r="BL17" s="2">
+        <v>869.27561851475491</v>
+      </c>
+      <c r="EB17" s="2">
         <f t="shared" si="25"/>
-        <v>989.81983281537157</v>
-      </c>
-      <c r="BM17" s="2">
+        <v>860.58286232960734</v>
+      </c>
+      <c r="EC17" s="2">
         <f t="shared" si="25"/>
-        <v>979.92163448721783</v>
-      </c>
-      <c r="BN17" s="2">
+        <v>851.9770337063112</v>
+      </c>
+      <c r="ED17" s="2">
         <f t="shared" si="25"/>
-        <v>970.12241814234562</v>
-      </c>
-      <c r="BO17" s="2">
+        <v>843.45726336924804</v>
+      </c>
+      <c r="EE17" s="2">
         <f t="shared" si="25"/>
-        <v>960.42119396092221</v>
-      </c>
-      <c r="BP17" s="2">
+        <v>835.02269073555556</v>
+      </c>
+      <c r="EF17" s="2">
         <f t="shared" si="25"/>
-        <v>950.81698202131292</v>
-      </c>
-      <c r="BQ17" s="2">
+        <v>826.67246382819997</v>
+      </c>
+      <c r="EG17" s="2">
         <f t="shared" si="25"/>
-        <v>941.30881220109984</v>
-      </c>
-      <c r="BR17" s="2">
+        <v>818.40573918991799</v>
+      </c>
+      <c r="EH17" s="2">
         <f t="shared" si="25"/>
-        <v>931.89572407908884</v>
-      </c>
-      <c r="BS17" s="2">
+        <v>810.22168179801884</v>
+      </c>
+      <c r="EI17" s="2">
         <f t="shared" si="25"/>
-        <v>922.57676683829789</v>
-      </c>
-      <c r="BT17" s="2">
+        <v>802.11946498003863</v>
+      </c>
+      <c r="EJ17" s="2">
         <f t="shared" si="25"/>
-        <v>913.35099916991487</v>
-      </c>
-      <c r="BU17" s="2">
-        <f t="shared" si="25"/>
-        <v>904.21748917821571</v>
-      </c>
-      <c r="BV17" s="2">
-        <f t="shared" si="25"/>
-        <v>895.1753142864336</v>
-      </c>
-      <c r="BW17" s="2">
-        <f t="shared" si="25"/>
-        <v>886.22356114356921</v>
-      </c>
-      <c r="BX17" s="2">
-        <f t="shared" si="25"/>
-        <v>877.36132553213349</v>
-      </c>
-      <c r="BY17" s="2">
-        <f t="shared" si="25"/>
-        <v>868.58771227681211</v>
-      </c>
-      <c r="BZ17" s="2">
-        <f t="shared" si="25"/>
-        <v>859.90183515404397</v>
-      </c>
-      <c r="CA17" s="2">
-        <f t="shared" si="25"/>
-        <v>851.30281680250357</v>
-      </c>
-      <c r="CB17" s="2">
-        <f t="shared" si="25"/>
-        <v>842.78978863447855</v>
-      </c>
-      <c r="CC17" s="2">
-        <f t="shared" si="25"/>
-        <v>834.36189074813376</v>
-      </c>
-      <c r="CD17" s="2">
-        <f t="shared" si="25"/>
-        <v>826.01827184065246</v>
-      </c>
-      <c r="CE17" s="2">
-        <f t="shared" si="25"/>
-        <v>817.75808912224591</v>
-      </c>
-      <c r="CF17" s="2">
-        <f t="shared" si="25"/>
-        <v>809.58050823102349</v>
-      </c>
-      <c r="CG17" s="2">
-        <f t="shared" si="25"/>
-        <v>801.48470314871327</v>
-      </c>
-      <c r="CH17" s="2">
-        <f t="shared" si="25"/>
-        <v>793.46985611722607</v>
-      </c>
-      <c r="CI17" s="2">
-        <f t="shared" si="25"/>
-        <v>785.53515755605383</v>
-      </c>
-      <c r="CJ17" s="2">
-        <f t="shared" si="25"/>
-        <v>777.67980598049326</v>
-      </c>
-      <c r="CK17" s="2">
-        <f t="shared" si="25"/>
-        <v>769.90300792068831</v>
-      </c>
-      <c r="CL17" s="2">
-        <f t="shared" si="25"/>
-        <v>762.20397784148145</v>
-      </c>
-      <c r="CM17" s="2">
-        <f t="shared" si="25"/>
-        <v>754.58193806306667</v>
-      </c>
-      <c r="CN17" s="2">
-        <f t="shared" si="25"/>
-        <v>747.03611868243604</v>
-      </c>
-      <c r="CO17" s="2">
-        <f t="shared" si="25"/>
-        <v>739.56575749561171</v>
-      </c>
-      <c r="CP17" s="2">
-        <f t="shared" si="25"/>
-        <v>732.17009992065562</v>
-      </c>
-      <c r="CQ17" s="2">
-        <f t="shared" si="25"/>
-        <v>724.84839892144907</v>
-      </c>
-      <c r="CR17" s="2">
-        <f t="shared" si="25"/>
-        <v>717.59991493223458</v>
-      </c>
-      <c r="CS17" s="2">
-        <f t="shared" si="25"/>
-        <v>710.42391578291222</v>
-      </c>
-      <c r="CT17" s="2">
-        <f t="shared" si="25"/>
-        <v>703.31967662508305</v>
-      </c>
-      <c r="CU17" s="2">
-        <f t="shared" si="25"/>
-        <v>696.28647985883219</v>
-      </c>
-      <c r="CV17" s="2">
-        <f t="shared" si="25"/>
-        <v>689.32361506024381</v>
-      </c>
-      <c r="CW17" s="2">
-        <f t="shared" si="25"/>
-        <v>682.43037890964138</v>
-      </c>
-      <c r="CX17" s="2">
-        <f t="shared" si="25"/>
-        <v>675.60607512054492</v>
-      </c>
-      <c r="CY17" s="2">
-        <f t="shared" si="25"/>
-        <v>668.85001436933942</v>
-      </c>
-      <c r="CZ17" s="2">
-        <f t="shared" si="25"/>
-        <v>662.16151422564599</v>
-      </c>
-      <c r="DA17" s="2">
-        <f t="shared" si="25"/>
-        <v>655.53989908338951</v>
-      </c>
-      <c r="DB17" s="2">
-        <f t="shared" ref="DB17:EF17" si="26">DA17*(1+$AQ$27)</f>
-        <v>648.98450009255566</v>
-      </c>
-      <c r="DC17" s="2">
-        <f t="shared" si="26"/>
-        <v>642.49465509163008</v>
-      </c>
-      <c r="DD17" s="2">
-        <f t="shared" si="26"/>
-        <v>636.0697085407138</v>
-      </c>
-      <c r="DE17" s="2">
-        <f t="shared" si="26"/>
-        <v>629.70901145530661</v>
-      </c>
-      <c r="DF17" s="2">
-        <f t="shared" si="26"/>
-        <v>623.41192134075357</v>
-      </c>
-      <c r="DG17" s="2">
-        <f t="shared" si="26"/>
-        <v>617.17780212734601</v>
-      </c>
-      <c r="DH17" s="2">
-        <f t="shared" si="26"/>
-        <v>611.00602410607257</v>
-      </c>
-      <c r="DI17" s="2">
-        <f t="shared" si="26"/>
-        <v>604.89596386501182</v>
-      </c>
-      <c r="DJ17" s="2">
-        <f t="shared" si="26"/>
-        <v>598.84700422636172</v>
-      </c>
-      <c r="DK17" s="2">
-        <f t="shared" si="26"/>
-        <v>592.85853418409806</v>
-      </c>
-      <c r="DL17" s="2">
-        <f t="shared" si="26"/>
-        <v>586.92994884225709</v>
-      </c>
-      <c r="DM17" s="2">
-        <f t="shared" si="26"/>
-        <v>581.06064935383449</v>
-      </c>
-      <c r="DN17" s="2">
-        <f t="shared" si="26"/>
-        <v>575.25004286029616</v>
-      </c>
-      <c r="DO17" s="2">
-        <f t="shared" si="26"/>
-        <v>569.4975424316932</v>
-      </c>
-      <c r="DP17" s="2">
-        <f t="shared" si="26"/>
-        <v>563.8025670073763</v>
-      </c>
-      <c r="DQ17" s="2">
-        <f t="shared" si="26"/>
-        <v>558.16454133730258</v>
-      </c>
-      <c r="DR17" s="2">
-        <f t="shared" si="26"/>
-        <v>552.58289592392953</v>
-      </c>
-      <c r="DS17" s="2">
-        <f t="shared" si="26"/>
-        <v>547.05706696469019</v>
-      </c>
-      <c r="DT17" s="2">
-        <f t="shared" si="26"/>
-        <v>541.58649629504328</v>
-      </c>
-      <c r="DU17" s="2">
-        <f t="shared" si="26"/>
-        <v>536.17063133209285</v>
-      </c>
-      <c r="DV17" s="2">
-        <f t="shared" si="26"/>
-        <v>530.8089250187719</v>
-      </c>
-      <c r="DW17" s="2">
-        <f t="shared" si="26"/>
-        <v>525.50083576858412</v>
-      </c>
-      <c r="DX17" s="2">
-        <f t="shared" si="26"/>
-        <v>520.2458274108983</v>
-      </c>
-      <c r="DY17" s="2">
-        <f t="shared" si="26"/>
-        <v>515.04336913678935</v>
-      </c>
-      <c r="DZ17" s="2">
-        <f t="shared" si="26"/>
-        <v>509.89293544542147</v>
-      </c>
-      <c r="EA17" s="2">
-        <f t="shared" si="26"/>
-        <v>504.79400609096723</v>
-      </c>
-      <c r="EB17" s="2">
-        <f t="shared" si="26"/>
-        <v>499.74606603005753</v>
-      </c>
-      <c r="EC17" s="2">
-        <f t="shared" si="26"/>
-        <v>494.74860536975694</v>
-      </c>
-      <c r="ED17" s="2">
-        <f t="shared" si="26"/>
-        <v>489.80111931605938</v>
-      </c>
-      <c r="EE17" s="2">
-        <f t="shared" si="26"/>
-        <v>484.9031081228988</v>
-      </c>
-      <c r="EF17" s="2">
-        <f t="shared" si="26"/>
-        <v>480.05407704166981</v>
+        <v>794.09827033023828</v>
       </c>
     </row>
-    <row r="18" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>2</v>
       </c>
@@ -2798,281 +2877,297 @@
         <v>324.2</v>
       </c>
       <c r="V18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
-      </c>
-      <c r="X18" s="6">
-        <f t="shared" ref="X18:AC18" si="27">3031.5</f>
+        <f>325</f>
+        <v>325</v>
+      </c>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AB18" s="6">
+        <f t="shared" ref="AB18:AG18" si="26">3031.5</f>
         <v>3031.5</v>
       </c>
-      <c r="Y18" s="6">
-        <f t="shared" si="27"/>
+      <c r="AC18" s="6">
+        <f t="shared" si="26"/>
         <v>3031.5</v>
       </c>
-      <c r="Z18" s="6">
-        <f t="shared" si="27"/>
+      <c r="AD18" s="6">
+        <f t="shared" si="26"/>
         <v>3031.5</v>
       </c>
-      <c r="AA18" s="6">
-        <f t="shared" si="27"/>
+      <c r="AE18" s="6">
+        <f t="shared" si="26"/>
         <v>3031.5</v>
       </c>
-      <c r="AB18" s="6">
-        <f t="shared" si="27"/>
+      <c r="AF18" s="6">
+        <f t="shared" si="26"/>
         <v>3031.5</v>
       </c>
-      <c r="AC18" s="6">
-        <f t="shared" si="27"/>
+      <c r="AG18" s="6">
+        <f t="shared" si="26"/>
         <v>3031.5</v>
       </c>
-      <c r="AD18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
-      </c>
-      <c r="AE18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
-      </c>
-      <c r="AF18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
-      </c>
-      <c r="AG18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
-      </c>
       <c r="AH18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AI18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AJ18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AK18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AL18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AM18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
       </c>
       <c r="AN18" s="6">
-        <f>324.2</f>
-        <v>324.2</v>
+        <f>325</f>
+        <v>325</v>
+      </c>
+      <c r="AO18" s="6">
+        <f>325</f>
+        <v>325</v>
+      </c>
+      <c r="AP18" s="6">
+        <f>325</f>
+        <v>325</v>
+      </c>
+      <c r="AQ18" s="6">
+        <f>325</f>
+        <v>325</v>
+      </c>
+      <c r="AR18" s="6">
+        <f>325</f>
+        <v>325</v>
       </c>
     </row>
-    <row r="19" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>24</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" ref="M19:T19" si="28">M17/M18</f>
+        <f t="shared" ref="M19:T19" si="27">M17/M18</f>
         <v>-0.20811479465611082</v>
       </c>
       <c r="N19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.21563582384957938</v>
+      </c>
+      <c r="O19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.22460827972950687</v>
+      </c>
+      <c r="P19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.2108972887912664</v>
+      </c>
+      <c r="Q19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.32742866567705758</v>
+      </c>
+      <c r="R19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.13102424542305793</v>
+      </c>
+      <c r="S19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.12005376520342262</v>
+      </c>
+      <c r="T19" s="8">
+        <f t="shared" si="27"/>
+        <v>-0.17686784906402653</v>
+      </c>
+      <c r="U19" s="8">
+        <f t="shared" ref="U19:V19" si="28">U17/U18</f>
+        <v>-3.0178901912399758</v>
+      </c>
+      <c r="V19" s="8">
         <f t="shared" si="28"/>
-        <v>-0.21563582384957938</v>
-      </c>
-      <c r="O19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.22460827972950687</v>
-      </c>
-      <c r="P19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.2108972887912664</v>
-      </c>
-      <c r="Q19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.32742866567705758</v>
-      </c>
-      <c r="R19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.13102424542305793</v>
-      </c>
-      <c r="S19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.12005376520342262</v>
-      </c>
-      <c r="T19" s="8">
-        <f t="shared" si="28"/>
-        <v>-0.17686784906402653</v>
-      </c>
-      <c r="U19" s="8">
-        <f t="shared" ref="U19:V19" si="29">U17/U18</f>
-        <v>-3.0178901912399758</v>
-      </c>
-      <c r="V19" s="8">
+        <v>-2.5046153846153838</v>
+      </c>
+      <c r="W19" s="8"/>
+      <c r="X19" s="8"/>
+      <c r="Y19" s="8"/>
+      <c r="Z19" s="8"/>
+      <c r="AB19" s="8">
+        <f t="shared" ref="AB19:AH19" si="29">AB17/AB18</f>
+        <v>-9.1472868217054248E-2</v>
+      </c>
+      <c r="AC19" s="8">
         <f t="shared" si="29"/>
-        <v>-2.2022362739049965</v>
-      </c>
-      <c r="X19" s="8">
-        <f t="shared" ref="X19:AD19" si="30">X17/X18</f>
-        <v>-9.1472868217054248E-2</v>
-      </c>
-      <c r="Y19" s="8">
+        <v>-0.23727527626587497</v>
+      </c>
+      <c r="AD19" s="8">
+        <f t="shared" si="29"/>
+        <v>-0.85096486887679379</v>
+      </c>
+      <c r="AE19" s="8">
+        <f t="shared" si="29"/>
+        <v>-0.43031502556490187</v>
+      </c>
+      <c r="AF19" s="8">
+        <f t="shared" si="29"/>
+        <v>-0.93297047666171873</v>
+      </c>
+      <c r="AG19" s="8">
+        <f t="shared" si="29"/>
+        <v>-0.89526636978393548</v>
+      </c>
+      <c r="AH19" s="8">
+        <f t="shared" si="29"/>
+        <v>-8.301846153846153</v>
+      </c>
+      <c r="AI19" s="8">
+        <f t="shared" ref="AI19:AR19" si="30">AI17/AI18</f>
+        <v>-8.1748646153846156</v>
+      </c>
+      <c r="AJ19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.23727527626587497</v>
-      </c>
-      <c r="Z19" s="8">
+        <v>-6.9909612615384633</v>
+      </c>
+      <c r="AK19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.85096486887679379</v>
-      </c>
-      <c r="AA19" s="8">
+        <v>-4.8922257510769231</v>
+      </c>
+      <c r="AL19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.43031502556490187</v>
-      </c>
-      <c r="AB19" s="8">
+        <v>-2.6955597739723078</v>
+      </c>
+      <c r="AM19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.93297047666171873</v>
-      </c>
-      <c r="AC19" s="8">
+        <v>-1.2747824083274153</v>
+      </c>
+      <c r="AN19" s="8">
         <f t="shared" si="30"/>
-        <v>-0.89526636978393548</v>
-      </c>
-      <c r="AD19" s="8">
+        <v>0.5365383475431561</v>
+      </c>
+      <c r="AO19" s="8">
         <f t="shared" si="30"/>
-        <v>-6.4999845774213449</v>
-      </c>
-      <c r="AE19" s="8">
-        <f t="shared" ref="AE19:AN19" si="31">AE17/AE18</f>
-        <v>-5.9301303207896368</v>
-      </c>
-      <c r="AF19" s="8">
-        <f t="shared" si="31"/>
-        <v>-4.5665001388032085</v>
-      </c>
-      <c r="AG19" s="8">
-        <f t="shared" si="31"/>
-        <v>-3.0332793790869848</v>
-      </c>
-      <c r="AH19" s="8">
-        <f t="shared" si="31"/>
-        <v>-1.9412540073935847</v>
-      </c>
-      <c r="AI19" s="8">
-        <f t="shared" si="31"/>
-        <v>-0.98880570219454</v>
-      </c>
-      <c r="AJ19" s="8">
-        <f t="shared" si="31"/>
-        <v>-9.8348286073944011E-2</v>
-      </c>
-      <c r="AK19" s="8">
-        <f t="shared" si="31"/>
-        <v>0.80319692518121688</v>
-      </c>
-      <c r="AL19" s="8">
-        <f t="shared" si="31"/>
-        <v>1.868539198125174</v>
-      </c>
-      <c r="AM19" s="8">
-        <f t="shared" si="31"/>
-        <v>2.8109918037097987</v>
-      </c>
-      <c r="AN19" s="8">
-        <f t="shared" si="31"/>
-        <v>3.8859612946185611</v>
+        <v>2.1132183372826252</v>
+      </c>
+      <c r="AP19" s="8">
+        <f t="shared" si="30"/>
+        <v>3.4303145205426921</v>
+      </c>
+      <c r="AQ19" s="8">
+        <f t="shared" si="30"/>
+        <v>4.9837326728787206</v>
+      </c>
+      <c r="AR19" s="8">
+        <f t="shared" si="30"/>
+        <v>6.4122760079592265</v>
       </c>
     </row>
-    <row r="21" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>63</v>
       </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="10">
-        <f t="shared" ref="R21" si="32">R3/N3-1</f>
+        <f t="shared" ref="R21" si="31">R3/N3-1</f>
         <v>0.78719723183390999</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" ref="S21" si="33">S3/O3-1</f>
+        <f t="shared" ref="S21" si="32">S3/O3-1</f>
         <v>0.58057956278596845</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" ref="T21" si="34">T3/P3-1</f>
+        <f t="shared" ref="T21" si="33">T3/P3-1</f>
         <v>0.3822055137844611</v>
       </c>
-      <c r="U21" s="15">
-        <f t="shared" ref="U21" si="35">U3/Q3-1</f>
-        <v>0.5</v>
-      </c>
-      <c r="V21" s="15">
-        <f t="shared" ref="V21" si="36">V3/R3-1</f>
-        <v>0.7</v>
-      </c>
-      <c r="AA21" s="10">
-        <f t="shared" ref="AA21:AA22" si="37">AA3/Z3-1</f>
+      <c r="U21" s="10">
+        <f t="shared" ref="U21" si="34">U3/Q3-1</f>
+        <v>0.46637900035958291</v>
+      </c>
+      <c r="V21" s="10">
+        <f t="shared" ref="V21" si="35">V3/R3-1</f>
+        <v>0.72474991932881583</v>
+      </c>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AE21" s="10">
+        <f t="shared" ref="AE21:AE22" si="36">AE3/AD3-1</f>
         <v>13.563333333333333</v>
       </c>
-      <c r="AB21" s="10">
-        <f t="shared" ref="AB21:AB22" si="38">AB3/AA3-1</f>
+      <c r="AF21" s="10">
+        <f t="shared" ref="AF21:AF22" si="37">AF3/AE3-1</f>
         <v>0.37354085603112841</v>
       </c>
-      <c r="AC21" s="10">
-        <f t="shared" ref="AC21" si="39">AC3/AB3-1</f>
+      <c r="AG21" s="10">
+        <f t="shared" ref="AG21" si="38">AG3/AF3-1</f>
         <v>0.70654890851524743</v>
       </c>
-      <c r="AD21" s="10">
-        <f t="shared" ref="AD21" si="40">AD3/AC3-1</f>
-        <v>0.54846206425153787</v>
+      <c r="AH21" s="10">
+        <f t="shared" ref="AH21" si="39">AH3/AG3-1</f>
+        <v>0.54682159945317843</v>
       </c>
     </row>
-    <row r="22" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>61</v>
       </c>
       <c r="O22" s="10"/>
       <c r="P22" s="10"/>
       <c r="Q22" s="10">
-        <f t="shared" ref="Q22" si="41">Q4/M4-1</f>
+        <f t="shared" ref="Q22" si="40">Q4/M4-1</f>
         <v>0.1645161290322581</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" ref="R22" si="42">R4/N4-1</f>
+        <f t="shared" ref="R22" si="41">R4/N4-1</f>
         <v>0.95271049596309121</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" ref="S22" si="43">S4/O4-1</f>
+        <f t="shared" ref="S22" si="42">S4/O4-1</f>
         <v>0.28009259259259256</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22" si="44">T4/P4-1</f>
+        <f t="shared" ref="T22" si="43">T4/P4-1</f>
         <v>0.83080568720379144</v>
       </c>
-      <c r="U22" s="15">
-        <f t="shared" ref="U22" si="45">U4/Q4-1</f>
-        <v>1.5</v>
-      </c>
-      <c r="V22" s="15">
-        <f t="shared" ref="V22" si="46">V4/R4-1</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="AA22" s="10">
+      <c r="U22" s="10">
+        <f t="shared" ref="U22" si="44">U4/Q4-1</f>
+        <v>1.155678670360111</v>
+      </c>
+      <c r="V22" s="10">
+        <f t="shared" ref="V22" si="45">V4/R4-1</f>
+        <v>1.3254577672770229</v>
+      </c>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
+      <c r="AE22" s="10">
+        <f t="shared" si="36"/>
+        <v>16.95</v>
+      </c>
+      <c r="AF22" s="10">
         <f t="shared" si="37"/>
-        <v>16.95</v>
-      </c>
-      <c r="AB22" s="10">
-        <f t="shared" si="38"/>
         <v>0.17381615598885802</v>
       </c>
-      <c r="AC22" s="10">
-        <f t="shared" ref="AC22:AD22" si="47">AC4/AB4-1</f>
+      <c r="AG22" s="10">
+        <f t="shared" ref="AG22:AH22" si="46">AG4/AF4-1</f>
         <v>7.130991931656383E-2</v>
       </c>
-      <c r="AD22" s="10">
-        <f t="shared" si="47"/>
-        <v>0.99764093476575488</v>
+      <c r="AH22" s="10">
+        <f t="shared" si="46"/>
+        <v>0.97585557647580012</v>
       </c>
     </row>
-    <row r="23" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>64</v>
       </c>
@@ -3081,55 +3176,59 @@
         <v>1</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" ref="O23:V23" si="48">O3/O4</f>
+        <f t="shared" ref="O23:V23" si="47">O3/O4</f>
         <v>1.1383101851851851</v>
       </c>
       <c r="P23" s="10">
+        <f t="shared" si="47"/>
+        <v>1.1345971563981043</v>
+      </c>
+      <c r="Q23" s="10">
+        <f t="shared" si="47"/>
+        <v>1.5407202216066482</v>
+      </c>
+      <c r="R23" s="10">
+        <f t="shared" si="47"/>
+        <v>0.91523922031896043</v>
+      </c>
+      <c r="S23" s="10">
+        <f t="shared" si="47"/>
+        <v>1.4055153707052441</v>
+      </c>
+      <c r="T23" s="10">
+        <f t="shared" si="47"/>
+        <v>0.85658814392958837</v>
+      </c>
+      <c r="U23" s="10">
+        <f t="shared" si="47"/>
+        <v>1.0480596247751222</v>
+      </c>
+      <c r="V23" s="10">
+        <f t="shared" si="47"/>
+        <v>0.67881635763271531</v>
+      </c>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AE23" s="10">
+        <f t="shared" ref="AE23:AH23" si="48">AE3/AE4</f>
+        <v>0.60849582172701955</v>
+      </c>
+      <c r="AF23" s="10">
         <f t="shared" si="48"/>
-        <v>1.1345971563981043</v>
-      </c>
-      <c r="Q23" s="10">
+        <v>0.71203132415756998</v>
+      </c>
+      <c r="AG23" s="10">
         <f t="shared" si="48"/>
-        <v>1.5407202216066482</v>
-      </c>
-      <c r="R23" s="10">
+        <v>1.134234134455643</v>
+      </c>
+      <c r="AH23" s="10">
         <f t="shared" si="48"/>
-        <v>0.91523922031896043</v>
-      </c>
-      <c r="S23" s="10">
-        <f t="shared" si="48"/>
-        <v>1.4055153707052441</v>
-      </c>
-      <c r="T23" s="10">
-        <f t="shared" si="48"/>
-        <v>0.85658814392958837</v>
-      </c>
-      <c r="U23" s="15">
-        <f t="shared" si="48"/>
-        <v>0.92443213296398896</v>
-      </c>
-      <c r="V23" s="15">
-        <f t="shared" si="48"/>
-        <v>0.70723030661010577</v>
-      </c>
-      <c r="AA23" s="10">
-        <f t="shared" ref="AA23:AD23" si="49">AA3/AA4</f>
-        <v>0.60849582172701955</v>
-      </c>
-      <c r="AB23" s="10">
-        <f t="shared" si="49"/>
-        <v>0.71203132415756998</v>
-      </c>
-      <c r="AC23" s="10">
-        <f t="shared" si="49"/>
-        <v>1.134234134455643</v>
-      </c>
-      <c r="AD23" s="10">
-        <f t="shared" si="49"/>
-        <v>0.87919630531083837</v>
+        <v>0.88794843049327354</v>
       </c>
     </row>
-    <row r="24" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>65</v>
       </c>
@@ -3138,150 +3237,158 @@
         <v>90657.43944636677</v>
       </c>
       <c r="O24" s="6">
-        <f t="shared" ref="O24:V24" si="50">(O6/O3)*1000000</f>
+        <f t="shared" ref="O24:V24" si="49">(O6/O3)*1000000</f>
         <v>87798.67819013726</v>
       </c>
       <c r="P24" s="6">
+        <f t="shared" si="49"/>
+        <v>83792.815371762743</v>
+      </c>
+      <c r="Q24" s="6">
+        <f t="shared" si="49"/>
+        <v>71916.5767709457</v>
+      </c>
+      <c r="R24" s="6">
+        <f t="shared" si="49"/>
+        <v>75669.570829299773</v>
+      </c>
+      <c r="S24" s="6">
+        <f t="shared" si="49"/>
+        <v>75587.005467996147</v>
+      </c>
+      <c r="T24" s="6">
+        <f t="shared" si="49"/>
+        <v>78392.263523723159</v>
+      </c>
+      <c r="U24" s="6">
+        <f t="shared" si="49"/>
+        <v>82540.461010299172</v>
+      </c>
+      <c r="V24" s="6">
+        <f t="shared" si="49"/>
+        <v>97792.329279700658</v>
+      </c>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AE24" s="6">
+        <f t="shared" ref="AE24:AH24" si="50">(AE6/AE3)*1000000</f>
+        <v>139208.05676356147</v>
+      </c>
+      <c r="AF24" s="6">
         <f t="shared" si="50"/>
-        <v>83792.815371762743</v>
-      </c>
-      <c r="Q24" s="6">
+        <v>99200.133311114812</v>
+      </c>
+      <c r="AG24" s="6">
         <f t="shared" si="50"/>
-        <v>71916.5767709457</v>
-      </c>
-      <c r="R24" s="6">
+        <v>78879.015721120973</v>
+      </c>
+      <c r="AH24" s="6">
         <f t="shared" si="50"/>
-        <v>75669.570829299773</v>
-      </c>
-      <c r="S24" s="6">
-        <f t="shared" si="50"/>
-        <v>75587.005467996147</v>
-      </c>
-      <c r="T24" s="6">
-        <f t="shared" si="50"/>
-        <v>78392.263523723159</v>
-      </c>
-      <c r="U24" s="14">
-        <f t="shared" si="50"/>
-        <v>80690.399137001092</v>
-      </c>
-      <c r="V24" s="14">
-        <f t="shared" si="50"/>
-        <v>73443.995216673298</v>
-      </c>
-      <c r="AA24" s="6">
-        <f t="shared" ref="AA24:AD24" si="51">(AA6/AA3)*1000000</f>
-        <v>139208.05676356147</v>
-      </c>
-      <c r="AB24" s="6">
-        <f t="shared" si="51"/>
-        <v>99200.133311114812</v>
-      </c>
-      <c r="AC24" s="6">
-        <f t="shared" si="51"/>
-        <v>78879.015721120973</v>
-      </c>
-      <c r="AD24" s="6">
-        <f t="shared" si="51"/>
-        <v>76802.898258270376</v>
+        <v>85455.463670222845</v>
       </c>
     </row>
-    <row r="26" spans="2:136" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:140" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2" t="s">
         <v>44</v>
       </c>
       <c r="M26" s="11"/>
       <c r="Q26" s="11">
-        <f t="shared" ref="Q26:V26" si="52">Q6/M6-1</f>
+        <f t="shared" ref="Q26:V26" si="51">Q6/M6-1</f>
         <v>0.45137880986937584</v>
       </c>
       <c r="R26" s="11">
+        <f t="shared" si="51"/>
+        <v>0.49173027989821905</v>
+      </c>
+      <c r="S26" s="11">
+        <f t="shared" si="51"/>
+        <v>0.36074116965836711</v>
+      </c>
+      <c r="T26" s="11">
+        <f t="shared" si="51"/>
+        <v>0.29312063808574274</v>
+      </c>
+      <c r="U26" s="11">
+        <f t="shared" si="51"/>
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="V26" s="11">
+        <f t="shared" si="51"/>
+        <v>1.2289978678038382</v>
+      </c>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
+      <c r="AB26" s="11"/>
+      <c r="AC26" s="11">
+        <f t="shared" ref="AC26:AE26" si="52">AC6/AB6-1</f>
+        <v>-0.13043478260869557</v>
+      </c>
+      <c r="AD26" s="11">
         <f t="shared" si="52"/>
-        <v>0.49173027989821905</v>
-      </c>
-      <c r="S26" s="11">
+        <v>5.7750000000000004</v>
+      </c>
+      <c r="AE26" s="11">
         <f t="shared" si="52"/>
-        <v>0.36074116965836711</v>
-      </c>
-      <c r="T26" s="11">
-        <f t="shared" si="52"/>
-        <v>0.29312063808574274</v>
-      </c>
-      <c r="U26" s="11">
-        <f t="shared" si="52"/>
-        <v>0.68300000000000005</v>
-      </c>
-      <c r="V26" s="11">
-        <f t="shared" si="52"/>
-        <v>0.64999999999999991</v>
-      </c>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="11">
-        <f t="shared" ref="Y26:AA26" si="53">Y6/X6-1</f>
-        <v>-0.13043478260869557</v>
-      </c>
-      <c r="Z26" s="11">
-        <f t="shared" si="53"/>
-        <v>5.7750000000000004</v>
-      </c>
-      <c r="AA26" s="11">
-        <f t="shared" si="53"/>
         <v>21.44280442804428</v>
       </c>
-      <c r="AB26" s="11">
-        <f t="shared" ref="AB26" si="54">AB6/AA6-1</f>
+      <c r="AF26" s="11">
+        <f t="shared" ref="AF26" si="53">AF6/AE6-1</f>
         <v>-2.1210128247287185E-2</v>
       </c>
-      <c r="AC26" s="11">
-        <f t="shared" ref="AC26:AN26" si="55">AC6/AB6-1</f>
+      <c r="AG26" s="11">
+        <f t="shared" ref="AG26:AR26" si="54">AG6/AF6-1</f>
         <v>0.35696287586091047</v>
       </c>
-      <c r="AD26" s="11">
-        <f t="shared" si="55"/>
-        <v>0.5077061153750928</v>
-      </c>
-      <c r="AE26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AH26" s="11">
+        <f t="shared" si="54"/>
+        <v>0.67578608566476861</v>
+      </c>
+      <c r="AI26" s="11">
+        <f t="shared" si="54"/>
         <v>0.5</v>
       </c>
-      <c r="AF26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AJ26" s="11">
+        <f t="shared" si="54"/>
         <v>0.39999999999999991</v>
       </c>
-      <c r="AG26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AK26" s="11">
+        <f t="shared" si="54"/>
         <v>0.35000000000000009</v>
       </c>
-      <c r="AH26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AL26" s="11">
+        <f t="shared" si="54"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="AI26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AM26" s="11">
+        <f t="shared" si="54"/>
         <v>0.25</v>
       </c>
-      <c r="AJ26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AN26" s="11">
+        <f t="shared" si="54"/>
         <v>0.19999999999999996</v>
       </c>
-      <c r="AK26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AO26" s="11">
+        <f t="shared" si="54"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AL26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AP26" s="11">
+        <f t="shared" si="54"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AM26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AQ26" s="11">
+        <f t="shared" si="54"/>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AN26" s="11">
-        <f t="shared" si="55"/>
+      <c r="AR26" s="11">
+        <f t="shared" si="54"/>
         <v>0.14999999999999991</v>
       </c>
     </row>
-    <row r="27" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>45</v>
       </c>
@@ -3294,7 +3401,7 @@
         <v>-1.608142493638677</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" ref="O27" si="56">O8/O6</f>
+        <f t="shared" ref="O27" si="55">O8/O6</f>
         <v>-1.3439490445859874</v>
       </c>
       <c r="P27" s="10">
@@ -3314,93 +3421,97 @@
         <v>-0.9727659574468086</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" ref="T27:V27" si="57">T8/T6</f>
+        <f t="shared" ref="T27:V27" si="56">T8/T6</f>
         <v>-1.0501156515034695</v>
       </c>
       <c r="U27" s="10">
+        <f t="shared" si="56"/>
+        <v>-0.9910873440285205</v>
+      </c>
+      <c r="V27" s="10">
+        <f t="shared" si="56"/>
+        <v>-0.80715515592117837</v>
+      </c>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
+      <c r="AB27" s="10">
+        <f t="shared" ref="AB27:AE27" si="57">AB8/AB6</f>
+        <v>0.15217391304347822</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="57"/>
-        <v>-0.9910873440285205</v>
-      </c>
-      <c r="V27" s="10">
+        <v>0.22499999999999998</v>
+      </c>
+      <c r="AD27" s="10">
         <f t="shared" si="57"/>
-        <v>-1</v>
-      </c>
-      <c r="X27" s="10">
-        <f t="shared" ref="X27:AA27" si="58">X8/X6</f>
-        <v>0.15217391304347822</v>
-      </c>
-      <c r="Y27" s="10">
-        <f t="shared" si="58"/>
-        <v>0.22499999999999998</v>
-      </c>
-      <c r="Z27" s="10">
-        <f t="shared" si="58"/>
         <v>-4.7158671586715872</v>
       </c>
-      <c r="AA27" s="10">
-        <f t="shared" si="58"/>
+      <c r="AE27" s="10">
+        <f t="shared" si="57"/>
         <v>-1.7065110161131203</v>
       </c>
-      <c r="AB27" s="10">
-        <f t="shared" ref="AB27" si="59">AB8/AB6</f>
+      <c r="AF27" s="10">
+        <f t="shared" ref="AF27" si="58">AF8/AF6</f>
         <v>-2.2523097597849824</v>
       </c>
-      <c r="AC27" s="10">
-        <f>AC8/AC6</f>
+      <c r="AG27" s="10">
+        <f>AG8/AG6</f>
         <v>-1.1427333498390693</v>
       </c>
-      <c r="AD27" s="10">
-        <f t="shared" ref="AD27:AN27" si="60">AD8/AD6</f>
+      <c r="AH27" s="10">
+        <f t="shared" ref="AH27:AR27" si="59">AH8/AH6</f>
+        <v>-0.92819679397207633</v>
+      </c>
+      <c r="AI27" s="10">
+        <f t="shared" si="59"/>
         <v>-0.6</v>
       </c>
-      <c r="AE27" s="10">
-        <f t="shared" si="60"/>
+      <c r="AJ27" s="10">
+        <f t="shared" si="59"/>
         <v>-0.3</v>
       </c>
-      <c r="AF27" s="10">
-        <f t="shared" si="60"/>
+      <c r="AK27" s="10">
+        <f t="shared" si="59"/>
         <v>-0.05</v>
       </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="60"/>
+      <c r="AL27" s="10">
+        <f t="shared" si="59"/>
         <v>0.1</v>
       </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="60"/>
+      <c r="AM27" s="10">
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="60"/>
-        <v>0.17</v>
-      </c>
-      <c r="AJ27" s="10">
-        <f t="shared" si="60"/>
-        <v>0.18</v>
-      </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="60"/>
-        <v>0.18999999999999997</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="60"/>
+      <c r="AN27" s="10">
+        <f t="shared" si="59"/>
         <v>0.2</v>
       </c>
-      <c r="AM27" s="10">
-        <f t="shared" si="60"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AN27" s="10">
-        <f t="shared" si="60"/>
-        <v>0.2</v>
-      </c>
-      <c r="AP27" s="1" t="s">
+      <c r="AO27" s="10">
+        <f t="shared" si="59"/>
+        <v>0.23</v>
+      </c>
+      <c r="AP27" s="10">
+        <f t="shared" si="59"/>
+        <v>0.24</v>
+      </c>
+      <c r="AQ27" s="10">
+        <f t="shared" si="59"/>
+        <v>0.25</v>
+      </c>
+      <c r="AR27" s="10">
+        <f t="shared" si="59"/>
+        <v>0.25</v>
+      </c>
+      <c r="AT27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AQ27" s="10">
+      <c r="AU27" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="28" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>46</v>
       </c>
@@ -3409,102 +3520,106 @@
       <c r="O28" s="10"/>
       <c r="P28" s="10"/>
       <c r="Q28" s="10">
-        <f t="shared" ref="Q28:S29" si="61">Q9/M9-1</f>
+        <f t="shared" ref="Q28:S29" si="60">Q9/M9-1</f>
         <v>0.40554592720970528</v>
       </c>
       <c r="R28" s="10">
+        <f t="shared" si="60"/>
+        <v>0.15349794238683123</v>
+      </c>
+      <c r="S28" s="10">
+        <f t="shared" si="60"/>
+        <v>-0.11735769501054127</v>
+      </c>
+      <c r="T28" s="10">
+        <f t="shared" ref="T28:V28" si="61">T9/P9-1</f>
+        <v>-4.6657381615598847E-2</v>
+      </c>
+      <c r="U28" s="10">
         <f t="shared" si="61"/>
-        <v>0.15349794238683123</v>
-      </c>
-      <c r="S28" s="10">
+        <v>2.7743526510481953E-3</v>
+      </c>
+      <c r="V28" s="10">
         <f t="shared" si="61"/>
-        <v>-0.11735769501054127</v>
-      </c>
-      <c r="T28" s="10">
-        <f t="shared" ref="T28:V28" si="62">T9/P9-1</f>
-        <v>-4.6657381615598847E-2</v>
-      </c>
-      <c r="U28" s="10">
+        <v>0.28790581519800207</v>
+      </c>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
+      <c r="AB28" s="10"/>
+      <c r="AC28" s="10">
+        <f t="shared" ref="AC28:AE28" si="62">AC9/AB9-1</f>
+        <v>1.3210717529518621</v>
+      </c>
+      <c r="AD28" s="10">
         <f t="shared" si="62"/>
-        <v>2.7743526510481953E-3</v>
-      </c>
-      <c r="V28" s="10">
+        <v>0.46781451770690663</v>
+      </c>
+      <c r="AE28" s="10">
         <f t="shared" si="62"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="X28" s="10"/>
-      <c r="Y28" s="10">
-        <f t="shared" ref="Y28:AA28" si="63">Y9/X9-1</f>
-        <v>1.3210717529518621</v>
-      </c>
-      <c r="Z28" s="10">
-        <f t="shared" si="63"/>
-        <v>0.46781451770690663</v>
-      </c>
-      <c r="AA28" s="10">
-        <f t="shared" si="63"/>
         <v>9.5041322314049603E-2</v>
       </c>
-      <c r="AB28" s="10">
-        <f t="shared" ref="AB28" si="64">AB9/AA9-1</f>
+      <c r="AF28" s="10">
+        <f t="shared" ref="AF28" si="63">AF9/AE9-1</f>
         <v>0.1405964698721851</v>
       </c>
-      <c r="AC28" s="10">
-        <f>AC9/AB9-1</f>
+      <c r="AG28" s="10">
+        <f>AG9/AF9-1</f>
         <v>0.25560298826040562</v>
       </c>
-      <c r="AD28" s="10">
-        <f t="shared" ref="AD28:AN28" si="65">AD9/AC9-1</f>
-        <v>8.6357841053972262E-3</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AH28" s="10">
+        <f t="shared" ref="AH28:AR28" si="64">AH9/AG9-1</f>
+        <v>2.9579260518487027E-2</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" si="64"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AF28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AJ28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AK28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AL28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AM28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AN28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AO28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AP28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AQ28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN28" s="10">
-        <f t="shared" si="65"/>
+      <c r="AR28" s="10">
+        <f t="shared" si="64"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP28" s="1" t="s">
+      <c r="AT28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AQ28" s="10">
+      <c r="AU28" s="10">
         <v>0.09</v>
       </c>
     </row>
-    <row r="29" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>47</v>
       </c>
@@ -3513,103 +3628,107 @@
       <c r="O29" s="10"/>
       <c r="P29" s="10"/>
       <c r="Q29" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>0.23141802846599901</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>1.2033195020746845E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-4.6904315196998336E-3</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" ref="T29:V29" si="66">T10/P10-1</f>
+        <f t="shared" ref="T29:V29" si="65">T10/P10-1</f>
         <v>0.22216936251189345</v>
       </c>
       <c r="U29" s="10">
+        <f t="shared" si="65"/>
+        <v>0.21190068493150704</v>
+      </c>
+      <c r="V29" s="10">
+        <f t="shared" si="65"/>
+        <v>0.15539155391553927</v>
+      </c>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
+      <c r="AB29" s="10"/>
+      <c r="AC29" s="10">
+        <f t="shared" ref="AC29:AE29" si="66">AC10/AB10-1</f>
+        <v>1.3177083333333335</v>
+      </c>
+      <c r="AD29" s="10">
         <f t="shared" si="66"/>
-        <v>0.21190068493150704</v>
-      </c>
-      <c r="V29" s="10">
+        <v>6.3314606741573032</v>
+      </c>
+      <c r="AE29" s="10">
         <f t="shared" si="66"/>
-        <v>0.19999999999999996</v>
-      </c>
-      <c r="X29" s="10"/>
-      <c r="Y29" s="10">
-        <f t="shared" ref="Y29:AA29" si="67">Y10/X10-1</f>
-        <v>1.3177083333333335</v>
-      </c>
-      <c r="Z29" s="10">
-        <f t="shared" si="67"/>
-        <v>6.3314606741573032</v>
-      </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="67"/>
         <v>0.12582375478927199</v>
       </c>
-      <c r="AB29" s="10">
-        <f t="shared" ref="AB29" si="68">AB10/AA10-1</f>
+      <c r="AF29" s="10">
+        <f t="shared" ref="AF29" si="67">AF10/AE10-1</f>
         <v>8.5216444323441332E-2</v>
       </c>
-      <c r="AC29" s="10">
-        <f>AC10/AB10-1</f>
+      <c r="AG29" s="10">
+        <f>AG10/AF10-1</f>
         <v>0.13020572002007014</v>
       </c>
-      <c r="AD29" s="10">
-        <f t="shared" ref="AD29:AN29" si="69">AD10/AC10-1</f>
-        <v>0.15968923418423975</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AH29" s="10">
+        <f t="shared" ref="AH29:AR29" si="68">AH10/AG10-1</f>
+        <v>0.14761376248612645</v>
+      </c>
+      <c r="AI29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AJ29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AK29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AL29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AM29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AJ29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AN29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AO29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AL29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AP29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AM29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AQ29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AN29" s="10">
-        <f t="shared" si="69"/>
+      <c r="AR29" s="10">
+        <f t="shared" si="68"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AP29" s="1" t="s">
+      <c r="AT29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AQ29" s="6">
-        <f>NPV(AQ28,AD17:EF17)</f>
-        <v>106.79980947248835</v>
+      <c r="AU29" s="6">
+        <f>NPV(AU28,AH17:EJ17)</f>
+        <v>2031.0200963842444</v>
       </c>
     </row>
-    <row r="30" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>59</v>
       </c>
@@ -3618,118 +3737,122 @@
         <v>1.3766328011611029</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" ref="N30:P30" si="70">N10/N6</f>
+        <f t="shared" ref="N30:P30" si="69">N10/N6</f>
         <v>1.5330788804071247</v>
       </c>
       <c r="O30" s="10">
+        <f t="shared" si="69"/>
+        <v>1.2345107122177186</v>
+      </c>
+      <c r="P30" s="10">
+        <f t="shared" si="69"/>
+        <v>1.0478564307078764</v>
+      </c>
+      <c r="Q30" s="10">
+        <f t="shared" ref="Q30:AR30" si="70">Q10/Q6</f>
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="R30" s="10">
         <f t="shared" si="70"/>
-        <v>1.2345107122177186</v>
-      </c>
-      <c r="P30" s="10">
+        <v>1.0400852878464819</v>
+      </c>
+      <c r="S30" s="10">
         <f t="shared" si="70"/>
-        <v>1.0478564307078764</v>
-      </c>
-      <c r="Q30" s="10">
-        <f t="shared" ref="Q30:AN30" si="71">Q10/Q6</f>
-        <v>1.1679999999999999</v>
-      </c>
-      <c r="R30" s="10">
-        <f t="shared" si="71"/>
-        <v>1.0400852878464819</v>
-      </c>
-      <c r="S30" s="10">
-        <f t="shared" si="71"/>
         <v>0.90297872340425522</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>0.99036237471087119</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>0.8410576351752822</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.75642566388835053</v>
-      </c>
-      <c r="X30" s="10">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
+        <v>0.53912378037114972</v>
+      </c>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
+      <c r="AB30" s="10">
+        <f t="shared" si="70"/>
         <v>8.3478260869565215</v>
       </c>
-      <c r="Y30" s="10">
-        <f t="shared" si="71"/>
+      <c r="AC30" s="10">
+        <f t="shared" si="70"/>
         <v>22.25</v>
       </c>
-      <c r="Z30" s="10">
-        <f t="shared" si="71"/>
+      <c r="AD30" s="10">
+        <f t="shared" si="70"/>
         <v>24.077490774907748</v>
       </c>
-      <c r="AA30" s="10">
-        <f t="shared" si="71"/>
+      <c r="AE30" s="10">
+        <f t="shared" si="70"/>
         <v>1.20782637290365</v>
       </c>
-      <c r="AB30" s="10">
-        <f t="shared" si="71"/>
+      <c r="AF30" s="10">
+        <f t="shared" si="70"/>
         <v>1.3391567277003193</v>
       </c>
-      <c r="AC30" s="10">
-        <f t="shared" si="71"/>
+      <c r="AG30" s="10">
+        <f t="shared" si="70"/>
         <v>1.1153750928447637</v>
       </c>
-      <c r="AD30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.85791818051193636</v>
-      </c>
-      <c r="AE30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.57766490821137062</v>
-      </c>
-      <c r="AF30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.41674396949534603</v>
-      </c>
-      <c r="AG30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.31178622902985148</v>
-      </c>
       <c r="AH30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.24223391640011532</v>
+        <f t="shared" si="70"/>
+        <v>0.76383245918593479</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.19572500445129321</v>
+        <f t="shared" si="70"/>
+        <v>0.51431385585186273</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.16473521207983846</v>
+        <f t="shared" si="70"/>
+        <v>0.37104071029312963</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.14468049060924942</v>
+        <f t="shared" si="70"/>
+        <v>0.27759342029337841</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.12706721349160169</v>
+        <f t="shared" si="70"/>
+        <v>0.21566873422793248</v>
       </c>
       <c r="AM30" s="10">
-        <f t="shared" si="71"/>
-        <v>0.11159816141436324</v>
+        <f t="shared" si="70"/>
+        <v>0.17426033725616946</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" si="71"/>
-        <v>9.8012298285658148E-2</v>
-      </c>
-      <c r="AP30" s="1" t="s">
+        <f t="shared" si="70"/>
+        <v>0.14666911719060929</v>
+      </c>
+      <c r="AO30" s="10">
+        <f t="shared" si="70"/>
+        <v>0.12881374640218729</v>
+      </c>
+      <c r="AP30" s="10">
+        <f t="shared" si="70"/>
+        <v>0.11313207292713841</v>
+      </c>
+      <c r="AQ30" s="10">
+        <f t="shared" si="70"/>
+        <v>9.9359472744704191E-2</v>
+      </c>
+      <c r="AR30" s="10">
+        <f t="shared" si="70"/>
+        <v>8.7263536932305416E-2</v>
+      </c>
+      <c r="AT30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ30" s="6">
+      <c r="AU30" s="6">
         <f>Main!D8</f>
-        <v>952.79999999999973</v>
+        <v>-577.19999999999982</v>
       </c>
     </row>
-    <row r="31" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>48</v>
       </c>
@@ -3742,7 +3865,7 @@
         <v>-4.6870229007633588</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" ref="O31" si="72">O13/O6</f>
+        <f t="shared" ref="O31" si="71">O13/O6</f>
         <v>-4.2264041690793288</v>
       </c>
       <c r="P31" s="10">
@@ -3762,94 +3885,98 @@
         <v>-2.9446808510638296</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" ref="T31:V31" si="73">T13/T6</f>
+        <f t="shared" ref="T31:V31" si="72">T13/T6</f>
         <v>-3.0959907478797226</v>
       </c>
       <c r="U31" s="10">
+        <f t="shared" si="72"/>
+        <v>-2.7985739750445635</v>
+      </c>
+      <c r="V31" s="10">
+        <f t="shared" si="72"/>
+        <v>-2.0369236655825516</v>
+      </c>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
+      <c r="AB31" s="10">
+        <f t="shared" ref="AB31:AE31" si="73">AB13/AB6</f>
+        <v>-56.065217391304344</v>
+      </c>
+      <c r="AC31" s="10">
         <f t="shared" si="73"/>
-        <v>-2.7985739750445635</v>
-      </c>
-      <c r="V31" s="10">
+        <v>-149.80000000000001</v>
+      </c>
+      <c r="AD31" s="10">
         <f t="shared" si="73"/>
-        <v>-2.6257414227563483</v>
-      </c>
-      <c r="X31" s="10">
-        <f t="shared" ref="X31:AA31" si="74">X13/X6</f>
-        <v>-56.065217391304344</v>
-      </c>
-      <c r="Y31" s="10">
-        <f t="shared" si="74"/>
-        <v>-149.80000000000001</v>
-      </c>
-      <c r="Z31" s="10">
-        <f t="shared" si="74"/>
         <v>-56.476014760147599</v>
       </c>
-      <c r="AA31" s="10">
-        <f t="shared" si="74"/>
+      <c r="AE31" s="10">
+        <f t="shared" si="73"/>
         <v>-4.2650443932916797</v>
       </c>
-      <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="75">AB13/AB6</f>
+      <c r="AF31" s="10">
+        <f t="shared" ref="AF31" si="74">AF13/AF6</f>
         <v>-5.2066185116747858</v>
       </c>
-      <c r="AC31" s="10">
-        <f>AC13/AC6</f>
+      <c r="AG31" s="10">
+        <f>AG13/AG6</f>
         <v>-3.7396632829908403</v>
       </c>
-      <c r="AD31" s="10">
-        <f t="shared" ref="AD31:AN31" si="76">AD13/AD6</f>
-        <v>-2.4322474700823125</v>
-      </c>
-      <c r="AE31" s="10">
-        <f t="shared" si="76"/>
-        <v>-1.5402088251192263</v>
-      </c>
-      <c r="AF31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.94472208097887056</v>
-      </c>
-      <c r="AG31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.56938466799159937</v>
-      </c>
       <c r="AH31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.37006039590116557</v>
+        <f t="shared" ref="AH31:AR31" si="75">AH13/AH6</f>
+        <v>-2.5868360788948808</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.25020879988814176</v>
+        <f t="shared" si="75"/>
+        <v>-1.7227824973529338</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.17367573990585275</v>
+        <f t="shared" si="75"/>
+        <v>-1.110007373090331</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" si="76"/>
-        <v>-0.12061956287383591</v>
+        <f t="shared" si="75"/>
+        <v>-0.65600551616387714</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" si="76"/>
-        <v>-7.2805007393542884E-2</v>
+        <f t="shared" si="75"/>
+        <v>-0.37081967025039692</v>
       </c>
       <c r="AM31" s="10">
-        <f t="shared" si="76"/>
-        <v>-3.9593963015198561E-2</v>
+        <f t="shared" si="75"/>
+        <v>-0.23042229356232072</v>
       </c>
       <c r="AN31" s="10">
-        <f t="shared" si="76"/>
-        <v>-1.0426002300304799E-2</v>
-      </c>
-      <c r="AP31" s="1" t="s">
+        <f t="shared" si="75"/>
+        <v>-0.12018876374828663</v>
+      </c>
+      <c r="AO31" s="10">
+        <f t="shared" si="75"/>
+        <v>-5.12092620745822E-2</v>
+      </c>
+      <c r="AP31" s="10">
+        <f t="shared" si="75"/>
+        <v>-6.9750910394156635E-3</v>
+      </c>
+      <c r="AQ31" s="10">
+        <f t="shared" si="75"/>
+        <v>3.3091441782774025E-2</v>
+      </c>
+      <c r="AR31" s="10">
+        <f t="shared" si="75"/>
+        <v>5.9497701044001539E-2</v>
+      </c>
+      <c r="AT31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="AQ31" s="6">
-        <f>AQ29+AQ30</f>
-        <v>1059.599809472488</v>
+      <c r="AU31" s="6">
+        <f>AU29+AU30</f>
+        <v>1453.8200963842446</v>
       </c>
     </row>
-    <row r="32" spans="2:136" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:140" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
         <v>22</v>
       </c>
@@ -3862,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" ref="O32" si="77">O16/O15</f>
+        <f t="shared" ref="O32" si="76">O16/O15</f>
         <v>-2.9381519024533566E-4</v>
       </c>
       <c r="P32" s="10">
@@ -3882,94 +4009,98 @@
         <v>3.8084874863982586E-3</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" ref="T32:V32" si="78">T16/T15</f>
+        <f t="shared" ref="T32:V32" si="77">T16/T15</f>
         <v>4.4288614135449336E-3</v>
       </c>
       <c r="U32" s="10">
+        <f t="shared" si="77"/>
+        <v>4.086636697997548E-4</v>
+      </c>
+      <c r="V32" s="10">
+        <f t="shared" si="77"/>
+        <v>-2.2162029056882549E-3</v>
+      </c>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
+      <c r="AB32" s="10">
+        <f t="shared" ref="AB32:AE32" si="78">AB16/AB15</f>
+        <v>0</v>
+      </c>
+      <c r="AC32" s="10">
         <f t="shared" si="78"/>
-        <v>4.086636697997548E-4</v>
-      </c>
-      <c r="V32" s="10">
+        <v>2.7797081306462821E-4</v>
+      </c>
+      <c r="AD32" s="10">
         <f t="shared" si="78"/>
-        <v>2.7934326398636809E-3</v>
-      </c>
-      <c r="X32" s="10">
-        <f t="shared" ref="X32:AA32" si="79">X16/X15</f>
-        <v>0</v>
-      </c>
-      <c r="Y32" s="10">
-        <f t="shared" si="79"/>
-        <v>2.7797081306462821E-4</v>
-      </c>
-      <c r="Z32" s="10">
-        <f t="shared" si="79"/>
         <v>3.8762694782541279E-5</v>
       </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="79"/>
+      <c r="AE32" s="10">
+        <f t="shared" si="78"/>
         <v>-3.0672494440610386E-4</v>
       </c>
-      <c r="AB32" s="10">
-        <f t="shared" ref="AB32" si="80">AB16/AB15</f>
+      <c r="AF32" s="10">
+        <f t="shared" ref="AF32" si="79">AF16/AF15</f>
         <v>-3.5369433735365894E-4</v>
       </c>
-      <c r="AC32" s="10">
-        <f>AC16/AC15</f>
+      <c r="AG32" s="10">
+        <f>AG16/AG15</f>
         <v>-4.4234739015039799E-4</v>
       </c>
-      <c r="AD32" s="10">
-        <f t="shared" ref="AD32:AN32" si="81">AD16/AD15</f>
-        <v>2.9335295328354223E-3</v>
-      </c>
-      <c r="AE32" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="AF32" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="AG32" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
       <c r="AH32" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
+        <f t="shared" ref="AH32:AR32" si="80">AH16/AH15</f>
+        <v>8.8872431031290517E-4</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AL32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AM32" s="10">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="AP32" s="1" t="s">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AO32" s="10">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AP32" s="10">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="10">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AR32" s="10">
+        <f t="shared" si="80"/>
+        <v>0</v>
+      </c>
+      <c r="AT32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AQ32" s="5">
-        <f>AQ31/AN18</f>
-        <v>3.268352280914522</v>
+      <c r="AU32" s="5">
+        <f>AU31/AR18</f>
+        <v>4.473292604259214</v>
       </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:47" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
         <v>49</v>
       </c>
@@ -3982,7 +4113,7 @@
         <v>-4.1583969465648858</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" ref="O33" si="82">O17/O6</f>
+        <f t="shared" ref="O33" si="81">O17/O6</f>
         <v>-3.9426751592356695</v>
       </c>
       <c r="P33" s="10">
@@ -4002,108 +4133,112 @@
         <v>-1.5582978723404257</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" ref="T33:V33" si="83">T17/T6</f>
+        <f t="shared" ref="T33:V33" si="82">T17/T6</f>
         <v>-2.0797995373939866</v>
       </c>
       <c r="U33" s="10">
+        <f t="shared" si="82"/>
+        <v>-2.9067142008318481</v>
+      </c>
+      <c r="V33" s="10">
+        <f t="shared" si="82"/>
+        <v>-1.5572986416682604</v>
+      </c>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
+      <c r="AB33" s="10">
+        <f t="shared" ref="AB33:AE33" si="83">AB17/AB6</f>
+        <v>-60.282608695652172</v>
+      </c>
+      <c r="AC33" s="10">
         <f t="shared" si="83"/>
-        <v>-2.9067142008318481</v>
-      </c>
-      <c r="V33" s="10">
+        <v>-179.82499999999999</v>
+      </c>
+      <c r="AD33" s="10">
         <f t="shared" si="83"/>
-        <v>-1.8452284034373587</v>
-      </c>
-      <c r="X33" s="10">
-        <f t="shared" ref="X33:AA33" si="84">X17/X6</f>
-        <v>-60.282608695652172</v>
-      </c>
-      <c r="Y33" s="10">
-        <f t="shared" si="84"/>
-        <v>-179.82499999999999</v>
-      </c>
-      <c r="Z33" s="10">
-        <f t="shared" si="84"/>
         <v>-95.191881918819192</v>
       </c>
-      <c r="AA33" s="10">
-        <f t="shared" si="84"/>
+      <c r="AE33" s="10">
+        <f t="shared" si="83"/>
         <v>-2.1448536665570535</v>
       </c>
-      <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="85">AB17/AB6</f>
+      <c r="AF33" s="10">
+        <f t="shared" ref="AF33" si="84">AF17/AF6</f>
         <v>-4.7510498908113563</v>
       </c>
-      <c r="AC33" s="10">
-        <f>AC17/AC6</f>
+      <c r="AG33" s="10">
+        <f>AG17/AG6</f>
         <v>-3.3597425105224072</v>
       </c>
-      <c r="AD33" s="10">
-        <f t="shared" ref="AD33:AN33" si="86">AD17/AD6</f>
-        <v>-1.7302337992897758</v>
-      </c>
-      <c r="AE33" s="10">
-        <f t="shared" si="86"/>
-        <v>-1.052362693378766</v>
-      </c>
-      <c r="AF33" s="10">
-        <f t="shared" si="86"/>
-        <v>-0.57883748217352526</v>
-      </c>
-      <c r="AG33" s="10">
-        <f t="shared" si="86"/>
-        <v>-0.28480775780966422</v>
-      </c>
       <c r="AH33" s="10">
-        <f t="shared" si="86"/>
-        <v>-0.1402098146003718</v>
+        <f t="shared" ref="AH33:AR33" si="85">AH17/AH6</f>
+        <v>-1.9931299401639948</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" si="86"/>
-        <v>-5.7134311595474961E-2</v>
+        <f t="shared" si="85"/>
+        <v>-1.3084292433084632</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" si="86"/>
-        <v>-4.7355626497692874E-3</v>
+        <f t="shared" si="85"/>
+        <v>-0.79924243255697802</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" si="86"/>
-        <v>3.3630164186066382E-2</v>
+        <f t="shared" si="85"/>
+        <v>-0.41429945130460266</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" si="86"/>
-        <v>6.80316999220201E-2</v>
+        <f t="shared" si="85"/>
+        <v>-0.17559554094098284</v>
       </c>
       <c r="AM33" s="10">
-        <f t="shared" si="86"/>
-        <v>8.8996074099011127E-2</v>
+        <f t="shared" si="85"/>
+        <v>-6.643402494241285E-2</v>
       </c>
       <c r="AN33" s="10">
-        <f t="shared" si="86"/>
-        <v>0.10698229245614756</v>
-      </c>
-      <c r="AP33" s="1" t="s">
+        <f t="shared" si="85"/>
+        <v>2.3300971294132743E-2</v>
+      </c>
+      <c r="AO33" s="10">
+        <f t="shared" si="85"/>
+        <v>7.9803104703278963E-2</v>
+      </c>
+      <c r="AP33" s="10">
+        <f t="shared" si="85"/>
+        <v>0.11264489601863151</v>
+      </c>
+      <c r="AQ33" s="10">
+        <f t="shared" si="85"/>
+        <v>0.14230969083577363</v>
+      </c>
+      <c r="AR33" s="10">
+        <f t="shared" si="85"/>
+        <v>0.15921871104891422</v>
+      </c>
+      <c r="AT33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AQ33" s="5">
+      <c r="AU33" s="5">
         <f>Main!D3</f>
         <v>12.84</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP34" s="2" t="s">
+    <row r="34" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="AQ34" s="11">
-        <f>AQ32/AQ33-1</f>
-        <v>-0.74545542983531754</v>
+      <c r="AU34" s="11">
+        <f>AU32/AU33-1</f>
+        <v>-0.65161272552498328</v>
       </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.3">
-      <c r="AP35" s="1" t="s">
+    <row r="35" spans="2:47" x14ac:dyDescent="0.3">
+      <c r="AT35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AQ35" s="7" t="s">
-        <v>66</v>
+      <c r="AU35" s="7" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
